--- a/finance/_refresh_jih-global.xlsx
+++ b/finance/_refresh_jih-global.xlsx
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="B19" s="12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>Cap on revenue sailings/day — ~1 sailing/70min in a 12h window; a believable on-demand premium duty cycle, not capacity-max (Jaideep 2026-06-19).</t>
+          <t>Cap on revenue sailings/day — MID headline duty cycle; thin=12 / full=18 bookends in _utilization_scenarios (Jaideep 2026-06-21).</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
         <v>0.45</v>
       </c>
       <c r="C31" s="19" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="F31" s="14" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>0.55</v>
       </c>
       <c r="C32" s="19" t="n">
-        <v>0.55</v>
+        <v>0.65</v>
       </c>
       <c r="F32" s="14" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>0.7</v>
       </c>
       <c r="C33" s="19" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="F33" s="14" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v/>
       </c>
       <c r="K4" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J4,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J4,1))</f>
         <v/>
       </c>
       <c r="L4" s="34">
@@ -2367,7 +2367,7 @@
         <v/>
       </c>
       <c r="K5" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J5,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J5,1))</f>
         <v/>
       </c>
       <c r="L5" s="34">
@@ -2555,7 +2555,7 @@
         <v/>
       </c>
       <c r="K6" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J6,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J6,1))</f>
         <v/>
       </c>
       <c r="L6" s="34">
@@ -2751,7 +2751,7 @@
         <v/>
       </c>
       <c r="K7" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J7,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J7,1))</f>
         <v/>
       </c>
       <c r="L7" s="34">
@@ -2947,7 +2947,7 @@
         <v/>
       </c>
       <c r="K8" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J8,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J8,1))</f>
         <v/>
       </c>
       <c r="L8" s="34">
@@ -3143,7 +3143,7 @@
         <v/>
       </c>
       <c r="K9" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J9,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J9,1))</f>
         <v/>
       </c>
       <c r="L9" s="34">
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="K10" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J10,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J10,1))</f>
         <v/>
       </c>
       <c r="L10" s="34">
@@ -3535,7 +3535,7 @@
         <v/>
       </c>
       <c r="K11" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J11,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J11,1))</f>
         <v/>
       </c>
       <c r="L11" s="34">
@@ -3723,7 +3723,7 @@
         <v/>
       </c>
       <c r="K12" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J12,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J12,1))</f>
         <v/>
       </c>
       <c r="L12" s="34">
@@ -3919,7 +3919,7 @@
         <v/>
       </c>
       <c r="K13" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J13,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J13,1))</f>
         <v/>
       </c>
       <c r="L13" s="34">
@@ -4115,7 +4115,7 @@
         <v/>
       </c>
       <c r="K14" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J14,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J14,1))</f>
         <v/>
       </c>
       <c r="L14" s="34">
@@ -4311,7 +4311,7 @@
         <v/>
       </c>
       <c r="K15" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J15,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J15,1))</f>
         <v/>
       </c>
       <c r="L15" s="34">
@@ -4507,7 +4507,7 @@
         <v/>
       </c>
       <c r="K16" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J16,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J16,1))</f>
         <v/>
       </c>
       <c r="L16" s="34">
@@ -4703,7 +4703,7 @@
         <v/>
       </c>
       <c r="K17" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J17,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J17,1))</f>
         <v/>
       </c>
       <c r="L17" s="34">
@@ -4899,7 +4899,7 @@
         <v/>
       </c>
       <c r="K18" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J18,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J18,1))</f>
         <v/>
       </c>
       <c r="L18" s="34">
@@ -5095,7 +5095,7 @@
         <v/>
       </c>
       <c r="K19" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J19,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J19,1))</f>
         <v/>
       </c>
       <c r="L19" s="34">
@@ -5291,7 +5291,7 @@
         <v/>
       </c>
       <c r="K20" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J20,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J20,1))</f>
         <v/>
       </c>
       <c r="L20" s="34">
@@ -5479,7 +5479,7 @@
         <v/>
       </c>
       <c r="K21" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J21,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J21,1))</f>
         <v/>
       </c>
       <c r="L21" s="34">
@@ -5675,7 +5675,7 @@
         <v/>
       </c>
       <c r="K22" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J22,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J22,1))</f>
         <v/>
       </c>
       <c r="L22" s="34">
@@ -5871,7 +5871,7 @@
         <v/>
       </c>
       <c r="K23" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J23,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J23,1))</f>
         <v/>
       </c>
       <c r="L23" s="34">
@@ -6067,7 +6067,7 @@
         <v/>
       </c>
       <c r="K24" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J24,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J24,1))</f>
         <v/>
       </c>
       <c r="L24" s="34">
@@ -6263,7 +6263,7 @@
         <v/>
       </c>
       <c r="K25" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J25,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J25,1))</f>
         <v/>
       </c>
       <c r="L25" s="34">
@@ -6459,7 +6459,7 @@
         <v/>
       </c>
       <c r="K26" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J26,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J26,1))</f>
         <v/>
       </c>
       <c r="L26" s="34">
@@ -6655,7 +6655,7 @@
         <v/>
       </c>
       <c r="K27" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J27,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J27,1))</f>
         <v/>
       </c>
       <c r="L27" s="34">
@@ -6843,7 +6843,7 @@
         <v/>
       </c>
       <c r="K28" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J28,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J28,1))</f>
         <v/>
       </c>
       <c r="L28" s="34">
@@ -7039,7 +7039,7 @@
         <v/>
       </c>
       <c r="K29" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J29,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J29,1))</f>
         <v/>
       </c>
       <c r="L29" s="34">
@@ -7235,7 +7235,7 @@
         <v/>
       </c>
       <c r="K30" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J30,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J30,1))</f>
         <v/>
       </c>
       <c r="L30" s="34">
@@ -7431,7 +7431,7 @@
         <v/>
       </c>
       <c r="K31" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J31,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J31,1))</f>
         <v/>
       </c>
       <c r="L31" s="34">
@@ -7627,7 +7627,7 @@
         <v/>
       </c>
       <c r="K32" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J32,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J32,1))</f>
         <v/>
       </c>
       <c r="L32" s="34">
@@ -7823,7 +7823,7 @@
         <v/>
       </c>
       <c r="K33" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J33,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J33,1))</f>
         <v/>
       </c>
       <c r="L33" s="34">
@@ -8019,7 +8019,7 @@
         <v/>
       </c>
       <c r="K34" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J34,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J34,1))</f>
         <v/>
       </c>
       <c r="L34" s="34">
@@ -8215,7 +8215,7 @@
         <v/>
       </c>
       <c r="K35" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J35,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J35,1))</f>
         <v/>
       </c>
       <c r="L35" s="34">
@@ -8403,7 +8403,7 @@
         <v/>
       </c>
       <c r="K36" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J36,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J36,1))</f>
         <v/>
       </c>
       <c r="L36" s="34">
@@ -8599,7 +8599,7 @@
         <v/>
       </c>
       <c r="K37" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J37,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J37,1))</f>
         <v/>
       </c>
       <c r="L37" s="34">
@@ -8795,7 +8795,7 @@
         <v/>
       </c>
       <c r="K38" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J38,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J38,1))</f>
         <v/>
       </c>
       <c r="L38" s="34">
@@ -8991,7 +8991,7 @@
         <v/>
       </c>
       <c r="K39" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J39,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J39,1))</f>
         <v/>
       </c>
       <c r="L39" s="34">
@@ -9187,7 +9187,7 @@
         <v/>
       </c>
       <c r="K40" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J40,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J40,1))</f>
         <v/>
       </c>
       <c r="L40" s="34">
@@ -9383,7 +9383,7 @@
         <v/>
       </c>
       <c r="K41" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J41,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J41,1))</f>
         <v/>
       </c>
       <c r="L41" s="34">
@@ -9579,7 +9579,7 @@
         <v/>
       </c>
       <c r="K42" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J42,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J42,1))</f>
         <v/>
       </c>
       <c r="L42" s="34">
@@ -9775,7 +9775,7 @@
         <v/>
       </c>
       <c r="K43" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J43,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J43,1))</f>
         <v/>
       </c>
       <c r="L43" s="34">
@@ -9971,7 +9971,7 @@
         <v/>
       </c>
       <c r="K44" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J44,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J44,1))</f>
         <v/>
       </c>
       <c r="L44" s="34">
@@ -10167,7 +10167,7 @@
         <v/>
       </c>
       <c r="K45" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J45,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J45,1))</f>
         <v/>
       </c>
       <c r="L45" s="34">
@@ -10363,7 +10363,7 @@
         <v/>
       </c>
       <c r="K46" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J46,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J46,1))</f>
         <v/>
       </c>
       <c r="L46" s="34">
@@ -10709,13 +10709,13 @@
         </is>
       </c>
       <c r="B6" s="39" t="n">
-        <v>0.834</v>
+        <v>0.8536</v>
       </c>
       <c r="C6" s="39" t="n">
-        <v>0.834</v>
+        <v>0.8536</v>
       </c>
       <c r="D6" s="39" t="n">
-        <v>0.884</v>
+        <v>0.9036000000000001</v>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
@@ -10787,11 +10787,11 @@
         </is>
       </c>
       <c r="C11" s="39" t="n">
-        <v>0.834</v>
+        <v>0.8536</v>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>Captive sole-operator capture (~83%) that builds the published floor; M_today = floor ÷ this = the true corridor spend pool.</t>
+          <t>Captive sole-operator capture (~85%) that builds the published floor; M_today = floor ÷ this = the true corridor spend pool.</t>
         </is>
       </c>
     </row>
@@ -10864,7 +10864,7 @@
     <row r="18">
       <c r="A18" s="25" t="inlineStr">
         <is>
-          <t>SOM full network (~83% capture, today, +greenfield)</t>
+          <t>SOM full network (~85% capture, today, +greenfield)</t>
         </is>
       </c>
       <c r="B18" s="50">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>Floor posture (~83% captive capture, today's demand) extended across the whole mapped network.</t>
+          <t>Floor posture (~85% captive capture, today's demand) extended across the whole mapped network.</t>
         </is>
       </c>
     </row>

--- a/finance/_refresh_jih-global.xlsx
+++ b/finance/_refresh_jih-global.xlsx
@@ -1311,7 +1311,7 @@
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>Cap on revenue sailings/day — MID headline duty cycle; thin=12 / full=18 bookends in _utilization_scenarios (Jaideep 2026-06-21).</t>
+          <t>Cap on revenue sailings/day — 15 across thin/mid/full scenarios (Jaideep 2026-06-21).</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
         <v>0.7</v>
       </c>
       <c r="C33" s="19" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="F33" s="14" t="inlineStr">
         <is>

--- a/finance/_refresh_jih-global.xlsx
+++ b/finance/_refresh_jih-global.xlsx
@@ -27,23 +27,23 @@
     <definedName name="dwell_min">'Assumptions'!$B$18</definedName>
     <definedName name="max_tpd">'Assumptions'!$B$19</definedName>
     <definedName name="crew_factor">'Assumptions'!$B$20</definedName>
-    <definedName name="ins_pct">'Assumptions'!$B$21</definedName>
-    <definedName name="charge_berth">'Assumptions'!$B$22</definedName>
-    <definedName name="mech_uptime">'Assumptions'!$B$23</definedName>
-    <definedName name="capture">'Assumptions'!$B$24</definedName>
-    <definedName name="capture_captive">'Assumptions'!$B$25</definedName>
-    <definedName name="discount">'Assumptions'!$B$26</definedName>
-    <definedName name="diesel_co2pg">'Assumptions'!$B$27</definedName>
-    <definedName name="load_thin">'Assumptions'!$B$31</definedName>
-    <definedName name="revleg_thin">'Assumptions'!$C$31</definedName>
-    <definedName name="load_mid">'Assumptions'!$B$32</definedName>
-    <definedName name="revleg_mid">'Assumptions'!$C$32</definedName>
-    <definedName name="load_full">'Assumptions'!$B$33</definedName>
-    <definedName name="revleg_full">'Assumptions'!$C$33</definedName>
-    <definedName name="band_tbl">'Assumptions'!$A$31:$C$33</definedName>
-    <definedName name="scenario">'Assumptions'!$B$35</definedName>
-    <definedName name="load_sel">'Assumptions'!$B$36</definedName>
-    <definedName name="revleg_sel">'Assumptions'!$B$37</definedName>
+    <definedName name="mech_uptime">'Assumptions'!$B$21</definedName>
+    <definedName name="capture">'Assumptions'!$B$22</definedName>
+    <definedName name="capture_captive">'Assumptions'!$B$23</definedName>
+    <definedName name="discount">'Assumptions'!$B$24</definedName>
+    <definedName name="diesel_co2pg">'Assumptions'!$B$25</definedName>
+    <definedName name="ins_pct">'Assumptions'!$B$29</definedName>
+    <definedName name="charge_berth">'Assumptions'!$B$30</definedName>
+    <definedName name="load_thin">'Assumptions'!$B$34</definedName>
+    <definedName name="revleg_thin">'Assumptions'!$C$34</definedName>
+    <definedName name="load_mid">'Assumptions'!$B$35</definedName>
+    <definedName name="revleg_mid">'Assumptions'!$C$35</definedName>
+    <definedName name="load_full">'Assumptions'!$B$36</definedName>
+    <definedName name="revleg_full">'Assumptions'!$C$36</definedName>
+    <definedName name="band_tbl">'Assumptions'!$A$34:$C$36</definedName>
+    <definedName name="scenario">'Assumptions'!$B$38</definedName>
+    <definedName name="load_sel">'Assumptions'!$B$39</definedName>
+    <definedName name="revleg_sel">'Assumptions'!$B$40</definedName>
     <definedName name="country_opex">'Country opex'!$A$4:$G$4</definedName>
     <definedName name="som_floor_fleet">'Corridor economics'!$D$52</definedName>
     <definedName name="som_floor_rev">'Corridor economics'!$E$52</definedName>
@@ -686,7 +686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B27"/>
+  <dimension ref="B2:B36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -765,84 +765,143 @@
     <row r="14">
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>EBITDA  = REVENUE − OPEX   (energy + captain + marina/overhead + maintenance)</t>
+          <t>EBITDA  = REVENUE − OPEX</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    OPEX = energy + crew + berth/port admin + maintenance + vessel insurance + fast-charge berth</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>PAYBACK = vessel CAPEX ÷ EBITDA</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="2" t="inlineStr"/>
-    </row>
     <row r="17">
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>From demand pool to fleet &amp; market size</t>
-        </is>
-      </c>
+      <c r="B17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Navier serviceable rides/yr = corridor demand pool × capture rate (10% on contested corridors; ~90% on captive sole-operator transfer legs — see the per-row Capture % column)</t>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>OPEX lines (per boat, per year — no double-counting)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Vessels supported = FLOOR(Navier rides/yr ÷ pax/yr per boat);  Market rev = vessels × rev/boat. The 'Market sizing' tab rolls these up into the SOM → SAM → TAM ladder.</t>
+          <t>Energy — variable propulsion cost: kWh on revenue sailings × local $/kWh (Country opex tab). Excludes utility demand charges.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Crew — fully-loaded captain + relief: local captain wage × crew FTE factor (Country opex + Assumptions).</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>The scenario toggle (what we flex)</t>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Berth &amp; port admin — fixed annual berth, port fees, and local marine admin (Country opex tab). Excludes vessel H&amp;M+P&amp;I and fast-charge infrastructure.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>'Corridor economics' has a SCENARIO cell = THIN / MID / FULL. It flexes two levers: load factor (how full the boat is) and revenue-leg factor (how many legs earn full fare). MID is the headline. Change that one cell and the whole model recomputes. The right-hand Payback THIN/MID/FULL columns always show all three at once.</t>
+          <t>Maintenance — vessel annual maintenance reserve (Assumptions tab).</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Vessel insurance — commercial H&amp;M + P&amp;I as % of regional CAPEX (Assumptions % × Country opex CAPEX column).</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Fast-charge berth — dedicated fast-charge berth slot + utility demand charges (Assumptions default; overridable per market). Separate from per-kWh energy and berth/port admin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>From demand pool to fleet &amp; market size</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Navier serviceable rides/yr = corridor demand pool × capture rate (10% on contested corridors; ~90% on captive sole-operator transfer legs — see the per-row Capture % column)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Vessels supported = FLOOR(Navier rides/yr ÷ pax/yr per boat);  Market rev = vessels × rev/boat. The 'Market sizing' tab rolls these up into the SOM → SAM → TAM ladder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>The scenario toggle (what we flex)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>'Corridor economics' has a SCENARIO cell = THIN / MID / FULL. It flexes load factor (occupancy) and revenue-leg factor (share of legs that earn full fare). Max trips/day is fixed across all three bands (see Assumptions). MID is the headline. Change SCENARIO and the whole model recomputes. Payback THIN/MID/FULL columns always show all three at once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>Colour &amp; provenance legend</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="6" t="inlineStr">
+    <row r="34">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">   Yellow = INPUTS you can change (fare, distance, demand, weather).</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="7" t="inlineStr">
+    <row r="35">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">   Green  = COMPUTED by formula.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="2" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   Every fare &amp; demand figure carries a Source tier (T1 official → T5 modeled) + Confidence (high/med/low). Null beats a wrong number: no published pool → blank, not a guess.</t>
         </is>
@@ -859,7 +918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1348,11 +1407,11 @@
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>Insurance (% of capex/yr)</t>
+          <t>Mechanical uptime</t>
         </is>
       </c>
       <c r="B21" s="17" t="n">
-        <v>0.025</v>
+        <v>0.75</v>
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
@@ -1361,7 +1420,7 @@
       </c>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
@@ -1371,29 +1430,25 @@
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>H&amp;M + P&amp;I for a commercial passenger vessel ~2.5%/yr of capex; scales with regional capex overrides (Jaideep 2026-06-19).</t>
+          <t>Blade luxury aviation ~75-80% reliability uptime</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>Charging &amp; berth (additional to marina+energy)</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="n">
-        <v>18000</v>
+          <t>Navier capture rate</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n">
+        <v>0.1</v>
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>USD/yr</t>
-        </is>
-      </c>
-      <c r="D22" s="13" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
+          <t>frac</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr"/>
       <c r="E22" s="13" t="inlineStr">
         <is>
           <t>med</t>
@@ -1401,29 +1456,25 @@
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>Dedicated fast-charge berth + demand charges, ADDITIONAL to marina overhead and energy (Jaideep 2026-06-19). L3-overridable.</t>
+          <t>Navier wins ~10% of a CONTESTED corridor demand pool (locked). Captive sole-operator transfer legs (captive:true / luxury_charter / hospitality archetypes) carry the captive rate instead — see per-row Capture %.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>Mechanical uptime</t>
+          <t>Captive capture rate (A′ corridors)</t>
         </is>
       </c>
       <c r="B23" s="17" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
           <t>frac</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
+      <c r="D23" s="13" t="inlineStr"/>
       <c r="E23" s="13" t="inlineStr">
         <is>
           <t>med</t>
@@ -1431,255 +1482,303 @@
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>Blade luxury aviation ~75-80% reliability uptime</t>
+          <t>Sole-operator water-access-only transfer legs (captive:true or luxury_charter/hospitality archetype): Navier IS the transfer fleet — capture ~90%. Applied per-row in the Capture % column.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>Navier capture rate</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="n">
-        <v>0.1</v>
+          <t>Discount factor (vs comparable fare)</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="n">
+        <v>1</v>
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
           <t>frac</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr"/>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>Navier wins ~10% of a CONTESTED corridor demand pool (locked). Captive sole-operator transfer legs (captive:true / luxury_charter / hospitality archetypes) carry the captive rate instead — see per-row Capture %.</t>
+          <t>Market parity — better product, not cheaper (locked).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>Captive capture rate (A′ corridors)</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="n">
-        <v>0.9</v>
+          <t>Diesel CO₂ per gallon</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="n">
+        <v>10.21</v>
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
+          <t>kg/gal</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="inlineStr">
+        <is>
+          <t>US EPA: 10.21 kg CO2 per gallon marine/diesel</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>OPEX defaults  (global fallbacks — localized energy, crew, berth admin on Country opex tab)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>Conf.</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>Source / note</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>Vessel insurance — H&amp;M + P&amp;I (% of CAPEX/yr)</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
           <t>frac</t>
         </is>
       </c>
-      <c r="D25" s="13" t="inlineStr"/>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
         <is>
           <t>med</t>
         </is>
       </c>
-      <c r="F25" s="14" t="inlineStr">
-        <is>
-          <t>Sole-operator water-access-only transfer legs (captive:true or luxury_charter/hospitality archetype): Navier IS the transfer fleet — capture ~90%. Applied per-row in the Capture % column.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>Discount factor (vs comparable fare)</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="13" t="inlineStr">
-        <is>
-          <t>frac</t>
-        </is>
-      </c>
-      <c r="D26" s="13" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F26" s="14" t="inlineStr">
-        <is>
-          <t>Market parity — better product, not cheaper (locked).</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>Diesel CO₂ per gallon</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="n">
-        <v>10.21</v>
-      </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>kg/gal</t>
-        </is>
-      </c>
-      <c r="D27" s="13" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="E27" s="13" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="inlineStr">
-        <is>
-          <t>US EPA: 10.21 kg CO2 per gallon marine/diesel</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>Utilization scenarios  (the two levers we flex)</t>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>Commercial vessel H&amp;M + P&amp;I ~2.5%/yr of regional CAPEX. Separate from berth/port admin in Country opex (Jaideep 2026-06-19).. Multiplied by regional CAPEX (Country opex col G). Not included in berth/port admin.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>Fast-charge berth &amp; demand charges (global default)</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="n">
+        <v>18000</v>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>USD/yr</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>Dedicated fast-charge berth slot + utility demand charges. Excludes per-kWh propulsion energy and berth/port admin (Jaideep 2026-06-19). L3-overridable per market.. Dedicated charge berth + utility demand charges. Excludes per-kWh propulsion energy and berth/port admin. L3-overridable per market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>Utilization scenarios  (load factor + revenue-leg factor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="B30" s="10" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
         <is>
           <t>Load factor</t>
         </is>
       </c>
-      <c r="C30" s="10" t="inlineStr">
+      <c r="C33" s="10" t="inlineStr">
         <is>
           <t>Rev-leg factor</t>
         </is>
       </c>
-      <c r="D30" s="10" t="inlineStr"/>
-      <c r="E30" s="10" t="inlineStr"/>
-      <c r="F30" s="10" t="inlineStr">
+      <c r="D33" s="10" t="inlineStr"/>
+      <c r="E33" s="10" t="inlineStr"/>
+      <c r="F33" s="10" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="18" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="18" t="inlineStr">
         <is>
           <t>THIN</t>
         </is>
       </c>
-      <c r="B31" s="19" t="n">
+      <c r="B34" s="19" t="n">
         <v>0.45</v>
       </c>
-      <c r="C31" s="19" t="n">
+      <c r="C34" s="19" t="n">
         <v>0.55</v>
       </c>
-      <c r="F31" s="14" t="inlineStr">
+      <c r="F34" s="14" t="inlineStr">
         <is>
           <t>thin/one-way/seasonal corridor — conservative floor</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="18" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="18" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="B32" s="19" t="n">
+      <c r="B35" s="19" t="n">
         <v>0.55</v>
       </c>
-      <c r="C32" s="19" t="n">
+      <c r="C35" s="19" t="n">
         <v>0.65</v>
       </c>
-      <c r="F32" s="14" t="inlineStr">
+      <c r="F35" s="14" t="inlineStr">
         <is>
           <t>HEADLINE — realistic busy two-way corridor</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="18" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="18" t="inlineStr">
         <is>
           <t>FULL</t>
         </is>
       </c>
-      <c r="B33" s="19" t="n">
+      <c r="B36" s="19" t="n">
         <v>0.7</v>
       </c>
-      <c r="C33" s="19" t="n">
+      <c r="C36" s="19" t="n">
         <v>0.75</v>
       </c>
-      <c r="F33" s="14" t="inlineStr">
+      <c r="F36" s="14" t="inlineStr">
         <is>
           <t>mature/dense corridor — optimistic ceiling</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="20" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="20" t="inlineStr">
         <is>
           <t>SCENARIO (toggle me)</t>
         </is>
       </c>
-      <c r="B35" s="21" t="inlineStr">
+      <c r="B38" s="21" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="C35" s="22" t="inlineStr">
+      <c r="C38" s="22" t="inlineStr">
         <is>
           <t>← set THIN / MID / FULL</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>Selected load factor</t>
         </is>
       </c>
-      <c r="B36" s="23">
-        <f>VLOOKUP(scenario,'Assumptions'!$A$31:$C$33,2,FALSE)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+      <c r="B39" s="23">
+        <f>VLOOKUP(scenario,'Assumptions'!$A$34:$C$36,2,FALSE)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>Selected rev-leg factor</t>
         </is>
       </c>
-      <c r="B37" s="23">
-        <f>VLOOKUP(scenario,'Assumptions'!$A$31:$C$33,3,FALSE)</f>
+      <c r="B40" s="23">
+        <f>VLOOKUP(scenario,'Assumptions'!$A$34:$C$36,3,FALSE)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A3:F3"/>
+  <mergeCells count="5">
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A3:F3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="B38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"THIN,MID,FULL"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1709,7 +1808,7 @@
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>Country opex — L3 localized layer (VLOOKUP target for the engine)</t>
+          <t>Country opex — localized inputs (crew, energy, berth admin, CAPEX)</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1835,7 @@
       </c>
       <c r="E3" s="24" t="inlineStr">
         <is>
-          <t>Marina $/yr</t>
+          <t>Berth &amp; port admin $/yr</t>
         </is>
       </c>
       <c r="F3" s="24" t="inlineStr">
@@ -1751,7 +1850,7 @@
       </c>
       <c r="H3" s="24" t="inlineStr">
         <is>
-          <t>Source notes (captain | energy | marina)</t>
+          <t>Source notes (crew | energy | berth admin)</t>
         </is>
       </c>
     </row>
@@ -1824,10 +1923,10 @@
     <col width="11" customWidth="1" min="20" max="20"/>
     <col width="10" customWidth="1" min="21" max="21"/>
     <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
     <col width="9" customWidth="1" min="24" max="24"/>
-    <col width="10" customWidth="1" min="25" max="25"/>
-    <col width="11" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
     <col width="11" customWidth="1" min="27" max="27"/>
     <col width="10" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
@@ -1988,7 +2087,7 @@
       </c>
       <c r="W3" s="24" t="inlineStr">
         <is>
-          <t>Marina/yr</t>
+          <t>Berth &amp; port admin/yr</t>
         </is>
       </c>
       <c r="X3" s="24" t="inlineStr">
@@ -1998,12 +2097,12 @@
       </c>
       <c r="Y3" s="24" t="inlineStr">
         <is>
-          <t>Insurance/yr</t>
+          <t>Vessel insurance/yr</t>
         </is>
       </c>
       <c r="Z3" s="24" t="inlineStr">
         <is>
-          <t>Charge+berth/yr</t>
+          <t>Fast-charge berth/yr</t>
         </is>
       </c>
       <c r="AA3" s="24" t="inlineStr">

--- a/finance/_refresh_jih-global.xlsx
+++ b/finance/_refresh_jih-global.xlsx
@@ -179,7 +179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -315,6 +315,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1898,7 +1904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX52"/>
+  <dimension ref="A1:AY53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1943,14 +1949,15 @@
     <col width="9" customWidth="1" min="40" max="40"/>
     <col width="13" customWidth="1" min="41" max="41"/>
     <col width="26" customWidth="1" min="42" max="42"/>
-    <col width="16" customWidth="1" min="43" max="43"/>
+    <col width="14" customWidth="1" min="43" max="43"/>
     <col width="16" customWidth="1" min="44" max="44"/>
-    <col width="9" customWidth="1" min="45" max="45"/>
+    <col width="16" customWidth="1" min="45" max="45"/>
     <col width="9" customWidth="1" min="46" max="46"/>
     <col width="9" customWidth="1" min="47" max="47"/>
     <col width="9" customWidth="1" min="48" max="48"/>
-    <col width="50" customWidth="1" min="49" max="49"/>
+    <col width="9" customWidth="1" min="49" max="49"/>
     <col width="50" customWidth="1" min="50" max="50"/>
+    <col width="50" customWidth="1" min="51" max="51"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2187,40 +2194,45 @@
       </c>
       <c r="AQ3" s="24" t="inlineStr">
         <is>
+          <t>Floor bucket (aggregate status)</t>
+        </is>
+      </c>
+      <c r="AR3" s="24" t="inlineStr">
+        <is>
           <t>Forward SAM (2030-dated; held OUT of grounded floor)</t>
         </is>
       </c>
-      <c r="AR3" s="24" t="inlineStr">
+      <c r="AS3" s="24" t="inlineStr">
         <is>
           <t>Upside tier (LB-99; held OUT of grounded floor)</t>
         </is>
       </c>
-      <c r="AS3" s="24" t="inlineStr">
+      <c r="AT3" s="24" t="inlineStr">
         <is>
           <t>Fleet ceiling (captive villas/25)</t>
         </is>
       </c>
-      <c r="AT3" s="24" t="inlineStr">
+      <c r="AU3" s="24" t="inlineStr">
         <is>
           <t>Payback THIN</t>
         </is>
       </c>
-      <c r="AU3" s="24" t="inlineStr">
+      <c r="AV3" s="24" t="inlineStr">
         <is>
           <t>Payback MID</t>
         </is>
       </c>
-      <c r="AV3" s="24" t="inlineStr">
+      <c r="AW3" s="24" t="inlineStr">
         <is>
           <t>Payback FULL</t>
         </is>
       </c>
-      <c r="AW3" s="24" t="inlineStr">
+      <c r="AX3" s="24" t="inlineStr">
         <is>
           <t>Fare source (provenance)</t>
         </is>
       </c>
-      <c r="AX3" s="24" t="inlineStr">
+      <c r="AY3" s="24" t="inlineStr">
         <is>
           <t>Demand source (provenance)</t>
         </is>
@@ -2378,7 +2390,7 @@
         <v/>
       </c>
       <c r="AL4" s="34">
-        <f>IF(OR(AG4="",R4=0),"",MIN(IF(AS4="",9.9E+99,AS4),FLOOR(AK4/R4,1)))</f>
+        <f>IF(OR(AG4="",R4=0),"",MIN(IF(AT4="",9.9E+99,AT4),FLOOR(AK4/R4,1)))</f>
         <v/>
       </c>
       <c r="AM4" s="38">
@@ -2386,7 +2398,7 @@
         <v/>
       </c>
       <c r="AN4" s="36">
-        <f>IF(OR(AG4="",R4=0),"",MIN(IF(AS4="",9.9E+99,AS4),AK4/R4))</f>
+        <f>IF(OR(AG4="",R4=0),"",MIN(IF(AT4="",9.9E+99,AT4),AK4/R4))</f>
         <v/>
       </c>
       <c r="AO4" s="38">
@@ -2394,29 +2406,34 @@
         <v/>
       </c>
       <c r="AP4" s="40" t="n"/>
-      <c r="AQ4" s="41" t="n"/>
+      <c r="AQ4" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR4" s="41" t="n"/>
-      <c r="AS4" s="42" t="n">
+      <c r="AS4" s="41" t="n"/>
+      <c r="AT4" s="42" t="n">
         <v>8</v>
       </c>
-      <c r="AT4" s="43">
+      <c r="AU4" s="43">
         <f>IF(((S4*pax_cap*load_thin*ROUND(K4*L4*revleg_thin,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_thin,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4))&lt;=0,"",VLOOKUP(B4,country_opex,7,FALSE)/((S4*pax_cap*load_thin*ROUND(K4*L4*revleg_thin,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_thin,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4)))</f>
         <v/>
       </c>
-      <c r="AU4" s="43">
+      <c r="AV4" s="43">
         <f>IF(((S4*pax_cap*load_mid*ROUND(K4*L4*revleg_mid,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_mid,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4))&lt;=0,"",VLOOKUP(B4,country_opex,7,FALSE)/((S4*pax_cap*load_mid*ROUND(K4*L4*revleg_mid,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_mid,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4)))</f>
         <v/>
       </c>
-      <c r="AV4" s="43">
+      <c r="AW4" s="43">
         <f>IF(((S4*pax_cap*load_full*ROUND(K4*L4*revleg_full,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_full,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4))&lt;=0,"",VLOOKUP(B4,country_opex,7,FALSE)/((S4*pax_cap*load_full*ROUND(K4*L4*revleg_full,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_full,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4)))</f>
         <v/>
       </c>
-      <c r="AW4" s="44" t="inlineStr">
+      <c r="AX4" s="44" t="inlineStr">
         <is>
           <t>Short 2.4nm/10-min North Male speedboat hop. maldivestour.guide: Kurumba round-trip speedboat USD 96/adult = $48/way. immaldives.com 2026 table: Kurumba shared speedboat $100-150 RT = $50-75/way. atolltransfer scheduled $25-120/way. Single-class resort speedboat (premium ~= standard on this short close hop); premium per-seat ~$60/way.</t>
         </is>
       </c>
-      <c r="AX4" s="44" t="inlineStr">
+      <c r="AY4" s="44" t="inlineStr">
         <is>
           <t>Modeled from resort key count. Kurumba Maldives (Vihamanafushi, North Malé): ~180 villas/keys (published resort/Virtuoso/booking figures). corridor_annual_oneway_pax = keys x 365 x occ(0.75) / avg_stay(7 nights) x guests/key(2) x 2 (arr+dep) ~= keys x 156. 180 keys -&gt; ~28,000 one-way pax/yr. Airport(MLE)&lt;-&gt;this resort is the sole transfer corridor (boat/seaplane only; no road/air alt - R3-EXCEPTION: arrivals = crossing ridership).</t>
         </is>
@@ -2568,7 +2585,7 @@
         <v/>
       </c>
       <c r="AL5" s="34">
-        <f>IF(OR(AG5="",R5=0),"",MIN(IF(AS5="",9.9E+99,AS5),FLOOR(AK5/R5,1)))</f>
+        <f>IF(OR(AG5="",R5=0),"",MIN(IF(AT5="",9.9E+99,AT5),FLOOR(AK5/R5,1)))</f>
         <v/>
       </c>
       <c r="AM5" s="38">
@@ -2576,7 +2593,7 @@
         <v/>
       </c>
       <c r="AN5" s="36">
-        <f>IF(OR(AG5="",R5=0),"",MIN(IF(AS5="",9.9E+99,AS5),AK5/R5))</f>
+        <f>IF(OR(AG5="",R5=0),"",MIN(IF(AT5="",9.9E+99,AT5),AK5/R5))</f>
         <v/>
       </c>
       <c r="AO5" s="38">
@@ -2584,27 +2601,32 @@
         <v/>
       </c>
       <c r="AP5" s="40" t="n"/>
-      <c r="AQ5" s="41" t="n"/>
+      <c r="AQ5" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
       <c r="AR5" s="41" t="n"/>
-      <c r="AS5" s="42" t="n"/>
-      <c r="AT5" s="43">
+      <c r="AS5" s="41" t="n"/>
+      <c r="AT5" s="42" t="n"/>
+      <c r="AU5" s="43">
         <f>IF(((S5*pax_cap*load_thin*ROUND(K5*L5*revleg_thin,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_thin,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5))&lt;=0,"",VLOOKUP(B5,country_opex,7,FALSE)/((S5*pax_cap*load_thin*ROUND(K5*L5*revleg_thin,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_thin,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5)))</f>
         <v/>
       </c>
-      <c r="AU5" s="43">
+      <c r="AV5" s="43">
         <f>IF(((S5*pax_cap*load_mid*ROUND(K5*L5*revleg_mid,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_mid,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5))&lt;=0,"",VLOOKUP(B5,country_opex,7,FALSE)/((S5*pax_cap*load_mid*ROUND(K5*L5*revleg_mid,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_mid,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5)))</f>
         <v/>
       </c>
-      <c r="AV5" s="43">
+      <c r="AW5" s="43">
         <f>IF(((S5*pax_cap*load_full*ROUND(K5*L5*revleg_full,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_full,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5))&lt;=0,"",VLOOKUP(B5,country_opex,7,FALSE)/((S5*pax_cap*load_full*ROUND(K5*L5*revleg_full,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_full,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5)))</f>
         <v/>
       </c>
-      <c r="AW5" s="44" t="inlineStr">
+      <c r="AX5" s="44" t="inlineStr">
         <is>
           <t>immaldives.com Maldives transfer costs (May 2026): shared speedboat $100-490 RT pp (=$50-245 OW); shared seaplane $400-820 RT pp (=$200-410 OW). atolltransfer.com scheduled $30-195 OW. Navier premium per-seat anchored between local premium speedboat and the seaplane the resort otherwise charges (R-MALDIVES-1).</t>
         </is>
       </c>
-      <c r="AX5" s="44" t="inlineStr">
+      <c r="AY5" s="44" t="inlineStr">
         <is>
           <t>NULL — pure inter-resort island-hop; no grounded crossing pool (R2). Geometry only.</t>
         </is>
@@ -2762,7 +2784,7 @@
         <v/>
       </c>
       <c r="AL6" s="34">
-        <f>IF(OR(AG6="",R6=0),"",MIN(IF(AS6="",9.9E+99,AS6),FLOOR(AK6/R6,1)))</f>
+        <f>IF(OR(AG6="",R6=0),"",MIN(IF(AT6="",9.9E+99,AT6),FLOOR(AK6/R6,1)))</f>
         <v/>
       </c>
       <c r="AM6" s="38">
@@ -2770,7 +2792,7 @@
         <v/>
       </c>
       <c r="AN6" s="36">
-        <f>IF(OR(AG6="",R6=0),"",MIN(IF(AS6="",9.9E+99,AS6),AK6/R6))</f>
+        <f>IF(OR(AG6="",R6=0),"",MIN(IF(AT6="",9.9E+99,AT6),AK6/R6))</f>
         <v/>
       </c>
       <c r="AO6" s="38">
@@ -2778,29 +2800,34 @@
         <v/>
       </c>
       <c r="AP6" s="40" t="n"/>
-      <c r="AQ6" s="41" t="n"/>
+      <c r="AQ6" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR6" s="41" t="n"/>
-      <c r="AS6" s="42" t="n">
+      <c r="AS6" s="41" t="n"/>
+      <c r="AT6" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="AT6" s="43">
+      <c r="AU6" s="43">
         <f>IF(((S6*pax_cap*load_thin*ROUND(K6*L6*revleg_thin,0))-(((battery/range_nm)*D6*ROUND(K6*L6*revleg_thin,0)*VLOOKUP(B6,country_opex,3,FALSE))+V6+W6+X6+Y6+Z6))&lt;=0,"",VLOOKUP(B6,country_opex,7,FALSE)/((S6*pax_cap*load_thin*ROUND(K6*L6*revleg_thin,0))-(((battery/range_nm)*D6*ROUND(K6*L6*revleg_thin,0)*VLOOKUP(B6,country_opex,3,FALSE))+V6+W6+X6+Y6+Z6)))</f>
         <v/>
       </c>
-      <c r="AU6" s="43">
+      <c r="AV6" s="43">
         <f>IF(((S6*pax_cap*load_mid*ROUND(K6*L6*revleg_mid,0))-(((battery/range_nm)*D6*ROUND(K6*L6*revleg_mid,0)*VLOOKUP(B6,country_opex,3,FALSE))+V6+W6+X6+Y6+Z6))&lt;=0,"",VLOOKUP(B6,country_opex,7,FALSE)/((S6*pax_cap*load_mid*ROUND(K6*L6*revleg_mid,0))-(((battery/range_nm)*D6*ROUND(K6*L6*revleg_mid,0)*VLOOKUP(B6,country_opex,3,FALSE))+V6+W6+X6+Y6+Z6)))</f>
         <v/>
       </c>
-      <c r="AV6" s="43">
+      <c r="AW6" s="43">
         <f>IF(((S6*pax_cap*load_full*ROUND(K6*L6*revleg_full,0))-(((battery/range_nm)*D6*ROUND(K6*L6*revleg_full,0)*VLOOKUP(B6,country_opex,3,FALSE))+V6+W6+X6+Y6+Z6))&lt;=0,"",VLOOKUP(B6,country_opex,7,FALSE)/((S6*pax_cap*load_full*ROUND(K6*L6*revleg_full,0))-(((battery/range_nm)*D6*ROUND(K6*L6*revleg_full,0)*VLOOKUP(B6,country_opex,3,FALSE))+V6+W6+X6+Y6+Z6)))</f>
         <v/>
       </c>
-      <c r="AW6" s="44" t="inlineStr">
+      <c r="AX6" s="44" t="inlineStr">
         <is>
           <t>immaldives.com Maldives transfer costs (May 2026): shared speedboat $100-490 RT pp (=$50-245 OW); shared seaplane $400-820 RT pp (=$200-410 OW). atolltransfer.com scheduled $30-195 OW. Navier premium per-seat anchored between local premium speedboat and the seaplane the resort otherwise charges (R-MALDIVES-1).</t>
         </is>
       </c>
-      <c r="AX6" s="44" t="inlineStr">
+      <c r="AY6" s="44" t="inlineStr">
         <is>
           <t>Modeled arrivals = published keys x occupancy 0.70 (Maldives Min. of Tourism avg) x (365/6.5 nights avg stay) x 1.9 pax/room. Inbound one-way transfers. T5-modeled/med; keys T1 resort-published. NULL for pure inter-resort excursion legs (R2).</t>
         </is>
@@ -2958,7 +2985,7 @@
         <v/>
       </c>
       <c r="AL7" s="34">
-        <f>IF(OR(AG7="",R7=0),"",MIN(IF(AS7="",9.9E+99,AS7),FLOOR(AK7/R7,1)))</f>
+        <f>IF(OR(AG7="",R7=0),"",MIN(IF(AT7="",9.9E+99,AT7),FLOOR(AK7/R7,1)))</f>
         <v/>
       </c>
       <c r="AM7" s="38">
@@ -2966,7 +2993,7 @@
         <v/>
       </c>
       <c r="AN7" s="36">
-        <f>IF(OR(AG7="",R7=0),"",MIN(IF(AS7="",9.9E+99,AS7),AK7/R7))</f>
+        <f>IF(OR(AG7="",R7=0),"",MIN(IF(AT7="",9.9E+99,AT7),AK7/R7))</f>
         <v/>
       </c>
       <c r="AO7" s="38">
@@ -2974,29 +3001,34 @@
         <v/>
       </c>
       <c r="AP7" s="40" t="n"/>
-      <c r="AQ7" s="41" t="n"/>
+      <c r="AQ7" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR7" s="41" t="n"/>
-      <c r="AS7" s="42" t="n">
+      <c r="AS7" s="41" t="n"/>
+      <c r="AT7" s="42" t="n">
         <v>19</v>
       </c>
-      <c r="AT7" s="43">
+      <c r="AU7" s="43">
         <f>IF(((S7*pax_cap*load_thin*ROUND(K7*L7*revleg_thin,0))-(((battery/range_nm)*D7*ROUND(K7*L7*revleg_thin,0)*VLOOKUP(B7,country_opex,3,FALSE))+V7+W7+X7+Y7+Z7))&lt;=0,"",VLOOKUP(B7,country_opex,7,FALSE)/((S7*pax_cap*load_thin*ROUND(K7*L7*revleg_thin,0))-(((battery/range_nm)*D7*ROUND(K7*L7*revleg_thin,0)*VLOOKUP(B7,country_opex,3,FALSE))+V7+W7+X7+Y7+Z7)))</f>
         <v/>
       </c>
-      <c r="AU7" s="43">
+      <c r="AV7" s="43">
         <f>IF(((S7*pax_cap*load_mid*ROUND(K7*L7*revleg_mid,0))-(((battery/range_nm)*D7*ROUND(K7*L7*revleg_mid,0)*VLOOKUP(B7,country_opex,3,FALSE))+V7+W7+X7+Y7+Z7))&lt;=0,"",VLOOKUP(B7,country_opex,7,FALSE)/((S7*pax_cap*load_mid*ROUND(K7*L7*revleg_mid,0))-(((battery/range_nm)*D7*ROUND(K7*L7*revleg_mid,0)*VLOOKUP(B7,country_opex,3,FALSE))+V7+W7+X7+Y7+Z7)))</f>
         <v/>
       </c>
-      <c r="AV7" s="43">
+      <c r="AW7" s="43">
         <f>IF(((S7*pax_cap*load_full*ROUND(K7*L7*revleg_full,0))-(((battery/range_nm)*D7*ROUND(K7*L7*revleg_full,0)*VLOOKUP(B7,country_opex,3,FALSE))+V7+W7+X7+Y7+Z7))&lt;=0,"",VLOOKUP(B7,country_opex,7,FALSE)/((S7*pax_cap*load_full*ROUND(K7*L7*revleg_full,0))-(((battery/range_nm)*D7*ROUND(K7*L7*revleg_full,0)*VLOOKUP(B7,country_opex,3,FALSE))+V7+W7+X7+Y7+Z7)))</f>
         <v/>
       </c>
-      <c r="AW7" s="44" t="inlineStr">
+      <c r="AX7" s="44" t="inlineStr">
         <is>
           <t>immaldives.com Maldives transfer costs (May 2026): shared speedboat $100-490 RT pp (=$50-245 OW); shared seaplane $400-820 RT pp (=$200-410 OW). atolltransfer.com scheduled $30-195 OW. Navier premium per-seat anchored between local premium speedboat and the seaplane the resort otherwise charges (R-MALDIVES-1).</t>
         </is>
       </c>
-      <c r="AX7" s="44" t="inlineStr">
+      <c r="AY7" s="44" t="inlineStr">
         <is>
           <t>Modeled arrivals = published keys x occupancy 0.70 (Maldives Min. of Tourism avg) x (365/6.5 nights avg stay) x 1.9 pax/room. Inbound one-way transfers. T5-modeled/med; keys T1 resort-published. NULL for pure inter-resort excursion legs (R2).</t>
         </is>
@@ -3154,7 +3186,7 @@
         <v/>
       </c>
       <c r="AL8" s="34">
-        <f>IF(OR(AG8="",R8=0),"",MIN(IF(AS8="",9.9E+99,AS8),FLOOR(AK8/R8,1)))</f>
+        <f>IF(OR(AG8="",R8=0),"",MIN(IF(AT8="",9.9E+99,AT8),FLOOR(AK8/R8,1)))</f>
         <v/>
       </c>
       <c r="AM8" s="38">
@@ -3162,7 +3194,7 @@
         <v/>
       </c>
       <c r="AN8" s="36">
-        <f>IF(OR(AG8="",R8=0),"",MIN(IF(AS8="",9.9E+99,AS8),AK8/R8))</f>
+        <f>IF(OR(AG8="",R8=0),"",MIN(IF(AT8="",9.9E+99,AT8),AK8/R8))</f>
         <v/>
       </c>
       <c r="AO8" s="38">
@@ -3170,29 +3202,34 @@
         <v/>
       </c>
       <c r="AP8" s="40" t="n"/>
-      <c r="AQ8" s="41" t="n"/>
+      <c r="AQ8" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR8" s="41" t="n"/>
-      <c r="AS8" s="42" t="n">
+      <c r="AS8" s="41" t="n"/>
+      <c r="AT8" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="AT8" s="43">
+      <c r="AU8" s="43">
         <f>IF(((S8*pax_cap*load_thin*ROUND(K8*L8*revleg_thin,0))-(((battery/range_nm)*D8*ROUND(K8*L8*revleg_thin,0)*VLOOKUP(B8,country_opex,3,FALSE))+V8+W8+X8+Y8+Z8))&lt;=0,"",VLOOKUP(B8,country_opex,7,FALSE)/((S8*pax_cap*load_thin*ROUND(K8*L8*revleg_thin,0))-(((battery/range_nm)*D8*ROUND(K8*L8*revleg_thin,0)*VLOOKUP(B8,country_opex,3,FALSE))+V8+W8+X8+Y8+Z8)))</f>
         <v/>
       </c>
-      <c r="AU8" s="43">
+      <c r="AV8" s="43">
         <f>IF(((S8*pax_cap*load_mid*ROUND(K8*L8*revleg_mid,0))-(((battery/range_nm)*D8*ROUND(K8*L8*revleg_mid,0)*VLOOKUP(B8,country_opex,3,FALSE))+V8+W8+X8+Y8+Z8))&lt;=0,"",VLOOKUP(B8,country_opex,7,FALSE)/((S8*pax_cap*load_mid*ROUND(K8*L8*revleg_mid,0))-(((battery/range_nm)*D8*ROUND(K8*L8*revleg_mid,0)*VLOOKUP(B8,country_opex,3,FALSE))+V8+W8+X8+Y8+Z8)))</f>
         <v/>
       </c>
-      <c r="AV8" s="43">
+      <c r="AW8" s="43">
         <f>IF(((S8*pax_cap*load_full*ROUND(K8*L8*revleg_full,0))-(((battery/range_nm)*D8*ROUND(K8*L8*revleg_full,0)*VLOOKUP(B8,country_opex,3,FALSE))+V8+W8+X8+Y8+Z8))&lt;=0,"",VLOOKUP(B8,country_opex,7,FALSE)/((S8*pax_cap*load_full*ROUND(K8*L8*revleg_full,0))-(((battery/range_nm)*D8*ROUND(K8*L8*revleg_full,0)*VLOOKUP(B8,country_opex,3,FALSE))+V8+W8+X8+Y8+Z8)))</f>
         <v/>
       </c>
-      <c r="AW8" s="44" t="inlineStr">
+      <c r="AX8" s="44" t="inlineStr">
         <is>
           <t>immaldives.com Maldives transfer costs (May 2026): shared speedboat $100-490 RT pp (=$50-245 OW); shared seaplane $400-820 RT pp (=$200-410 OW). atolltransfer.com scheduled $30-195 OW. Navier premium per-seat anchored between local premium speedboat and the seaplane the resort otherwise charges (R-MALDIVES-1).</t>
         </is>
       </c>
-      <c r="AX8" s="44" t="inlineStr">
+      <c r="AY8" s="44" t="inlineStr">
         <is>
           <t>Modeled arrivals = published keys x occupancy 0.70 (Maldives Min. of Tourism avg) x (365/6.5 nights avg stay) x 1.9 pax/room. Inbound one-way transfers. T5-modeled/med; keys T1 resort-published. NULL for pure inter-resort excursion legs (R2).</t>
         </is>
@@ -3350,7 +3387,7 @@
         <v/>
       </c>
       <c r="AL9" s="34">
-        <f>IF(OR(AG9="",R9=0),"",MIN(IF(AS9="",9.9E+99,AS9),FLOOR(AK9/R9,1)))</f>
+        <f>IF(OR(AG9="",R9=0),"",MIN(IF(AT9="",9.9E+99,AT9),FLOOR(AK9/R9,1)))</f>
         <v/>
       </c>
       <c r="AM9" s="38">
@@ -3358,7 +3395,7 @@
         <v/>
       </c>
       <c r="AN9" s="36">
-        <f>IF(OR(AG9="",R9=0),"",MIN(IF(AS9="",9.9E+99,AS9),AK9/R9))</f>
+        <f>IF(OR(AG9="",R9=0),"",MIN(IF(AT9="",9.9E+99,AT9),AK9/R9))</f>
         <v/>
       </c>
       <c r="AO9" s="38">
@@ -3366,29 +3403,34 @@
         <v/>
       </c>
       <c r="AP9" s="40" t="n"/>
-      <c r="AQ9" s="41" t="n"/>
+      <c r="AQ9" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR9" s="41" t="n"/>
-      <c r="AS9" s="42" t="n">
+      <c r="AS9" s="41" t="n"/>
+      <c r="AT9" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="AT9" s="43">
+      <c r="AU9" s="43">
         <f>IF(((S9*pax_cap*load_thin*ROUND(K9*L9*revleg_thin,0))-(((battery/range_nm)*D9*ROUND(K9*L9*revleg_thin,0)*VLOOKUP(B9,country_opex,3,FALSE))+V9+W9+X9+Y9+Z9))&lt;=0,"",VLOOKUP(B9,country_opex,7,FALSE)/((S9*pax_cap*load_thin*ROUND(K9*L9*revleg_thin,0))-(((battery/range_nm)*D9*ROUND(K9*L9*revleg_thin,0)*VLOOKUP(B9,country_opex,3,FALSE))+V9+W9+X9+Y9+Z9)))</f>
         <v/>
       </c>
-      <c r="AU9" s="43">
+      <c r="AV9" s="43">
         <f>IF(((S9*pax_cap*load_mid*ROUND(K9*L9*revleg_mid,0))-(((battery/range_nm)*D9*ROUND(K9*L9*revleg_mid,0)*VLOOKUP(B9,country_opex,3,FALSE))+V9+W9+X9+Y9+Z9))&lt;=0,"",VLOOKUP(B9,country_opex,7,FALSE)/((S9*pax_cap*load_mid*ROUND(K9*L9*revleg_mid,0))-(((battery/range_nm)*D9*ROUND(K9*L9*revleg_mid,0)*VLOOKUP(B9,country_opex,3,FALSE))+V9+W9+X9+Y9+Z9)))</f>
         <v/>
       </c>
-      <c r="AV9" s="43">
+      <c r="AW9" s="43">
         <f>IF(((S9*pax_cap*load_full*ROUND(K9*L9*revleg_full,0))-(((battery/range_nm)*D9*ROUND(K9*L9*revleg_full,0)*VLOOKUP(B9,country_opex,3,FALSE))+V9+W9+X9+Y9+Z9))&lt;=0,"",VLOOKUP(B9,country_opex,7,FALSE)/((S9*pax_cap*load_full*ROUND(K9*L9*revleg_full,0))-(((battery/range_nm)*D9*ROUND(K9*L9*revleg_full,0)*VLOOKUP(B9,country_opex,3,FALSE))+V9+W9+X9+Y9+Z9)))</f>
         <v/>
       </c>
-      <c r="AW9" s="44" t="inlineStr">
+      <c r="AX9" s="44" t="inlineStr">
         <is>
           <t>immaldives.com Maldives transfer costs (May 2026): shared speedboat $100-490 RT pp (=$50-245 OW); shared seaplane $400-820 RT pp (=$200-410 OW). atolltransfer.com scheduled $30-195 OW. Navier premium per-seat anchored between local premium speedboat and the seaplane the resort otherwise charges (R-MALDIVES-1).</t>
         </is>
       </c>
-      <c r="AX9" s="44" t="inlineStr">
+      <c r="AY9" s="44" t="inlineStr">
         <is>
           <t>Modeled arrivals = published keys x occupancy 0.70 (Maldives Min. of Tourism avg) x (365/6.5 nights avg stay) x 1.9 pax/room. Inbound one-way transfers. T5-modeled/med; keys T1 resort-published. NULL for pure inter-resort excursion legs (R2).</t>
         </is>
@@ -3546,7 +3588,7 @@
         <v/>
       </c>
       <c r="AL10" s="34">
-        <f>IF(OR(AG10="",R10=0),"",MIN(IF(AS10="",9.9E+99,AS10),FLOOR(AK10/R10,1)))</f>
+        <f>IF(OR(AG10="",R10=0),"",MIN(IF(AT10="",9.9E+99,AT10),FLOOR(AK10/R10,1)))</f>
         <v/>
       </c>
       <c r="AM10" s="38">
@@ -3554,7 +3596,7 @@
         <v/>
       </c>
       <c r="AN10" s="36">
-        <f>IF(OR(AG10="",R10=0),"",MIN(IF(AS10="",9.9E+99,AS10),AK10/R10))</f>
+        <f>IF(OR(AG10="",R10=0),"",MIN(IF(AT10="",9.9E+99,AT10),AK10/R10))</f>
         <v/>
       </c>
       <c r="AO10" s="38">
@@ -3562,29 +3604,34 @@
         <v/>
       </c>
       <c r="AP10" s="40" t="n"/>
-      <c r="AQ10" s="41" t="n"/>
+      <c r="AQ10" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR10" s="41" t="n"/>
-      <c r="AS10" s="42" t="n">
+      <c r="AS10" s="41" t="n"/>
+      <c r="AT10" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="AT10" s="43">
+      <c r="AU10" s="43">
         <f>IF(((S10*pax_cap*load_thin*ROUND(K10*L10*revleg_thin,0))-(((battery/range_nm)*D10*ROUND(K10*L10*revleg_thin,0)*VLOOKUP(B10,country_opex,3,FALSE))+V10+W10+X10+Y10+Z10))&lt;=0,"",VLOOKUP(B10,country_opex,7,FALSE)/((S10*pax_cap*load_thin*ROUND(K10*L10*revleg_thin,0))-(((battery/range_nm)*D10*ROUND(K10*L10*revleg_thin,0)*VLOOKUP(B10,country_opex,3,FALSE))+V10+W10+X10+Y10+Z10)))</f>
         <v/>
       </c>
-      <c r="AU10" s="43">
+      <c r="AV10" s="43">
         <f>IF(((S10*pax_cap*load_mid*ROUND(K10*L10*revleg_mid,0))-(((battery/range_nm)*D10*ROUND(K10*L10*revleg_mid,0)*VLOOKUP(B10,country_opex,3,FALSE))+V10+W10+X10+Y10+Z10))&lt;=0,"",VLOOKUP(B10,country_opex,7,FALSE)/((S10*pax_cap*load_mid*ROUND(K10*L10*revleg_mid,0))-(((battery/range_nm)*D10*ROUND(K10*L10*revleg_mid,0)*VLOOKUP(B10,country_opex,3,FALSE))+V10+W10+X10+Y10+Z10)))</f>
         <v/>
       </c>
-      <c r="AV10" s="43">
+      <c r="AW10" s="43">
         <f>IF(((S10*pax_cap*load_full*ROUND(K10*L10*revleg_full,0))-(((battery/range_nm)*D10*ROUND(K10*L10*revleg_full,0)*VLOOKUP(B10,country_opex,3,FALSE))+V10+W10+X10+Y10+Z10))&lt;=0,"",VLOOKUP(B10,country_opex,7,FALSE)/((S10*pax_cap*load_full*ROUND(K10*L10*revleg_full,0))-(((battery/range_nm)*D10*ROUND(K10*L10*revleg_full,0)*VLOOKUP(B10,country_opex,3,FALSE))+V10+W10+X10+Y10+Z10)))</f>
         <v/>
       </c>
-      <c r="AW10" s="44" t="inlineStr">
+      <c r="AX10" s="44" t="inlineStr">
         <is>
           <t>Mr &amp; Mrs Smith: Gili Lankanfushi shared return speedboat transfer US$302/person (excl tax) = $151/way. immaldives near-Male speedboat band $100-490 RT. Resort offers complimentary transfer on 4+ night book-direct stays (gili-lankanfushi.com) - underlying paid rate ~$150/way.</t>
         </is>
       </c>
-      <c r="AX10" s="44" t="inlineStr">
+      <c r="AY10" s="44" t="inlineStr">
         <is>
           <t>Modeled from resort key count. Gili Lankanfushi (North Malé): ~45 villas/keys (published resort/Virtuoso/booking figures). corridor_annual_oneway_pax = keys x 365 x occ(0.75) / avg_stay(7 nights) x guests/key(2) x 2 (arr+dep) ~= keys x 156. 45 keys -&gt; ~7,000 one-way pax/yr. Airport(MLE)&lt;-&gt;this resort is the sole transfer corridor (boat/seaplane only; no road/air alt - R3-EXCEPTION: arrivals = crossing ridership).</t>
         </is>
@@ -3736,7 +3783,7 @@
         <v/>
       </c>
       <c r="AL11" s="34">
-        <f>IF(OR(AG11="",R11=0),"",MIN(IF(AS11="",9.9E+99,AS11),FLOOR(AK11/R11,1)))</f>
+        <f>IF(OR(AG11="",R11=0),"",MIN(IF(AT11="",9.9E+99,AT11),FLOOR(AK11/R11,1)))</f>
         <v/>
       </c>
       <c r="AM11" s="38">
@@ -3744,7 +3791,7 @@
         <v/>
       </c>
       <c r="AN11" s="36">
-        <f>IF(OR(AG11="",R11=0),"",MIN(IF(AS11="",9.9E+99,AS11),AK11/R11))</f>
+        <f>IF(OR(AG11="",R11=0),"",MIN(IF(AT11="",9.9E+99,AT11),AK11/R11))</f>
         <v/>
       </c>
       <c r="AO11" s="38">
@@ -3752,27 +3799,32 @@
         <v/>
       </c>
       <c r="AP11" s="40" t="n"/>
-      <c r="AQ11" s="41" t="n"/>
+      <c r="AQ11" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
       <c r="AR11" s="41" t="n"/>
-      <c r="AS11" s="42" t="n"/>
-      <c r="AT11" s="43">
+      <c r="AS11" s="41" t="n"/>
+      <c r="AT11" s="42" t="n"/>
+      <c r="AU11" s="43">
         <f>IF(((S11*pax_cap*load_thin*ROUND(K11*L11*revleg_thin,0))-(((battery/range_nm)*D11*ROUND(K11*L11*revleg_thin,0)*VLOOKUP(B11,country_opex,3,FALSE))+V11+W11+X11+Y11+Z11))&lt;=0,"",VLOOKUP(B11,country_opex,7,FALSE)/((S11*pax_cap*load_thin*ROUND(K11*L11*revleg_thin,0))-(((battery/range_nm)*D11*ROUND(K11*L11*revleg_thin,0)*VLOOKUP(B11,country_opex,3,FALSE))+V11+W11+X11+Y11+Z11)))</f>
         <v/>
       </c>
-      <c r="AU11" s="43">
+      <c r="AV11" s="43">
         <f>IF(((S11*pax_cap*load_mid*ROUND(K11*L11*revleg_mid,0))-(((battery/range_nm)*D11*ROUND(K11*L11*revleg_mid,0)*VLOOKUP(B11,country_opex,3,FALSE))+V11+W11+X11+Y11+Z11))&lt;=0,"",VLOOKUP(B11,country_opex,7,FALSE)/((S11*pax_cap*load_mid*ROUND(K11*L11*revleg_mid,0))-(((battery/range_nm)*D11*ROUND(K11*L11*revleg_mid,0)*VLOOKUP(B11,country_opex,3,FALSE))+V11+W11+X11+Y11+Z11)))</f>
         <v/>
       </c>
-      <c r="AV11" s="43">
+      <c r="AW11" s="43">
         <f>IF(((S11*pax_cap*load_full*ROUND(K11*L11*revleg_full,0))-(((battery/range_nm)*D11*ROUND(K11*L11*revleg_full,0)*VLOOKUP(B11,country_opex,3,FALSE))+V11+W11+X11+Y11+Z11))&lt;=0,"",VLOOKUP(B11,country_opex,7,FALSE)/((S11*pax_cap*load_full*ROUND(K11*L11*revleg_full,0))-(((battery/range_nm)*D11*ROUND(K11*L11*revleg_full,0)*VLOOKUP(B11,country_opex,3,FALSE))+V11+W11+X11+Y11+Z11)))</f>
         <v/>
       </c>
-      <c r="AW11" s="44" t="inlineStr">
+      <c r="AX11" s="44" t="inlineStr">
         <is>
           <t>immaldives.com Maldives transfer costs (May 2026): shared speedboat $100-490 RT pp (=$50-245 OW); shared seaplane $400-820 RT pp (=$200-410 OW). atolltransfer.com scheduled $30-195 OW. Navier premium per-seat anchored between local premium speedboat and the seaplane the resort otherwise charges (R-MALDIVES-1).</t>
         </is>
       </c>
-      <c r="AX11" s="44" t="inlineStr">
+      <c r="AY11" s="44" t="inlineStr">
         <is>
           <t>NULL — pure inter-resort island-hop; no grounded crossing pool (R2). Geometry only.</t>
         </is>
@@ -3930,7 +3982,7 @@
         <v/>
       </c>
       <c r="AL12" s="34">
-        <f>IF(OR(AG12="",R12=0),"",MIN(IF(AS12="",9.9E+99,AS12),FLOOR(AK12/R12,1)))</f>
+        <f>IF(OR(AG12="",R12=0),"",MIN(IF(AT12="",9.9E+99,AT12),FLOOR(AK12/R12,1)))</f>
         <v/>
       </c>
       <c r="AM12" s="38">
@@ -3938,7 +3990,7 @@
         <v/>
       </c>
       <c r="AN12" s="36">
-        <f>IF(OR(AG12="",R12=0),"",MIN(IF(AS12="",9.9E+99,AS12),AK12/R12))</f>
+        <f>IF(OR(AG12="",R12=0),"",MIN(IF(AT12="",9.9E+99,AT12),AK12/R12))</f>
         <v/>
       </c>
       <c r="AO12" s="38">
@@ -3946,29 +3998,34 @@
         <v/>
       </c>
       <c r="AP12" s="40" t="n"/>
-      <c r="AQ12" s="41" t="n"/>
+      <c r="AQ12" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR12" s="41" t="n"/>
-      <c r="AS12" s="42" t="n">
+      <c r="AS12" s="41" t="n"/>
+      <c r="AT12" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="AT12" s="43">
+      <c r="AU12" s="43">
         <f>IF(((S12*pax_cap*load_thin*ROUND(K12*L12*revleg_thin,0))-(((battery/range_nm)*D12*ROUND(K12*L12*revleg_thin,0)*VLOOKUP(B12,country_opex,3,FALSE))+V12+W12+X12+Y12+Z12))&lt;=0,"",VLOOKUP(B12,country_opex,7,FALSE)/((S12*pax_cap*load_thin*ROUND(K12*L12*revleg_thin,0))-(((battery/range_nm)*D12*ROUND(K12*L12*revleg_thin,0)*VLOOKUP(B12,country_opex,3,FALSE))+V12+W12+X12+Y12+Z12)))</f>
         <v/>
       </c>
-      <c r="AU12" s="43">
+      <c r="AV12" s="43">
         <f>IF(((S12*pax_cap*load_mid*ROUND(K12*L12*revleg_mid,0))-(((battery/range_nm)*D12*ROUND(K12*L12*revleg_mid,0)*VLOOKUP(B12,country_opex,3,FALSE))+V12+W12+X12+Y12+Z12))&lt;=0,"",VLOOKUP(B12,country_opex,7,FALSE)/((S12*pax_cap*load_mid*ROUND(K12*L12*revleg_mid,0))-(((battery/range_nm)*D12*ROUND(K12*L12*revleg_mid,0)*VLOOKUP(B12,country_opex,3,FALSE))+V12+W12+X12+Y12+Z12)))</f>
         <v/>
       </c>
-      <c r="AV12" s="43">
+      <c r="AW12" s="43">
         <f>IF(((S12*pax_cap*load_full*ROUND(K12*L12*revleg_full,0))-(((battery/range_nm)*D12*ROUND(K12*L12*revleg_full,0)*VLOOKUP(B12,country_opex,3,FALSE))+V12+W12+X12+Y12+Z12))&lt;=0,"",VLOOKUP(B12,country_opex,7,FALSE)/((S12*pax_cap*load_full*ROUND(K12*L12*revleg_full,0))-(((battery/range_nm)*D12*ROUND(K12*L12*revleg_full,0)*VLOOKUP(B12,country_opex,3,FALSE))+V12+W12+X12+Y12+Z12)))</f>
         <v/>
       </c>
-      <c r="AW12" s="44" t="inlineStr">
+      <c r="AX12" s="44" t="inlineStr">
         <is>
           <t>immaldives.com Maldives transfer costs (May 2026): shared speedboat $100-490 RT pp (=$50-245 OW); shared seaplane $400-820 RT pp (=$200-410 OW). atolltransfer.com scheduled $30-195 OW. Navier premium per-seat anchored between local premium speedboat and the seaplane the resort otherwise charges (R-MALDIVES-1).</t>
         </is>
       </c>
-      <c r="AX12" s="44" t="inlineStr">
+      <c r="AY12" s="44" t="inlineStr">
         <is>
           <t>Modeled arrivals = published keys x occupancy 0.70 (Maldives Min. of Tourism avg) x (365/6.5 nights avg stay) x 1.9 pax/room. Inbound one-way transfers. T5-modeled/med; keys T1 resort-published. NULL for pure inter-resort excursion legs (R2).</t>
         </is>
@@ -4126,7 +4183,7 @@
         <v/>
       </c>
       <c r="AL13" s="34">
-        <f>IF(OR(AG13="",R13=0),"",MIN(IF(AS13="",9.9E+99,AS13),FLOOR(AK13/R13,1)))</f>
+        <f>IF(OR(AG13="",R13=0),"",MIN(IF(AT13="",9.9E+99,AT13),FLOOR(AK13/R13,1)))</f>
         <v/>
       </c>
       <c r="AM13" s="38">
@@ -4134,7 +4191,7 @@
         <v/>
       </c>
       <c r="AN13" s="36">
-        <f>IF(OR(AG13="",R13=0),"",MIN(IF(AS13="",9.9E+99,AS13),AK13/R13))</f>
+        <f>IF(OR(AG13="",R13=0),"",MIN(IF(AT13="",9.9E+99,AT13),AK13/R13))</f>
         <v/>
       </c>
       <c r="AO13" s="38">
@@ -4142,29 +4199,34 @@
         <v/>
       </c>
       <c r="AP13" s="40" t="n"/>
-      <c r="AQ13" s="41" t="n"/>
+      <c r="AQ13" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR13" s="41" t="n"/>
-      <c r="AS13" s="42" t="n">
+      <c r="AS13" s="41" t="n"/>
+      <c r="AT13" s="42" t="n">
         <v>5</v>
       </c>
-      <c r="AT13" s="43">
+      <c r="AU13" s="43">
         <f>IF(((S13*pax_cap*load_thin*ROUND(K13*L13*revleg_thin,0))-(((battery/range_nm)*D13*ROUND(K13*L13*revleg_thin,0)*VLOOKUP(B13,country_opex,3,FALSE))+V13+W13+X13+Y13+Z13))&lt;=0,"",VLOOKUP(B13,country_opex,7,FALSE)/((S13*pax_cap*load_thin*ROUND(K13*L13*revleg_thin,0))-(((battery/range_nm)*D13*ROUND(K13*L13*revleg_thin,0)*VLOOKUP(B13,country_opex,3,FALSE))+V13+W13+X13+Y13+Z13)))</f>
         <v/>
       </c>
-      <c r="AU13" s="43">
+      <c r="AV13" s="43">
         <f>IF(((S13*pax_cap*load_mid*ROUND(K13*L13*revleg_mid,0))-(((battery/range_nm)*D13*ROUND(K13*L13*revleg_mid,0)*VLOOKUP(B13,country_opex,3,FALSE))+V13+W13+X13+Y13+Z13))&lt;=0,"",VLOOKUP(B13,country_opex,7,FALSE)/((S13*pax_cap*load_mid*ROUND(K13*L13*revleg_mid,0))-(((battery/range_nm)*D13*ROUND(K13*L13*revleg_mid,0)*VLOOKUP(B13,country_opex,3,FALSE))+V13+W13+X13+Y13+Z13)))</f>
         <v/>
       </c>
-      <c r="AV13" s="43">
+      <c r="AW13" s="43">
         <f>IF(((S13*pax_cap*load_full*ROUND(K13*L13*revleg_full,0))-(((battery/range_nm)*D13*ROUND(K13*L13*revleg_full,0)*VLOOKUP(B13,country_opex,3,FALSE))+V13+W13+X13+Y13+Z13))&lt;=0,"",VLOOKUP(B13,country_opex,7,FALSE)/((S13*pax_cap*load_full*ROUND(K13*L13*revleg_full,0))-(((battery/range_nm)*D13*ROUND(K13*L13*revleg_full,0)*VLOOKUP(B13,country_opex,3,FALSE))+V13+W13+X13+Y13+Z13)))</f>
         <v/>
       </c>
-      <c r="AW13" s="44" t="inlineStr">
+      <c r="AX13" s="44" t="inlineStr">
         <is>
           <t>immaldives.com Maldives transfer costs (May 2026): shared speedboat $100-490 RT pp (=$50-245 OW); shared seaplane $400-820 RT pp (=$200-410 OW). atolltransfer.com scheduled $30-195 OW. Navier premium per-seat anchored between local premium speedboat and the seaplane the resort otherwise charges (R-MALDIVES-1).</t>
         </is>
       </c>
-      <c r="AX13" s="44" t="inlineStr">
+      <c r="AY13" s="44" t="inlineStr">
         <is>
           <t>Modeled arrivals = published keys x occupancy 0.70 (Maldives Min. of Tourism avg) x (365/6.5 nights avg stay) x 1.9 pax/room. Inbound one-way transfers. T5-modeled/med; keys T1 resort-published. NULL for pure inter-resort excursion legs (R2).</t>
         </is>
@@ -4322,7 +4384,7 @@
         <v/>
       </c>
       <c r="AL14" s="34">
-        <f>IF(OR(AG14="",R14=0),"",MIN(IF(AS14="",9.9E+99,AS14),FLOOR(AK14/R14,1)))</f>
+        <f>IF(OR(AG14="",R14=0),"",MIN(IF(AT14="",9.9E+99,AT14),FLOOR(AK14/R14,1)))</f>
         <v/>
       </c>
       <c r="AM14" s="38">
@@ -4330,7 +4392,7 @@
         <v/>
       </c>
       <c r="AN14" s="36">
-        <f>IF(OR(AG14="",R14=0),"",MIN(IF(AS14="",9.9E+99,AS14),AK14/R14))</f>
+        <f>IF(OR(AG14="",R14=0),"",MIN(IF(AT14="",9.9E+99,AT14),AK14/R14))</f>
         <v/>
       </c>
       <c r="AO14" s="38">
@@ -4338,29 +4400,34 @@
         <v/>
       </c>
       <c r="AP14" s="40" t="n"/>
-      <c r="AQ14" s="41" t="n"/>
+      <c r="AQ14" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR14" s="41" t="n"/>
-      <c r="AS14" s="42" t="n">
+      <c r="AS14" s="41" t="n"/>
+      <c r="AT14" s="42" t="n">
         <v>4</v>
       </c>
-      <c r="AT14" s="43">
+      <c r="AU14" s="43">
         <f>IF(((S14*pax_cap*load_thin*ROUND(K14*L14*revleg_thin,0))-(((battery/range_nm)*D14*ROUND(K14*L14*revleg_thin,0)*VLOOKUP(B14,country_opex,3,FALSE))+V14+W14+X14+Y14+Z14))&lt;=0,"",VLOOKUP(B14,country_opex,7,FALSE)/((S14*pax_cap*load_thin*ROUND(K14*L14*revleg_thin,0))-(((battery/range_nm)*D14*ROUND(K14*L14*revleg_thin,0)*VLOOKUP(B14,country_opex,3,FALSE))+V14+W14+X14+Y14+Z14)))</f>
         <v/>
       </c>
-      <c r="AU14" s="43">
+      <c r="AV14" s="43">
         <f>IF(((S14*pax_cap*load_mid*ROUND(K14*L14*revleg_mid,0))-(((battery/range_nm)*D14*ROUND(K14*L14*revleg_mid,0)*VLOOKUP(B14,country_opex,3,FALSE))+V14+W14+X14+Y14+Z14))&lt;=0,"",VLOOKUP(B14,country_opex,7,FALSE)/((S14*pax_cap*load_mid*ROUND(K14*L14*revleg_mid,0))-(((battery/range_nm)*D14*ROUND(K14*L14*revleg_mid,0)*VLOOKUP(B14,country_opex,3,FALSE))+V14+W14+X14+Y14+Z14)))</f>
         <v/>
       </c>
-      <c r="AV14" s="43">
+      <c r="AW14" s="43">
         <f>IF(((S14*pax_cap*load_full*ROUND(K14*L14*revleg_full,0))-(((battery/range_nm)*D14*ROUND(K14*L14*revleg_full,0)*VLOOKUP(B14,country_opex,3,FALSE))+V14+W14+X14+Y14+Z14))&lt;=0,"",VLOOKUP(B14,country_opex,7,FALSE)/((S14*pax_cap*load_full*ROUND(K14*L14*revleg_full,0))-(((battery/range_nm)*D14*ROUND(K14*L14*revleg_full,0)*VLOOKUP(B14,country_opex,3,FALSE))+V14+W14+X14+Y14+Z14)))</f>
         <v/>
       </c>
-      <c r="AW14" s="44" t="inlineStr">
+      <c r="AX14" s="44" t="inlineStr">
         <is>
           <t>immaldives.com Maldives transfer costs (May 2026): shared speedboat $100-490 RT pp (=$50-245 OW); shared seaplane $400-820 RT pp (=$200-410 OW). atolltransfer.com scheduled $30-195 OW. Navier premium per-seat anchored between local premium speedboat and the seaplane the resort otherwise charges (R-MALDIVES-1).</t>
         </is>
       </c>
-      <c r="AX14" s="44" t="inlineStr">
+      <c r="AY14" s="44" t="inlineStr">
         <is>
           <t>Modeled arrivals = published keys x occupancy 0.70 (Maldives Min. of Tourism avg) x (365/6.5 nights avg stay) x 1.9 pax/room. Inbound one-way transfers. T5-modeled/med; keys T1 resort-published. NULL for pure inter-resort excursion legs (R2).</t>
         </is>
@@ -4518,7 +4585,7 @@
         <v/>
       </c>
       <c r="AL15" s="34">
-        <f>IF(OR(AG15="",R15=0),"",MIN(IF(AS15="",9.9E+99,AS15),FLOOR(AK15/R15,1)))</f>
+        <f>IF(OR(AG15="",R15=0),"",MIN(IF(AT15="",9.9E+99,AT15),FLOOR(AK15/R15,1)))</f>
         <v/>
       </c>
       <c r="AM15" s="38">
@@ -4526,7 +4593,7 @@
         <v/>
       </c>
       <c r="AN15" s="36">
-        <f>IF(OR(AG15="",R15=0),"",MIN(IF(AS15="",9.9E+99,AS15),AK15/R15))</f>
+        <f>IF(OR(AG15="",R15=0),"",MIN(IF(AT15="",9.9E+99,AT15),AK15/R15))</f>
         <v/>
       </c>
       <c r="AO15" s="38">
@@ -4534,29 +4601,34 @@
         <v/>
       </c>
       <c r="AP15" s="40" t="n"/>
-      <c r="AQ15" s="41" t="n"/>
+      <c r="AQ15" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR15" s="41" t="n"/>
-      <c r="AS15" s="42" t="n">
+      <c r="AS15" s="41" t="n"/>
+      <c r="AT15" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="AT15" s="43">
+      <c r="AU15" s="43">
         <f>IF(((S15*pax_cap*load_thin*ROUND(K15*L15*revleg_thin,0))-(((battery/range_nm)*D15*ROUND(K15*L15*revleg_thin,0)*VLOOKUP(B15,country_opex,3,FALSE))+V15+W15+X15+Y15+Z15))&lt;=0,"",VLOOKUP(B15,country_opex,7,FALSE)/((S15*pax_cap*load_thin*ROUND(K15*L15*revleg_thin,0))-(((battery/range_nm)*D15*ROUND(K15*L15*revleg_thin,0)*VLOOKUP(B15,country_opex,3,FALSE))+V15+W15+X15+Y15+Z15)))</f>
         <v/>
       </c>
-      <c r="AU15" s="43">
+      <c r="AV15" s="43">
         <f>IF(((S15*pax_cap*load_mid*ROUND(K15*L15*revleg_mid,0))-(((battery/range_nm)*D15*ROUND(K15*L15*revleg_mid,0)*VLOOKUP(B15,country_opex,3,FALSE))+V15+W15+X15+Y15+Z15))&lt;=0,"",VLOOKUP(B15,country_opex,7,FALSE)/((S15*pax_cap*load_mid*ROUND(K15*L15*revleg_mid,0))-(((battery/range_nm)*D15*ROUND(K15*L15*revleg_mid,0)*VLOOKUP(B15,country_opex,3,FALSE))+V15+W15+X15+Y15+Z15)))</f>
         <v/>
       </c>
-      <c r="AV15" s="43">
+      <c r="AW15" s="43">
         <f>IF(((S15*pax_cap*load_full*ROUND(K15*L15*revleg_full,0))-(((battery/range_nm)*D15*ROUND(K15*L15*revleg_full,0)*VLOOKUP(B15,country_opex,3,FALSE))+V15+W15+X15+Y15+Z15))&lt;=0,"",VLOOKUP(B15,country_opex,7,FALSE)/((S15*pax_cap*load_full*ROUND(K15*L15*revleg_full,0))-(((battery/range_nm)*D15*ROUND(K15*L15*revleg_full,0)*VLOOKUP(B15,country_opex,3,FALSE))+V15+W15+X15+Y15+Z15)))</f>
         <v/>
       </c>
-      <c r="AW15" s="44" t="inlineStr">
+      <c r="AX15" s="44" t="inlineStr">
         <is>
           <t>tourbonjour live booking: Baros boat transfer per adult USD 232 round-trip = $116/way. immaldives.com 2026 table: Baros shared speedboat $180-260 RT = $90-130/way. baros.com publishes private rates on request. Premium per-seat ~$120/way.</t>
         </is>
       </c>
-      <c r="AX15" s="44" t="inlineStr">
+      <c r="AY15" s="44" t="inlineStr">
         <is>
           <t>Modeled from resort key count. Baros Maldives (North Malé): ~75 villas/keys (published resort/Virtuoso/booking figures). corridor_annual_oneway_pax = keys x 365 x occ(0.75) / avg_stay(7 nights) x guests/key(2) x 2 (arr+dep) ~= keys x 156. 75 keys -&gt; ~11,700 one-way pax/yr. Airport(MLE)&lt;-&gt;this resort is the sole transfer corridor (boat/seaplane only; no road/air alt - R3-EXCEPTION: arrivals = crossing ridership).</t>
         </is>
@@ -4714,7 +4786,7 @@
         <v/>
       </c>
       <c r="AL16" s="34">
-        <f>IF(OR(AG16="",R16=0),"",MIN(IF(AS16="",9.9E+99,AS16),FLOOR(AK16/R16,1)))</f>
+        <f>IF(OR(AG16="",R16=0),"",MIN(IF(AT16="",9.9E+99,AT16),FLOOR(AK16/R16,1)))</f>
         <v/>
       </c>
       <c r="AM16" s="38">
@@ -4722,7 +4794,7 @@
         <v/>
       </c>
       <c r="AN16" s="36">
-        <f>IF(OR(AG16="",R16=0),"",MIN(IF(AS16="",9.9E+99,AS16),AK16/R16))</f>
+        <f>IF(OR(AG16="",R16=0),"",MIN(IF(AT16="",9.9E+99,AT16),AK16/R16))</f>
         <v/>
       </c>
       <c r="AO16" s="38">
@@ -4730,29 +4802,34 @@
         <v/>
       </c>
       <c r="AP16" s="40" t="n"/>
-      <c r="AQ16" s="41" t="n"/>
+      <c r="AQ16" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR16" s="41" t="n"/>
-      <c r="AS16" s="42" t="n">
+      <c r="AS16" s="41" t="n"/>
+      <c r="AT16" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="AT16" s="43">
+      <c r="AU16" s="43">
         <f>IF(((S16*pax_cap*load_thin*ROUND(K16*L16*revleg_thin,0))-(((battery/range_nm)*D16*ROUND(K16*L16*revleg_thin,0)*VLOOKUP(B16,country_opex,3,FALSE))+V16+W16+X16+Y16+Z16))&lt;=0,"",VLOOKUP(B16,country_opex,7,FALSE)/((S16*pax_cap*load_thin*ROUND(K16*L16*revleg_thin,0))-(((battery/range_nm)*D16*ROUND(K16*L16*revleg_thin,0)*VLOOKUP(B16,country_opex,3,FALSE))+V16+W16+X16+Y16+Z16)))</f>
         <v/>
       </c>
-      <c r="AU16" s="43">
+      <c r="AV16" s="43">
         <f>IF(((S16*pax_cap*load_mid*ROUND(K16*L16*revleg_mid,0))-(((battery/range_nm)*D16*ROUND(K16*L16*revleg_mid,0)*VLOOKUP(B16,country_opex,3,FALSE))+V16+W16+X16+Y16+Z16))&lt;=0,"",VLOOKUP(B16,country_opex,7,FALSE)/((S16*pax_cap*load_mid*ROUND(K16*L16*revleg_mid,0))-(((battery/range_nm)*D16*ROUND(K16*L16*revleg_mid,0)*VLOOKUP(B16,country_opex,3,FALSE))+V16+W16+X16+Y16+Z16)))</f>
         <v/>
       </c>
-      <c r="AV16" s="43">
+      <c r="AW16" s="43">
         <f>IF(((S16*pax_cap*load_full*ROUND(K16*L16*revleg_full,0))-(((battery/range_nm)*D16*ROUND(K16*L16*revleg_full,0)*VLOOKUP(B16,country_opex,3,FALSE))+V16+W16+X16+Y16+Z16))&lt;=0,"",VLOOKUP(B16,country_opex,7,FALSE)/((S16*pax_cap*load_full*ROUND(K16*L16*revleg_full,0))-(((battery/range_nm)*D16*ROUND(K16*L16*revleg_full,0)*VLOOKUP(B16,country_opex,3,FALSE))+V16+W16+X16+Y16+Z16)))</f>
         <v/>
       </c>
-      <c r="AW16" s="44" t="inlineStr">
+      <c r="AX16" s="44" t="inlineStr">
         <is>
           <t>immaldives.com Maldives transfer costs (May 2026): shared speedboat $100-490 RT pp (=$50-245 OW); shared seaplane $400-820 RT pp (=$200-410 OW). atolltransfer.com scheduled $30-195 OW. Navier premium per-seat anchored between local premium speedboat and the seaplane the resort otherwise charges (R-MALDIVES-1).</t>
         </is>
       </c>
-      <c r="AX16" s="44" t="inlineStr">
+      <c r="AY16" s="44" t="inlineStr">
         <is>
           <t>Modeled arrivals = published keys x occupancy 0.70 (Maldives Min. of Tourism avg) x (365/6.5 nights avg stay) x 1.9 pax/room. Inbound one-way transfers. T5-modeled/med; keys T1 resort-published. NULL for pure inter-resort excursion legs (R2).</t>
         </is>
@@ -4910,7 +4987,7 @@
         <v/>
       </c>
       <c r="AL17" s="34">
-        <f>IF(OR(AG17="",R17=0),"",MIN(IF(AS17="",9.9E+99,AS17),FLOOR(AK17/R17,1)))</f>
+        <f>IF(OR(AG17="",R17=0),"",MIN(IF(AT17="",9.9E+99,AT17),FLOOR(AK17/R17,1)))</f>
         <v/>
       </c>
       <c r="AM17" s="38">
@@ -4918,7 +4995,7 @@
         <v/>
       </c>
       <c r="AN17" s="36">
-        <f>IF(OR(AG17="",R17=0),"",MIN(IF(AS17="",9.9E+99,AS17),AK17/R17))</f>
+        <f>IF(OR(AG17="",R17=0),"",MIN(IF(AT17="",9.9E+99,AT17),AK17/R17))</f>
         <v/>
       </c>
       <c r="AO17" s="38">
@@ -4926,29 +5003,34 @@
         <v/>
       </c>
       <c r="AP17" s="40" t="n"/>
-      <c r="AQ17" s="41" t="n"/>
+      <c r="AQ17" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR17" s="41" t="n"/>
-      <c r="AS17" s="42" t="n">
+      <c r="AS17" s="41" t="n"/>
+      <c r="AT17" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="AT17" s="43">
+      <c r="AU17" s="43">
         <f>IF(((S17*pax_cap*load_thin*ROUND(K17*L17*revleg_thin,0))-(((battery/range_nm)*D17*ROUND(K17*L17*revleg_thin,0)*VLOOKUP(B17,country_opex,3,FALSE))+V17+W17+X17+Y17+Z17))&lt;=0,"",VLOOKUP(B17,country_opex,7,FALSE)/((S17*pax_cap*load_thin*ROUND(K17*L17*revleg_thin,0))-(((battery/range_nm)*D17*ROUND(K17*L17*revleg_thin,0)*VLOOKUP(B17,country_opex,3,FALSE))+V17+W17+X17+Y17+Z17)))</f>
         <v/>
       </c>
-      <c r="AU17" s="43">
+      <c r="AV17" s="43">
         <f>IF(((S17*pax_cap*load_mid*ROUND(K17*L17*revleg_mid,0))-(((battery/range_nm)*D17*ROUND(K17*L17*revleg_mid,0)*VLOOKUP(B17,country_opex,3,FALSE))+V17+W17+X17+Y17+Z17))&lt;=0,"",VLOOKUP(B17,country_opex,7,FALSE)/((S17*pax_cap*load_mid*ROUND(K17*L17*revleg_mid,0))-(((battery/range_nm)*D17*ROUND(K17*L17*revleg_mid,0)*VLOOKUP(B17,country_opex,3,FALSE))+V17+W17+X17+Y17+Z17)))</f>
         <v/>
       </c>
-      <c r="AV17" s="43">
+      <c r="AW17" s="43">
         <f>IF(((S17*pax_cap*load_full*ROUND(K17*L17*revleg_full,0))-(((battery/range_nm)*D17*ROUND(K17*L17*revleg_full,0)*VLOOKUP(B17,country_opex,3,FALSE))+V17+W17+X17+Y17+Z17))&lt;=0,"",VLOOKUP(B17,country_opex,7,FALSE)/((S17*pax_cap*load_full*ROUND(K17*L17*revleg_full,0))-(((battery/range_nm)*D17*ROUND(K17*L17*revleg_full,0)*VLOOKUP(B17,country_opex,3,FALSE))+V17+W17+X17+Y17+Z17)))</f>
         <v/>
       </c>
-      <c r="AW17" s="44" t="inlineStr">
+      <c r="AX17" s="44" t="inlineStr">
         <is>
           <t>immaldives.com Maldives transfer costs (May 2026): shared speedboat $100-490 RT pp (=$50-245 OW); shared seaplane $400-820 RT pp (=$200-410 OW). atolltransfer.com scheduled $30-195 OW. Navier premium per-seat anchored between local premium speedboat and the seaplane the resort otherwise charges (R-MALDIVES-1).</t>
         </is>
       </c>
-      <c r="AX17" s="44" t="inlineStr">
+      <c r="AY17" s="44" t="inlineStr">
         <is>
           <t>Modeled arrivals = published keys x occupancy 0.70 (Maldives Min. of Tourism avg) x (365/6.5 nights avg stay) x 1.9 pax/room. Inbound one-way transfers. T5-modeled/med; keys T1 resort-published. NULL for pure inter-resort excursion legs (R2).</t>
         </is>
@@ -5106,7 +5188,7 @@
         <v/>
       </c>
       <c r="AL18" s="34">
-        <f>IF(OR(AG18="",R18=0),"",MIN(IF(AS18="",9.9E+99,AS18),FLOOR(AK18/R18,1)))</f>
+        <f>IF(OR(AG18="",R18=0),"",MIN(IF(AT18="",9.9E+99,AT18),FLOOR(AK18/R18,1)))</f>
         <v/>
       </c>
       <c r="AM18" s="38">
@@ -5114,7 +5196,7 @@
         <v/>
       </c>
       <c r="AN18" s="36">
-        <f>IF(OR(AG18="",R18=0),"",MIN(IF(AS18="",9.9E+99,AS18),AK18/R18))</f>
+        <f>IF(OR(AG18="",R18=0),"",MIN(IF(AT18="",9.9E+99,AT18),AK18/R18))</f>
         <v/>
       </c>
       <c r="AO18" s="38">
@@ -5122,29 +5204,34 @@
         <v/>
       </c>
       <c r="AP18" s="40" t="n"/>
-      <c r="AQ18" s="41" t="n"/>
+      <c r="AQ18" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR18" s="41" t="n"/>
-      <c r="AS18" s="42" t="n">
+      <c r="AS18" s="41" t="n"/>
+      <c r="AT18" s="42" t="n">
         <v>5</v>
       </c>
-      <c r="AT18" s="43">
+      <c r="AU18" s="43">
         <f>IF(((S18*pax_cap*load_thin*ROUND(K18*L18*revleg_thin,0))-(((battery/range_nm)*D18*ROUND(K18*L18*revleg_thin,0)*VLOOKUP(B18,country_opex,3,FALSE))+V18+W18+X18+Y18+Z18))&lt;=0,"",VLOOKUP(B18,country_opex,7,FALSE)/((S18*pax_cap*load_thin*ROUND(K18*L18*revleg_thin,0))-(((battery/range_nm)*D18*ROUND(K18*L18*revleg_thin,0)*VLOOKUP(B18,country_opex,3,FALSE))+V18+W18+X18+Y18+Z18)))</f>
         <v/>
       </c>
-      <c r="AU18" s="43">
+      <c r="AV18" s="43">
         <f>IF(((S18*pax_cap*load_mid*ROUND(K18*L18*revleg_mid,0))-(((battery/range_nm)*D18*ROUND(K18*L18*revleg_mid,0)*VLOOKUP(B18,country_opex,3,FALSE))+V18+W18+X18+Y18+Z18))&lt;=0,"",VLOOKUP(B18,country_opex,7,FALSE)/((S18*pax_cap*load_mid*ROUND(K18*L18*revleg_mid,0))-(((battery/range_nm)*D18*ROUND(K18*L18*revleg_mid,0)*VLOOKUP(B18,country_opex,3,FALSE))+V18+W18+X18+Y18+Z18)))</f>
         <v/>
       </c>
-      <c r="AV18" s="43">
+      <c r="AW18" s="43">
         <f>IF(((S18*pax_cap*load_full*ROUND(K18*L18*revleg_full,0))-(((battery/range_nm)*D18*ROUND(K18*L18*revleg_full,0)*VLOOKUP(B18,country_opex,3,FALSE))+V18+W18+X18+Y18+Z18))&lt;=0,"",VLOOKUP(B18,country_opex,7,FALSE)/((S18*pax_cap*load_full*ROUND(K18*L18*revleg_full,0))-(((battery/range_nm)*D18*ROUND(K18*L18*revleg_full,0)*VLOOKUP(B18,country_opex,3,FALSE))+V18+W18+X18+Y18+Z18)))</f>
         <v/>
       </c>
-      <c r="AW18" s="44" t="inlineStr">
+      <c r="AX18" s="44" t="inlineStr">
         <is>
           <t>immaldives.com Maldives transfer costs (May 2026): shared speedboat $100-490 RT pp (=$50-245 OW); shared seaplane $400-820 RT pp (=$200-410 OW). atolltransfer.com scheduled $30-195 OW. Navier premium per-seat anchored between local premium speedboat and the seaplane the resort otherwise charges (R-MALDIVES-1).</t>
         </is>
       </c>
-      <c r="AX18" s="44" t="inlineStr">
+      <c r="AY18" s="44" t="inlineStr">
         <is>
           <t>Modeled arrivals = published keys x occupancy 0.70 (Maldives Min. of Tourism avg) x (365/6.5 nights avg stay) x 1.9 pax/room. Inbound one-way transfers. T5-modeled/med; keys T1 resort-published. NULL for pure inter-resort excursion legs (R2).</t>
         </is>
@@ -5302,7 +5389,7 @@
         <v/>
       </c>
       <c r="AL19" s="34">
-        <f>IF(OR(AG19="",R19=0),"",MIN(IF(AS19="",9.9E+99,AS19),FLOOR(AK19/R19,1)))</f>
+        <f>IF(OR(AG19="",R19=0),"",MIN(IF(AT19="",9.9E+99,AT19),FLOOR(AK19/R19,1)))</f>
         <v/>
       </c>
       <c r="AM19" s="38">
@@ -5310,7 +5397,7 @@
         <v/>
       </c>
       <c r="AN19" s="36">
-        <f>IF(OR(AG19="",R19=0),"",MIN(IF(AS19="",9.9E+99,AS19),AK19/R19))</f>
+        <f>IF(OR(AG19="",R19=0),"",MIN(IF(AT19="",9.9E+99,AT19),AK19/R19))</f>
         <v/>
       </c>
       <c r="AO19" s="38">
@@ -5318,29 +5405,34 @@
         <v/>
       </c>
       <c r="AP19" s="40" t="n"/>
-      <c r="AQ19" s="41" t="n"/>
+      <c r="AQ19" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR19" s="41" t="n"/>
-      <c r="AS19" s="42" t="n">
+      <c r="AS19" s="41" t="n"/>
+      <c r="AT19" s="42" t="n">
         <v>20</v>
       </c>
-      <c r="AT19" s="43">
+      <c r="AU19" s="43">
         <f>IF(((S19*pax_cap*load_thin*ROUND(K19*L19*revleg_thin,0))-(((battery/range_nm)*D19*ROUND(K19*L19*revleg_thin,0)*VLOOKUP(B19,country_opex,3,FALSE))+V19+W19+X19+Y19+Z19))&lt;=0,"",VLOOKUP(B19,country_opex,7,FALSE)/((S19*pax_cap*load_thin*ROUND(K19*L19*revleg_thin,0))-(((battery/range_nm)*D19*ROUND(K19*L19*revleg_thin,0)*VLOOKUP(B19,country_opex,3,FALSE))+V19+W19+X19+Y19+Z19)))</f>
         <v/>
       </c>
-      <c r="AU19" s="43">
+      <c r="AV19" s="43">
         <f>IF(((S19*pax_cap*load_mid*ROUND(K19*L19*revleg_mid,0))-(((battery/range_nm)*D19*ROUND(K19*L19*revleg_mid,0)*VLOOKUP(B19,country_opex,3,FALSE))+V19+W19+X19+Y19+Z19))&lt;=0,"",VLOOKUP(B19,country_opex,7,FALSE)/((S19*pax_cap*load_mid*ROUND(K19*L19*revleg_mid,0))-(((battery/range_nm)*D19*ROUND(K19*L19*revleg_mid,0)*VLOOKUP(B19,country_opex,3,FALSE))+V19+W19+X19+Y19+Z19)))</f>
         <v/>
       </c>
-      <c r="AV19" s="43">
+      <c r="AW19" s="43">
         <f>IF(((S19*pax_cap*load_full*ROUND(K19*L19*revleg_full,0))-(((battery/range_nm)*D19*ROUND(K19*L19*revleg_full,0)*VLOOKUP(B19,country_opex,3,FALSE))+V19+W19+X19+Y19+Z19))&lt;=0,"",VLOOKUP(B19,country_opex,7,FALSE)/((S19*pax_cap*load_full*ROUND(K19*L19*revleg_full,0))-(((battery/range_nm)*D19*ROUND(K19*L19*revleg_full,0)*VLOOKUP(B19,country_opex,3,FALSE))+V19+W19+X19+Y19+Z19)))</f>
         <v/>
       </c>
-      <c r="AW19" s="44" t="inlineStr">
+      <c r="AX19" s="44" t="inlineStr">
         <is>
           <t>immaldives.com Maldives transfer costs (May 2026): shared speedboat $100-490 RT pp (=$50-245 OW); shared seaplane $400-820 RT pp (=$200-410 OW). atolltransfer.com scheduled $30-195 OW. Navier premium per-seat anchored between local premium speedboat and the seaplane the resort otherwise charges (R-MALDIVES-1).</t>
         </is>
       </c>
-      <c r="AX19" s="44" t="inlineStr">
+      <c r="AY19" s="44" t="inlineStr">
         <is>
           <t>Modeled arrivals = published keys x occupancy 0.70 (Maldives Min. of Tourism avg) x (365/6.5 nights avg stay) x 1.9 pax/room. Inbound one-way transfers. T5-modeled/med; keys T1 resort-published. NULL for pure inter-resort excursion legs (R2).</t>
         </is>
@@ -5492,7 +5584,7 @@
         <v/>
       </c>
       <c r="AL20" s="34">
-        <f>IF(OR(AG20="",R20=0),"",MIN(IF(AS20="",9.9E+99,AS20),FLOOR(AK20/R20,1)))</f>
+        <f>IF(OR(AG20="",R20=0),"",MIN(IF(AT20="",9.9E+99,AT20),FLOOR(AK20/R20,1)))</f>
         <v/>
       </c>
       <c r="AM20" s="38">
@@ -5500,7 +5592,7 @@
         <v/>
       </c>
       <c r="AN20" s="36">
-        <f>IF(OR(AG20="",R20=0),"",MIN(IF(AS20="",9.9E+99,AS20),AK20/R20))</f>
+        <f>IF(OR(AG20="",R20=0),"",MIN(IF(AT20="",9.9E+99,AT20),AK20/R20))</f>
         <v/>
       </c>
       <c r="AO20" s="38">
@@ -5508,27 +5600,32 @@
         <v/>
       </c>
       <c r="AP20" s="40" t="n"/>
-      <c r="AQ20" s="41" t="n"/>
+      <c r="AQ20" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
       <c r="AR20" s="41" t="n"/>
-      <c r="AS20" s="42" t="n"/>
-      <c r="AT20" s="43">
+      <c r="AS20" s="41" t="n"/>
+      <c r="AT20" s="42" t="n"/>
+      <c r="AU20" s="43">
         <f>IF(((S20*pax_cap*load_thin*ROUND(K20*L20*revleg_thin,0))-(((battery/range_nm)*D20*ROUND(K20*L20*revleg_thin,0)*VLOOKUP(B20,country_opex,3,FALSE))+V20+W20+X20+Y20+Z20))&lt;=0,"",VLOOKUP(B20,country_opex,7,FALSE)/((S20*pax_cap*load_thin*ROUND(K20*L20*revleg_thin,0))-(((battery/range_nm)*D20*ROUND(K20*L20*revleg_thin,0)*VLOOKUP(B20,country_opex,3,FALSE))+V20+W20+X20+Y20+Z20)))</f>
         <v/>
       </c>
-      <c r="AU20" s="43">
+      <c r="AV20" s="43">
         <f>IF(((S20*pax_cap*load_mid*ROUND(K20*L20*revleg_mid,0))-(((battery/range_nm)*D20*ROUND(K20*L20*revleg_mid,0)*VLOOKUP(B20,country_opex,3,FALSE))+V20+W20+X20+Y20+Z20))&lt;=0,"",VLOOKUP(B20,country_opex,7,FALSE)/((S20*pax_cap*load_mid*ROUND(K20*L20*revleg_mid,0))-(((battery/range_nm)*D20*ROUND(K20*L20*revleg_mid,0)*VLOOKUP(B20,country_opex,3,FALSE))+V20+W20+X20+Y20+Z20)))</f>
         <v/>
       </c>
-      <c r="AV20" s="43">
+      <c r="AW20" s="43">
         <f>IF(((S20*pax_cap*load_full*ROUND(K20*L20*revleg_full,0))-(((battery/range_nm)*D20*ROUND(K20*L20*revleg_full,0)*VLOOKUP(B20,country_opex,3,FALSE))+V20+W20+X20+Y20+Z20))&lt;=0,"",VLOOKUP(B20,country_opex,7,FALSE)/((S20*pax_cap*load_full*ROUND(K20*L20*revleg_full,0))-(((battery/range_nm)*D20*ROUND(K20*L20*revleg_full,0)*VLOOKUP(B20,country_opex,3,FALSE))+V20+W20+X20+Y20+Z20)))</f>
         <v/>
       </c>
-      <c r="AW20" s="44" t="inlineStr">
+      <c r="AX20" s="44" t="inlineStr">
         <is>
           <t>immaldives.com Maldives transfer costs (May 2026): shared speedboat $100-490 RT pp (=$50-245 OW); shared seaplane $400-820 RT pp (=$200-410 OW). atolltransfer.com scheduled $30-195 OW. Navier premium per-seat anchored between local premium speedboat and the seaplane the resort otherwise charges (R-MALDIVES-1).</t>
         </is>
       </c>
-      <c r="AX20" s="44" t="inlineStr">
+      <c r="AY20" s="44" t="inlineStr">
         <is>
           <t>NULL — pure inter-resort island-hop; no grounded crossing pool (R2). Geometry only.</t>
         </is>
@@ -5686,7 +5783,7 @@
         <v/>
       </c>
       <c r="AL21" s="34">
-        <f>IF(OR(AG21="",R21=0),"",MIN(IF(AS21="",9.9E+99,AS21),FLOOR(AK21/R21,1)))</f>
+        <f>IF(OR(AG21="",R21=0),"",MIN(IF(AT21="",9.9E+99,AT21),FLOOR(AK21/R21,1)))</f>
         <v/>
       </c>
       <c r="AM21" s="38">
@@ -5694,7 +5791,7 @@
         <v/>
       </c>
       <c r="AN21" s="36">
-        <f>IF(OR(AG21="",R21=0),"",MIN(IF(AS21="",9.9E+99,AS21),AK21/R21))</f>
+        <f>IF(OR(AG21="",R21=0),"",MIN(IF(AT21="",9.9E+99,AT21),AK21/R21))</f>
         <v/>
       </c>
       <c r="AO21" s="38">
@@ -5702,29 +5799,34 @@
         <v/>
       </c>
       <c r="AP21" s="40" t="n"/>
-      <c r="AQ21" s="41" t="n"/>
+      <c r="AQ21" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR21" s="41" t="n"/>
-      <c r="AS21" s="42" t="n">
+      <c r="AS21" s="41" t="n"/>
+      <c r="AT21" s="42" t="n">
         <v>4</v>
       </c>
-      <c r="AT21" s="43">
+      <c r="AU21" s="43">
         <f>IF(((S21*pax_cap*load_thin*ROUND(K21*L21*revleg_thin,0))-(((battery/range_nm)*D21*ROUND(K21*L21*revleg_thin,0)*VLOOKUP(B21,country_opex,3,FALSE))+V21+W21+X21+Y21+Z21))&lt;=0,"",VLOOKUP(B21,country_opex,7,FALSE)/((S21*pax_cap*load_thin*ROUND(K21*L21*revleg_thin,0))-(((battery/range_nm)*D21*ROUND(K21*L21*revleg_thin,0)*VLOOKUP(B21,country_opex,3,FALSE))+V21+W21+X21+Y21+Z21)))</f>
         <v/>
       </c>
-      <c r="AU21" s="43">
+      <c r="AV21" s="43">
         <f>IF(((S21*pax_cap*load_mid*ROUND(K21*L21*revleg_mid,0))-(((battery/range_nm)*D21*ROUND(K21*L21*revleg_mid,0)*VLOOKUP(B21,country_opex,3,FALSE))+V21+W21+X21+Y21+Z21))&lt;=0,"",VLOOKUP(B21,country_opex,7,FALSE)/((S21*pax_cap*load_mid*ROUND(K21*L21*revleg_mid,0))-(((battery/range_nm)*D21*ROUND(K21*L21*revleg_mid,0)*VLOOKUP(B21,country_opex,3,FALSE))+V21+W21+X21+Y21+Z21)))</f>
         <v/>
       </c>
-      <c r="AV21" s="43">
+      <c r="AW21" s="43">
         <f>IF(((S21*pax_cap*load_full*ROUND(K21*L21*revleg_full,0))-(((battery/range_nm)*D21*ROUND(K21*L21*revleg_full,0)*VLOOKUP(B21,country_opex,3,FALSE))+V21+W21+X21+Y21+Z21))&lt;=0,"",VLOOKUP(B21,country_opex,7,FALSE)/((S21*pax_cap*load_full*ROUND(K21*L21*revleg_full,0))-(((battery/range_nm)*D21*ROUND(K21*L21*revleg_full,0)*VLOOKUP(B21,country_opex,3,FALSE))+V21+W21+X21+Y21+Z21)))</f>
         <v/>
       </c>
-      <c r="AW21" s="44" t="inlineStr">
+      <c r="AX21" s="44" t="inlineStr">
         <is>
           <t>immaldives.com Maldives transfer costs (May 2026): shared speedboat $100-490 RT pp (=$50-245 OW); shared seaplane $400-820 RT pp (=$200-410 OW). atolltransfer.com scheduled $30-195 OW. Navier premium per-seat anchored between local premium speedboat and the seaplane the resort otherwise charges (R-MALDIVES-1).</t>
         </is>
       </c>
-      <c r="AX21" s="44" t="inlineStr">
+      <c r="AY21" s="44" t="inlineStr">
         <is>
           <t>Modeled arrivals = published keys x occupancy 0.70 (Maldives Min. of Tourism avg) x (365/6.5 nights avg stay) x 1.9 pax/room. Inbound one-way transfers. T5-modeled/med; keys T1 resort-published. NULL for pure inter-resort excursion legs (R2).</t>
         </is>
@@ -5882,7 +5984,7 @@
         <v/>
       </c>
       <c r="AL22" s="34">
-        <f>IF(OR(AG22="",R22=0),"",MIN(IF(AS22="",9.9E+99,AS22),FLOOR(AK22/R22,1)))</f>
+        <f>IF(OR(AG22="",R22=0),"",MIN(IF(AT22="",9.9E+99,AT22),FLOOR(AK22/R22,1)))</f>
         <v/>
       </c>
       <c r="AM22" s="38">
@@ -5890,7 +5992,7 @@
         <v/>
       </c>
       <c r="AN22" s="36">
-        <f>IF(OR(AG22="",R22=0),"",MIN(IF(AS22="",9.9E+99,AS22),AK22/R22))</f>
+        <f>IF(OR(AG22="",R22=0),"",MIN(IF(AT22="",9.9E+99,AT22),AK22/R22))</f>
         <v/>
       </c>
       <c r="AO22" s="38">
@@ -5898,29 +6000,34 @@
         <v/>
       </c>
       <c r="AP22" s="40" t="n"/>
-      <c r="AQ22" s="41" t="n"/>
+      <c r="AQ22" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR22" s="41" t="n"/>
-      <c r="AS22" s="42" t="n">
+      <c r="AS22" s="41" t="n"/>
+      <c r="AT22" s="42" t="n">
         <v>5</v>
       </c>
-      <c r="AT22" s="43">
+      <c r="AU22" s="43">
         <f>IF(((S22*pax_cap*load_thin*ROUND(K22*L22*revleg_thin,0))-(((battery/range_nm)*D22*ROUND(K22*L22*revleg_thin,0)*VLOOKUP(B22,country_opex,3,FALSE))+V22+W22+X22+Y22+Z22))&lt;=0,"",VLOOKUP(B22,country_opex,7,FALSE)/((S22*pax_cap*load_thin*ROUND(K22*L22*revleg_thin,0))-(((battery/range_nm)*D22*ROUND(K22*L22*revleg_thin,0)*VLOOKUP(B22,country_opex,3,FALSE))+V22+W22+X22+Y22+Z22)))</f>
         <v/>
       </c>
-      <c r="AU22" s="43">
+      <c r="AV22" s="43">
         <f>IF(((S22*pax_cap*load_mid*ROUND(K22*L22*revleg_mid,0))-(((battery/range_nm)*D22*ROUND(K22*L22*revleg_mid,0)*VLOOKUP(B22,country_opex,3,FALSE))+V22+W22+X22+Y22+Z22))&lt;=0,"",VLOOKUP(B22,country_opex,7,FALSE)/((S22*pax_cap*load_mid*ROUND(K22*L22*revleg_mid,0))-(((battery/range_nm)*D22*ROUND(K22*L22*revleg_mid,0)*VLOOKUP(B22,country_opex,3,FALSE))+V22+W22+X22+Y22+Z22)))</f>
         <v/>
       </c>
-      <c r="AV22" s="43">
+      <c r="AW22" s="43">
         <f>IF(((S22*pax_cap*load_full*ROUND(K22*L22*revleg_full,0))-(((battery/range_nm)*D22*ROUND(K22*L22*revleg_full,0)*VLOOKUP(B22,country_opex,3,FALSE))+V22+W22+X22+Y22+Z22))&lt;=0,"",VLOOKUP(B22,country_opex,7,FALSE)/((S22*pax_cap*load_full*ROUND(K22*L22*revleg_full,0))-(((battery/range_nm)*D22*ROUND(K22*L22*revleg_full,0)*VLOOKUP(B22,country_opex,3,FALSE))+V22+W22+X22+Y22+Z22)))</f>
         <v/>
       </c>
-      <c r="AW22" s="44" t="inlineStr">
+      <c r="AX22" s="44" t="inlineStr">
         <is>
           <t>immaldives.com Maldives transfer costs (May 2026): shared speedboat $100-490 RT pp (=$50-245 OW); shared seaplane $400-820 RT pp (=$200-410 OW). atolltransfer.com scheduled $30-195 OW. Navier premium per-seat anchored between local premium speedboat and the seaplane the resort otherwise charges (R-MALDIVES-1).</t>
         </is>
       </c>
-      <c r="AX22" s="44" t="inlineStr">
+      <c r="AY22" s="44" t="inlineStr">
         <is>
           <t>Modeled arrivals = published keys x occupancy 0.70 (Maldives Min. of Tourism avg) x (365/6.5 nights avg stay) x 1.9 pax/room. Inbound one-way transfers. T5-modeled/med; keys T1 resort-published. NULL for pure inter-resort excursion legs (R2).</t>
         </is>
@@ -6078,7 +6185,7 @@
         <v/>
       </c>
       <c r="AL23" s="34">
-        <f>IF(OR(AG23="",R23=0),"",MIN(IF(AS23="",9.9E+99,AS23),FLOOR(AK23/R23,1)))</f>
+        <f>IF(OR(AG23="",R23=0),"",MIN(IF(AT23="",9.9E+99,AT23),FLOOR(AK23/R23,1)))</f>
         <v/>
       </c>
       <c r="AM23" s="38">
@@ -6086,7 +6193,7 @@
         <v/>
       </c>
       <c r="AN23" s="36">
-        <f>IF(OR(AG23="",R23=0),"",MIN(IF(AS23="",9.9E+99,AS23),AK23/R23))</f>
+        <f>IF(OR(AG23="",R23=0),"",MIN(IF(AT23="",9.9E+99,AT23),AK23/R23))</f>
         <v/>
       </c>
       <c r="AO23" s="38">
@@ -6094,29 +6201,34 @@
         <v/>
       </c>
       <c r="AP23" s="40" t="n"/>
-      <c r="AQ23" s="41" t="n"/>
+      <c r="AQ23" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR23" s="41" t="n"/>
-      <c r="AS23" s="42" t="n">
+      <c r="AS23" s="41" t="n"/>
+      <c r="AT23" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="AT23" s="43">
+      <c r="AU23" s="43">
         <f>IF(((S23*pax_cap*load_thin*ROUND(K23*L23*revleg_thin,0))-(((battery/range_nm)*D23*ROUND(K23*L23*revleg_thin,0)*VLOOKUP(B23,country_opex,3,FALSE))+V23+W23+X23+Y23+Z23))&lt;=0,"",VLOOKUP(B23,country_opex,7,FALSE)/((S23*pax_cap*load_thin*ROUND(K23*L23*revleg_thin,0))-(((battery/range_nm)*D23*ROUND(K23*L23*revleg_thin,0)*VLOOKUP(B23,country_opex,3,FALSE))+V23+W23+X23+Y23+Z23)))</f>
         <v/>
       </c>
-      <c r="AU23" s="43">
+      <c r="AV23" s="43">
         <f>IF(((S23*pax_cap*load_mid*ROUND(K23*L23*revleg_mid,0))-(((battery/range_nm)*D23*ROUND(K23*L23*revleg_mid,0)*VLOOKUP(B23,country_opex,3,FALSE))+V23+W23+X23+Y23+Z23))&lt;=0,"",VLOOKUP(B23,country_opex,7,FALSE)/((S23*pax_cap*load_mid*ROUND(K23*L23*revleg_mid,0))-(((battery/range_nm)*D23*ROUND(K23*L23*revleg_mid,0)*VLOOKUP(B23,country_opex,3,FALSE))+V23+W23+X23+Y23+Z23)))</f>
         <v/>
       </c>
-      <c r="AV23" s="43">
+      <c r="AW23" s="43">
         <f>IF(((S23*pax_cap*load_full*ROUND(K23*L23*revleg_full,0))-(((battery/range_nm)*D23*ROUND(K23*L23*revleg_full,0)*VLOOKUP(B23,country_opex,3,FALSE))+V23+W23+X23+Y23+Z23))&lt;=0,"",VLOOKUP(B23,country_opex,7,FALSE)/((S23*pax_cap*load_full*ROUND(K23*L23*revleg_full,0))-(((battery/range_nm)*D23*ROUND(K23*L23*revleg_full,0)*VLOOKUP(B23,country_opex,3,FALSE))+V23+W23+X23+Y23+Z23)))</f>
         <v/>
       </c>
-      <c r="AW23" s="44" t="inlineStr">
+      <c r="AX23" s="44" t="inlineStr">
         <is>
           <t>immaldives.com Maldives transfer costs (May 2026): shared speedboat $100-490 RT pp (=$50-245 OW); shared seaplane $400-820 RT pp (=$200-410 OW). atolltransfer.com scheduled $30-195 OW. Navier premium per-seat anchored between local premium speedboat and the seaplane the resort otherwise charges (R-MALDIVES-1).</t>
         </is>
       </c>
-      <c r="AX23" s="44" t="inlineStr">
+      <c r="AY23" s="44" t="inlineStr">
         <is>
           <t>Modeled arrivals = published keys x occupancy 0.70 (Maldives Min. of Tourism avg) x (365/6.5 nights avg stay) x 1.9 pax/room. Inbound one-way transfers. T5-modeled/med; keys T1 resort-published. NULL for pure inter-resort excursion legs (R2).</t>
         </is>
@@ -6274,7 +6386,7 @@
         <v/>
       </c>
       <c r="AL24" s="34">
-        <f>IF(OR(AG24="",R24=0),"",MIN(IF(AS24="",9.9E+99,AS24),FLOOR(AK24/R24,1)))</f>
+        <f>IF(OR(AG24="",R24=0),"",MIN(IF(AT24="",9.9E+99,AT24),FLOOR(AK24/R24,1)))</f>
         <v/>
       </c>
       <c r="AM24" s="38">
@@ -6282,7 +6394,7 @@
         <v/>
       </c>
       <c r="AN24" s="36">
-        <f>IF(OR(AG24="",R24=0),"",MIN(IF(AS24="",9.9E+99,AS24),AK24/R24))</f>
+        <f>IF(OR(AG24="",R24=0),"",MIN(IF(AT24="",9.9E+99,AT24),AK24/R24))</f>
         <v/>
       </c>
       <c r="AO24" s="38">
@@ -6290,29 +6402,34 @@
         <v/>
       </c>
       <c r="AP24" s="40" t="n"/>
-      <c r="AQ24" s="41" t="n"/>
+      <c r="AQ24" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR24" s="41" t="n"/>
-      <c r="AS24" s="42" t="n">
+      <c r="AS24" s="41" t="n"/>
+      <c r="AT24" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="AT24" s="43">
+      <c r="AU24" s="43">
         <f>IF(((S24*pax_cap*load_thin*ROUND(K24*L24*revleg_thin,0))-(((battery/range_nm)*D24*ROUND(K24*L24*revleg_thin,0)*VLOOKUP(B24,country_opex,3,FALSE))+V24+W24+X24+Y24+Z24))&lt;=0,"",VLOOKUP(B24,country_opex,7,FALSE)/((S24*pax_cap*load_thin*ROUND(K24*L24*revleg_thin,0))-(((battery/range_nm)*D24*ROUND(K24*L24*revleg_thin,0)*VLOOKUP(B24,country_opex,3,FALSE))+V24+W24+X24+Y24+Z24)))</f>
         <v/>
       </c>
-      <c r="AU24" s="43">
+      <c r="AV24" s="43">
         <f>IF(((S24*pax_cap*load_mid*ROUND(K24*L24*revleg_mid,0))-(((battery/range_nm)*D24*ROUND(K24*L24*revleg_mid,0)*VLOOKUP(B24,country_opex,3,FALSE))+V24+W24+X24+Y24+Z24))&lt;=0,"",VLOOKUP(B24,country_opex,7,FALSE)/((S24*pax_cap*load_mid*ROUND(K24*L24*revleg_mid,0))-(((battery/range_nm)*D24*ROUND(K24*L24*revleg_mid,0)*VLOOKUP(B24,country_opex,3,FALSE))+V24+W24+X24+Y24+Z24)))</f>
         <v/>
       </c>
-      <c r="AV24" s="43">
+      <c r="AW24" s="43">
         <f>IF(((S24*pax_cap*load_full*ROUND(K24*L24*revleg_full,0))-(((battery/range_nm)*D24*ROUND(K24*L24*revleg_full,0)*VLOOKUP(B24,country_opex,3,FALSE))+V24+W24+X24+Y24+Z24))&lt;=0,"",VLOOKUP(B24,country_opex,7,FALSE)/((S24*pax_cap*load_full*ROUND(K24*L24*revleg_full,0))-(((battery/range_nm)*D24*ROUND(K24*L24*revleg_full,0)*VLOOKUP(B24,country_opex,3,FALSE))+V24+W24+X24+Y24+Z24)))</f>
         <v/>
       </c>
-      <c r="AW24" s="44" t="inlineStr">
+      <c r="AX24" s="44" t="inlineStr">
         <is>
           <t>immaldives.com Maldives transfer costs (May 2026): shared speedboat $100-490 RT pp (=$50-245 OW); shared seaplane $400-820 RT pp (=$200-410 OW). atolltransfer.com scheduled $30-195 OW. Navier premium per-seat anchored between local premium speedboat and the seaplane the resort otherwise charges (R-MALDIVES-1).</t>
         </is>
       </c>
-      <c r="AX24" s="44" t="inlineStr">
+      <c r="AY24" s="44" t="inlineStr">
         <is>
           <t>Modeled arrivals = published keys x occupancy 0.70 (Maldives Min. of Tourism avg) x (365/6.5 nights avg stay) x 1.9 pax/room. Inbound one-way transfers. T5-modeled/med; keys T1 resort-published. NULL for pure inter-resort excursion legs (R2).</t>
         </is>
@@ -6470,7 +6587,7 @@
         <v/>
       </c>
       <c r="AL25" s="34">
-        <f>IF(OR(AG25="",R25=0),"",MIN(IF(AS25="",9.9E+99,AS25),FLOOR(AK25/R25,1)))</f>
+        <f>IF(OR(AG25="",R25=0),"",MIN(IF(AT25="",9.9E+99,AT25),FLOOR(AK25/R25,1)))</f>
         <v/>
       </c>
       <c r="AM25" s="38">
@@ -6478,7 +6595,7 @@
         <v/>
       </c>
       <c r="AN25" s="36">
-        <f>IF(OR(AG25="",R25=0),"",MIN(IF(AS25="",9.9E+99,AS25),AK25/R25))</f>
+        <f>IF(OR(AG25="",R25=0),"",MIN(IF(AT25="",9.9E+99,AT25),AK25/R25))</f>
         <v/>
       </c>
       <c r="AO25" s="38">
@@ -6486,29 +6603,34 @@
         <v/>
       </c>
       <c r="AP25" s="40" t="n"/>
-      <c r="AQ25" s="41" t="n"/>
+      <c r="AQ25" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR25" s="41" t="n"/>
-      <c r="AS25" s="42" t="n">
+      <c r="AS25" s="41" t="n"/>
+      <c r="AT25" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="AT25" s="43">
+      <c r="AU25" s="43">
         <f>IF(((S25*pax_cap*load_thin*ROUND(K25*L25*revleg_thin,0))-(((battery/range_nm)*D25*ROUND(K25*L25*revleg_thin,0)*VLOOKUP(B25,country_opex,3,FALSE))+V25+W25+X25+Y25+Z25))&lt;=0,"",VLOOKUP(B25,country_opex,7,FALSE)/((S25*pax_cap*load_thin*ROUND(K25*L25*revleg_thin,0))-(((battery/range_nm)*D25*ROUND(K25*L25*revleg_thin,0)*VLOOKUP(B25,country_opex,3,FALSE))+V25+W25+X25+Y25+Z25)))</f>
         <v/>
       </c>
-      <c r="AU25" s="43">
+      <c r="AV25" s="43">
         <f>IF(((S25*pax_cap*load_mid*ROUND(K25*L25*revleg_mid,0))-(((battery/range_nm)*D25*ROUND(K25*L25*revleg_mid,0)*VLOOKUP(B25,country_opex,3,FALSE))+V25+W25+X25+Y25+Z25))&lt;=0,"",VLOOKUP(B25,country_opex,7,FALSE)/((S25*pax_cap*load_mid*ROUND(K25*L25*revleg_mid,0))-(((battery/range_nm)*D25*ROUND(K25*L25*revleg_mid,0)*VLOOKUP(B25,country_opex,3,FALSE))+V25+W25+X25+Y25+Z25)))</f>
         <v/>
       </c>
-      <c r="AV25" s="43">
+      <c r="AW25" s="43">
         <f>IF(((S25*pax_cap*load_full*ROUND(K25*L25*revleg_full,0))-(((battery/range_nm)*D25*ROUND(K25*L25*revleg_full,0)*VLOOKUP(B25,country_opex,3,FALSE))+V25+W25+X25+Y25+Z25))&lt;=0,"",VLOOKUP(B25,country_opex,7,FALSE)/((S25*pax_cap*load_full*ROUND(K25*L25*revleg_full,0))-(((battery/range_nm)*D25*ROUND(K25*L25*revleg_full,0)*VLOOKUP(B25,country_opex,3,FALSE))+V25+W25+X25+Y25+Z25)))</f>
         <v/>
       </c>
-      <c r="AW25" s="44" t="inlineStr">
+      <c r="AX25" s="44" t="inlineStr">
         <is>
           <t>immaldives.com Maldives transfer costs (May 2026): shared speedboat $100-490 RT pp (=$50-245 OW); shared seaplane $400-820 RT pp (=$200-410 OW). atolltransfer.com scheduled $30-195 OW. Navier premium per-seat anchored between local premium speedboat and the seaplane the resort otherwise charges (R-MALDIVES-1).</t>
         </is>
       </c>
-      <c r="AX25" s="44" t="inlineStr">
+      <c r="AY25" s="44" t="inlineStr">
         <is>
           <t>Modeled arrivals = published keys x occupancy 0.70 (Maldives Min. of Tourism avg) x (365/6.5 nights avg stay) x 1.9 pax/room. Inbound one-way transfers. T5-modeled/med; keys T1 resort-published. NULL for pure inter-resort excursion legs (R2).</t>
         </is>
@@ -6666,7 +6788,7 @@
         <v/>
       </c>
       <c r="AL26" s="34">
-        <f>IF(OR(AG26="",R26=0),"",MIN(IF(AS26="",9.9E+99,AS26),FLOOR(AK26/R26,1)))</f>
+        <f>IF(OR(AG26="",R26=0),"",MIN(IF(AT26="",9.9E+99,AT26),FLOOR(AK26/R26,1)))</f>
         <v/>
       </c>
       <c r="AM26" s="38">
@@ -6674,7 +6796,7 @@
         <v/>
       </c>
       <c r="AN26" s="36">
-        <f>IF(OR(AG26="",R26=0),"",MIN(IF(AS26="",9.9E+99,AS26),AK26/R26))</f>
+        <f>IF(OR(AG26="",R26=0),"",MIN(IF(AT26="",9.9E+99,AT26),AK26/R26))</f>
         <v/>
       </c>
       <c r="AO26" s="38">
@@ -6682,29 +6804,34 @@
         <v/>
       </c>
       <c r="AP26" s="40" t="n"/>
-      <c r="AQ26" s="41" t="n"/>
+      <c r="AQ26" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR26" s="41" t="n"/>
-      <c r="AS26" s="42" t="n">
+      <c r="AS26" s="41" t="n"/>
+      <c r="AT26" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="AT26" s="43">
+      <c r="AU26" s="43">
         <f>IF(((S26*pax_cap*load_thin*ROUND(K26*L26*revleg_thin,0))-(((battery/range_nm)*D26*ROUND(K26*L26*revleg_thin,0)*VLOOKUP(B26,country_opex,3,FALSE))+V26+W26+X26+Y26+Z26))&lt;=0,"",VLOOKUP(B26,country_opex,7,FALSE)/((S26*pax_cap*load_thin*ROUND(K26*L26*revleg_thin,0))-(((battery/range_nm)*D26*ROUND(K26*L26*revleg_thin,0)*VLOOKUP(B26,country_opex,3,FALSE))+V26+W26+X26+Y26+Z26)))</f>
         <v/>
       </c>
-      <c r="AU26" s="43">
+      <c r="AV26" s="43">
         <f>IF(((S26*pax_cap*load_mid*ROUND(K26*L26*revleg_mid,0))-(((battery/range_nm)*D26*ROUND(K26*L26*revleg_mid,0)*VLOOKUP(B26,country_opex,3,FALSE))+V26+W26+X26+Y26+Z26))&lt;=0,"",VLOOKUP(B26,country_opex,7,FALSE)/((S26*pax_cap*load_mid*ROUND(K26*L26*revleg_mid,0))-(((battery/range_nm)*D26*ROUND(K26*L26*revleg_mid,0)*VLOOKUP(B26,country_opex,3,FALSE))+V26+W26+X26+Y26+Z26)))</f>
         <v/>
       </c>
-      <c r="AV26" s="43">
+      <c r="AW26" s="43">
         <f>IF(((S26*pax_cap*load_full*ROUND(K26*L26*revleg_full,0))-(((battery/range_nm)*D26*ROUND(K26*L26*revleg_full,0)*VLOOKUP(B26,country_opex,3,FALSE))+V26+W26+X26+Y26+Z26))&lt;=0,"",VLOOKUP(B26,country_opex,7,FALSE)/((S26*pax_cap*load_full*ROUND(K26*L26*revleg_full,0))-(((battery/range_nm)*D26*ROUND(K26*L26*revleg_full,0)*VLOOKUP(B26,country_opex,3,FALSE))+V26+W26+X26+Y26+Z26)))</f>
         <v/>
       </c>
-      <c r="AW26" s="44" t="inlineStr">
+      <c r="AX26" s="44" t="inlineStr">
         <is>
           <t>immaldives.com Maldives transfer costs (May 2026): shared speedboat $100-490 RT pp (=$50-245 OW); shared seaplane $400-820 RT pp (=$200-410 OW). atolltransfer.com scheduled $30-195 OW. Navier premium per-seat anchored between local premium speedboat and the seaplane the resort otherwise charges (R-MALDIVES-1).</t>
         </is>
       </c>
-      <c r="AX26" s="44" t="inlineStr">
+      <c r="AY26" s="44" t="inlineStr">
         <is>
           <t>Modeled arrivals = published keys x occupancy 0.70 (Maldives Min. of Tourism avg) x (365/6.5 nights avg stay) x 1.9 pax/room. Inbound one-way transfers. T5-modeled/med; keys T1 resort-published. NULL for pure inter-resort excursion legs (R2).</t>
         </is>
@@ -6856,7 +6983,7 @@
         <v/>
       </c>
       <c r="AL27" s="34">
-        <f>IF(OR(AG27="",R27=0),"",MIN(IF(AS27="",9.9E+99,AS27),FLOOR(AK27/R27,1)))</f>
+        <f>IF(OR(AG27="",R27=0),"",MIN(IF(AT27="",9.9E+99,AT27),FLOOR(AK27/R27,1)))</f>
         <v/>
       </c>
       <c r="AM27" s="38">
@@ -6864,7 +6991,7 @@
         <v/>
       </c>
       <c r="AN27" s="36">
-        <f>IF(OR(AG27="",R27=0),"",MIN(IF(AS27="",9.9E+99,AS27),AK27/R27))</f>
+        <f>IF(OR(AG27="",R27=0),"",MIN(IF(AT27="",9.9E+99,AT27),AK27/R27))</f>
         <v/>
       </c>
       <c r="AO27" s="38">
@@ -6872,27 +6999,32 @@
         <v/>
       </c>
       <c r="AP27" s="40" t="n"/>
-      <c r="AQ27" s="41" t="n"/>
+      <c r="AQ27" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
       <c r="AR27" s="41" t="n"/>
-      <c r="AS27" s="42" t="n"/>
-      <c r="AT27" s="43">
+      <c r="AS27" s="41" t="n"/>
+      <c r="AT27" s="42" t="n"/>
+      <c r="AU27" s="43">
         <f>IF(((S27*pax_cap*load_thin*ROUND(K27*L27*revleg_thin,0))-(((battery/range_nm)*D27*ROUND(K27*L27*revleg_thin,0)*VLOOKUP(B27,country_opex,3,FALSE))+V27+W27+X27+Y27+Z27))&lt;=0,"",VLOOKUP(B27,country_opex,7,FALSE)/((S27*pax_cap*load_thin*ROUND(K27*L27*revleg_thin,0))-(((battery/range_nm)*D27*ROUND(K27*L27*revleg_thin,0)*VLOOKUP(B27,country_opex,3,FALSE))+V27+W27+X27+Y27+Z27)))</f>
         <v/>
       </c>
-      <c r="AU27" s="43">
+      <c r="AV27" s="43">
         <f>IF(((S27*pax_cap*load_mid*ROUND(K27*L27*revleg_mid,0))-(((battery/range_nm)*D27*ROUND(K27*L27*revleg_mid,0)*VLOOKUP(B27,country_opex,3,FALSE))+V27+W27+X27+Y27+Z27))&lt;=0,"",VLOOKUP(B27,country_opex,7,FALSE)/((S27*pax_cap*load_mid*ROUND(K27*L27*revleg_mid,0))-(((battery/range_nm)*D27*ROUND(K27*L27*revleg_mid,0)*VLOOKUP(B27,country_opex,3,FALSE))+V27+W27+X27+Y27+Z27)))</f>
         <v/>
       </c>
-      <c r="AV27" s="43">
+      <c r="AW27" s="43">
         <f>IF(((S27*pax_cap*load_full*ROUND(K27*L27*revleg_full,0))-(((battery/range_nm)*D27*ROUND(K27*L27*revleg_full,0)*VLOOKUP(B27,country_opex,3,FALSE))+V27+W27+X27+Y27+Z27))&lt;=0,"",VLOOKUP(B27,country_opex,7,FALSE)/((S27*pax_cap*load_full*ROUND(K27*L27*revleg_full,0))-(((battery/range_nm)*D27*ROUND(K27*L27*revleg_full,0)*VLOOKUP(B27,country_opex,3,FALSE))+V27+W27+X27+Y27+Z27)))</f>
         <v/>
       </c>
-      <c r="AW27" s="44" t="inlineStr">
+      <c r="AX27" s="44" t="inlineStr">
         <is>
           <t>immaldives.com Maldives transfer costs (May 2026): shared speedboat $100-490 RT pp (=$50-245 OW); shared seaplane $400-820 RT pp (=$200-410 OW). atolltransfer.com scheduled $30-195 OW. Navier premium per-seat anchored between local premium speedboat and the seaplane the resort otherwise charges (R-MALDIVES-1).</t>
         </is>
       </c>
-      <c r="AX27" s="44" t="inlineStr">
+      <c r="AY27" s="44" t="inlineStr">
         <is>
           <t>NULL — pure inter-resort island-hop; no grounded crossing pool (R2). Geometry only.</t>
         </is>
@@ -7050,7 +7182,7 @@
         <v/>
       </c>
       <c r="AL28" s="34">
-        <f>IF(OR(AG28="",R28=0),"",MIN(IF(AS28="",9.9E+99,AS28),FLOOR(AK28/R28,1)))</f>
+        <f>IF(OR(AG28="",R28=0),"",MIN(IF(AT28="",9.9E+99,AT28),FLOOR(AK28/R28,1)))</f>
         <v/>
       </c>
       <c r="AM28" s="38">
@@ -7058,7 +7190,7 @@
         <v/>
       </c>
       <c r="AN28" s="36">
-        <f>IF(OR(AG28="",R28=0),"",MIN(IF(AS28="",9.9E+99,AS28),AK28/R28))</f>
+        <f>IF(OR(AG28="",R28=0),"",MIN(IF(AT28="",9.9E+99,AT28),AK28/R28))</f>
         <v/>
       </c>
       <c r="AO28" s="38">
@@ -7066,29 +7198,34 @@
         <v/>
       </c>
       <c r="AP28" s="40" t="n"/>
-      <c r="AQ28" s="41" t="n"/>
+      <c r="AQ28" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR28" s="41" t="n"/>
-      <c r="AS28" s="42" t="n">
+      <c r="AS28" s="41" t="n"/>
+      <c r="AT28" s="42" t="n">
         <v>5</v>
       </c>
-      <c r="AT28" s="43">
+      <c r="AU28" s="43">
         <f>IF(((S28*pax_cap*load_thin*ROUND(K28*L28*revleg_thin,0))-(((battery/range_nm)*D28*ROUND(K28*L28*revleg_thin,0)*VLOOKUP(B28,country_opex,3,FALSE))+V28+W28+X28+Y28+Z28))&lt;=0,"",VLOOKUP(B28,country_opex,7,FALSE)/((S28*pax_cap*load_thin*ROUND(K28*L28*revleg_thin,0))-(((battery/range_nm)*D28*ROUND(K28*L28*revleg_thin,0)*VLOOKUP(B28,country_opex,3,FALSE))+V28+W28+X28+Y28+Z28)))</f>
         <v/>
       </c>
-      <c r="AU28" s="43">
+      <c r="AV28" s="43">
         <f>IF(((S28*pax_cap*load_mid*ROUND(K28*L28*revleg_mid,0))-(((battery/range_nm)*D28*ROUND(K28*L28*revleg_mid,0)*VLOOKUP(B28,country_opex,3,FALSE))+V28+W28+X28+Y28+Z28))&lt;=0,"",VLOOKUP(B28,country_opex,7,FALSE)/((S28*pax_cap*load_mid*ROUND(K28*L28*revleg_mid,0))-(((battery/range_nm)*D28*ROUND(K28*L28*revleg_mid,0)*VLOOKUP(B28,country_opex,3,FALSE))+V28+W28+X28+Y28+Z28)))</f>
         <v/>
       </c>
-      <c r="AV28" s="43">
+      <c r="AW28" s="43">
         <f>IF(((S28*pax_cap*load_full*ROUND(K28*L28*revleg_full,0))-(((battery/range_nm)*D28*ROUND(K28*L28*revleg_full,0)*VLOOKUP(B28,country_opex,3,FALSE))+V28+W28+X28+Y28+Z28))&lt;=0,"",VLOOKUP(B28,country_opex,7,FALSE)/((S28*pax_cap*load_full*ROUND(K28*L28*revleg_full,0))-(((battery/range_nm)*D28*ROUND(K28*L28*revleg_full,0)*VLOOKUP(B28,country_opex,3,FALSE))+V28+W28+X28+Y28+Z28)))</f>
         <v/>
       </c>
-      <c r="AW28" s="44" t="inlineStr">
+      <c r="AX28" s="44" t="inlineStr">
         <is>
           <t>immaldives.com Maldives transfer costs (May 2026): shared speedboat $100-490 RT pp (=$50-245 OW); shared seaplane $400-820 RT pp (=$200-410 OW). atolltransfer.com scheduled $30-195 OW. Navier premium per-seat anchored between local premium speedboat and the seaplane the resort otherwise charges (R-MALDIVES-1).</t>
         </is>
       </c>
-      <c r="AX28" s="44" t="inlineStr">
+      <c r="AY28" s="44" t="inlineStr">
         <is>
           <t>Modeled arrivals = published keys x occupancy 0.70 (Maldives Min. of Tourism avg) x (365/6.5 nights avg stay) x 1.9 pax/room. Inbound one-way transfers. T5-modeled/med; keys T1 resort-published. NULL for pure inter-resort excursion legs (R2).</t>
         </is>
@@ -7246,7 +7383,7 @@
         <v/>
       </c>
       <c r="AL29" s="34">
-        <f>IF(OR(AG29="",R29=0),"",MIN(IF(AS29="",9.9E+99,AS29),FLOOR(AK29/R29,1)))</f>
+        <f>IF(OR(AG29="",R29=0),"",MIN(IF(AT29="",9.9E+99,AT29),FLOOR(AK29/R29,1)))</f>
         <v/>
       </c>
       <c r="AM29" s="38">
@@ -7254,7 +7391,7 @@
         <v/>
       </c>
       <c r="AN29" s="36">
-        <f>IF(OR(AG29="",R29=0),"",MIN(IF(AS29="",9.9E+99,AS29),AK29/R29))</f>
+        <f>IF(OR(AG29="",R29=0),"",MIN(IF(AT29="",9.9E+99,AT29),AK29/R29))</f>
         <v/>
       </c>
       <c r="AO29" s="38">
@@ -7262,29 +7399,34 @@
         <v/>
       </c>
       <c r="AP29" s="40" t="n"/>
-      <c r="AQ29" s="41" t="n"/>
+      <c r="AQ29" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR29" s="41" t="n"/>
-      <c r="AS29" s="42" t="n">
+      <c r="AS29" s="41" t="n"/>
+      <c r="AT29" s="42" t="n">
         <v>5</v>
       </c>
-      <c r="AT29" s="43">
+      <c r="AU29" s="43">
         <f>IF(((S29*pax_cap*load_thin*ROUND(K29*L29*revleg_thin,0))-(((battery/range_nm)*D29*ROUND(K29*L29*revleg_thin,0)*VLOOKUP(B29,country_opex,3,FALSE))+V29+W29+X29+Y29+Z29))&lt;=0,"",VLOOKUP(B29,country_opex,7,FALSE)/((S29*pax_cap*load_thin*ROUND(K29*L29*revleg_thin,0))-(((battery/range_nm)*D29*ROUND(K29*L29*revleg_thin,0)*VLOOKUP(B29,country_opex,3,FALSE))+V29+W29+X29+Y29+Z29)))</f>
         <v/>
       </c>
-      <c r="AU29" s="43">
+      <c r="AV29" s="43">
         <f>IF(((S29*pax_cap*load_mid*ROUND(K29*L29*revleg_mid,0))-(((battery/range_nm)*D29*ROUND(K29*L29*revleg_mid,0)*VLOOKUP(B29,country_opex,3,FALSE))+V29+W29+X29+Y29+Z29))&lt;=0,"",VLOOKUP(B29,country_opex,7,FALSE)/((S29*pax_cap*load_mid*ROUND(K29*L29*revleg_mid,0))-(((battery/range_nm)*D29*ROUND(K29*L29*revleg_mid,0)*VLOOKUP(B29,country_opex,3,FALSE))+V29+W29+X29+Y29+Z29)))</f>
         <v/>
       </c>
-      <c r="AV29" s="43">
+      <c r="AW29" s="43">
         <f>IF(((S29*pax_cap*load_full*ROUND(K29*L29*revleg_full,0))-(((battery/range_nm)*D29*ROUND(K29*L29*revleg_full,0)*VLOOKUP(B29,country_opex,3,FALSE))+V29+W29+X29+Y29+Z29))&lt;=0,"",VLOOKUP(B29,country_opex,7,FALSE)/((S29*pax_cap*load_full*ROUND(K29*L29*revleg_full,0))-(((battery/range_nm)*D29*ROUND(K29*L29*revleg_full,0)*VLOOKUP(B29,country_opex,3,FALSE))+V29+W29+X29+Y29+Z29)))</f>
         <v/>
       </c>
-      <c r="AW29" s="44" t="inlineStr">
+      <c r="AX29" s="44" t="inlineStr">
         <is>
           <t>immaldives.com Maldives transfer costs (May 2026): shared speedboat $100-490 RT pp (=$50-245 OW); shared seaplane $400-820 RT pp (=$200-410 OW). atolltransfer.com scheduled $30-195 OW. Navier premium per-seat anchored between local premium speedboat and the seaplane the resort otherwise charges (R-MALDIVES-1).</t>
         </is>
       </c>
-      <c r="AX29" s="44" t="inlineStr">
+      <c r="AY29" s="44" t="inlineStr">
         <is>
           <t>Modeled arrivals = published keys x occupancy 0.70 (Maldives Min. of Tourism avg) x (365/6.5 nights avg stay) x 1.9 pax/room. Inbound one-way transfers. T5-modeled/med; keys T1 resort-published. NULL for pure inter-resort excursion legs (R2).</t>
         </is>
@@ -7442,7 +7584,7 @@
         <v/>
       </c>
       <c r="AL30" s="34">
-        <f>IF(OR(AG30="",R30=0),"",MIN(IF(AS30="",9.9E+99,AS30),FLOOR(AK30/R30,1)))</f>
+        <f>IF(OR(AG30="",R30=0),"",MIN(IF(AT30="",9.9E+99,AT30),FLOOR(AK30/R30,1)))</f>
         <v/>
       </c>
       <c r="AM30" s="38">
@@ -7450,7 +7592,7 @@
         <v/>
       </c>
       <c r="AN30" s="36">
-        <f>IF(OR(AG30="",R30=0),"",MIN(IF(AS30="",9.9E+99,AS30),AK30/R30))</f>
+        <f>IF(OR(AG30="",R30=0),"",MIN(IF(AT30="",9.9E+99,AT30),AK30/R30))</f>
         <v/>
       </c>
       <c r="AO30" s="38">
@@ -7458,29 +7600,34 @@
         <v/>
       </c>
       <c r="AP30" s="40" t="n"/>
-      <c r="AQ30" s="41" t="n"/>
+      <c r="AQ30" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR30" s="41" t="n"/>
-      <c r="AS30" s="42" t="n">
+      <c r="AS30" s="41" t="n"/>
+      <c r="AT30" s="42" t="n">
         <v>5</v>
       </c>
-      <c r="AT30" s="43">
+      <c r="AU30" s="43">
         <f>IF(((S30*pax_cap*load_thin*ROUND(K30*L30*revleg_thin,0))-(((battery/range_nm)*D30*ROUND(K30*L30*revleg_thin,0)*VLOOKUP(B30,country_opex,3,FALSE))+V30+W30+X30+Y30+Z30))&lt;=0,"",VLOOKUP(B30,country_opex,7,FALSE)/((S30*pax_cap*load_thin*ROUND(K30*L30*revleg_thin,0))-(((battery/range_nm)*D30*ROUND(K30*L30*revleg_thin,0)*VLOOKUP(B30,country_opex,3,FALSE))+V30+W30+X30+Y30+Z30)))</f>
         <v/>
       </c>
-      <c r="AU30" s="43">
+      <c r="AV30" s="43">
         <f>IF(((S30*pax_cap*load_mid*ROUND(K30*L30*revleg_mid,0))-(((battery/range_nm)*D30*ROUND(K30*L30*revleg_mid,0)*VLOOKUP(B30,country_opex,3,FALSE))+V30+W30+X30+Y30+Z30))&lt;=0,"",VLOOKUP(B30,country_opex,7,FALSE)/((S30*pax_cap*load_mid*ROUND(K30*L30*revleg_mid,0))-(((battery/range_nm)*D30*ROUND(K30*L30*revleg_mid,0)*VLOOKUP(B30,country_opex,3,FALSE))+V30+W30+X30+Y30+Z30)))</f>
         <v/>
       </c>
-      <c r="AV30" s="43">
+      <c r="AW30" s="43">
         <f>IF(((S30*pax_cap*load_full*ROUND(K30*L30*revleg_full,0))-(((battery/range_nm)*D30*ROUND(K30*L30*revleg_full,0)*VLOOKUP(B30,country_opex,3,FALSE))+V30+W30+X30+Y30+Z30))&lt;=0,"",VLOOKUP(B30,country_opex,7,FALSE)/((S30*pax_cap*load_full*ROUND(K30*L30*revleg_full,0))-(((battery/range_nm)*D30*ROUND(K30*L30*revleg_full,0)*VLOOKUP(B30,country_opex,3,FALSE))+V30+W30+X30+Y30+Z30)))</f>
         <v/>
       </c>
-      <c r="AW30" s="44" t="inlineStr">
+      <c r="AX30" s="44" t="inlineStr">
         <is>
           <t>Waldorf/Hilton official + reviews: shared transfer US$350 base + 23.2% tax &amp; service per adult per way = ~$431 all-in (onemileatatime, travelupdate/BLTraveler). PointChaser: boat transfer charged $862.40 RT = $431/way. Private yacht US$3,600++ per way max 8 guests = $450/pax (whole-boat charter ceiling). Premium per-seat shared = ~$400/way (base $350, all-in ~$431).</t>
         </is>
       </c>
-      <c r="AX30" s="44" t="inlineStr">
+      <c r="AY30" s="44" t="inlineStr">
         <is>
           <t>Modeled from resort key count. Waldorf Astoria Maldives Ithaafushi: ~120 villas/keys (published resort/Virtuoso/booking figures). corridor_annual_oneway_pax = keys x 365 x occ(0.75) / avg_stay(7 nights) x guests/key(2) x 2 (arr+dep) ~= keys x 156. 120 keys -&gt; ~18,800 one-way pax/yr. Airport(MLE)&lt;-&gt;this resort is the sole transfer corridor (boat/seaplane only; no road/air alt - R3-EXCEPTION: arrivals = crossing ridership).</t>
         </is>
@@ -7638,7 +7785,7 @@
         <v/>
       </c>
       <c r="AL31" s="34">
-        <f>IF(OR(AG31="",R31=0),"",MIN(IF(AS31="",9.9E+99,AS31),FLOOR(AK31/R31,1)))</f>
+        <f>IF(OR(AG31="",R31=0),"",MIN(IF(AT31="",9.9E+99,AT31),FLOOR(AK31/R31,1)))</f>
         <v/>
       </c>
       <c r="AM31" s="38">
@@ -7646,7 +7793,7 @@
         <v/>
       </c>
       <c r="AN31" s="36">
-        <f>IF(OR(AG31="",R31=0),"",MIN(IF(AS31="",9.9E+99,AS31),AK31/R31))</f>
+        <f>IF(OR(AG31="",R31=0),"",MIN(IF(AT31="",9.9E+99,AT31),AK31/R31))</f>
         <v/>
       </c>
       <c r="AO31" s="38">
@@ -7654,29 +7801,34 @@
         <v/>
       </c>
       <c r="AP31" s="40" t="n"/>
-      <c r="AQ31" s="41" t="n"/>
+      <c r="AQ31" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR31" s="41" t="n"/>
-      <c r="AS31" s="42" t="n">
+      <c r="AS31" s="41" t="n"/>
+      <c r="AT31" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="AT31" s="43">
+      <c r="AU31" s="43">
         <f>IF(((S31*pax_cap*load_thin*ROUND(K31*L31*revleg_thin,0))-(((battery/range_nm)*D31*ROUND(K31*L31*revleg_thin,0)*VLOOKUP(B31,country_opex,3,FALSE))+V31+W31+X31+Y31+Z31))&lt;=0,"",VLOOKUP(B31,country_opex,7,FALSE)/((S31*pax_cap*load_thin*ROUND(K31*L31*revleg_thin,0))-(((battery/range_nm)*D31*ROUND(K31*L31*revleg_thin,0)*VLOOKUP(B31,country_opex,3,FALSE))+V31+W31+X31+Y31+Z31)))</f>
         <v/>
       </c>
-      <c r="AU31" s="43">
+      <c r="AV31" s="43">
         <f>IF(((S31*pax_cap*load_mid*ROUND(K31*L31*revleg_mid,0))-(((battery/range_nm)*D31*ROUND(K31*L31*revleg_mid,0)*VLOOKUP(B31,country_opex,3,FALSE))+V31+W31+X31+Y31+Z31))&lt;=0,"",VLOOKUP(B31,country_opex,7,FALSE)/((S31*pax_cap*load_mid*ROUND(K31*L31*revleg_mid,0))-(((battery/range_nm)*D31*ROUND(K31*L31*revleg_mid,0)*VLOOKUP(B31,country_opex,3,FALSE))+V31+W31+X31+Y31+Z31)))</f>
         <v/>
       </c>
-      <c r="AV31" s="43">
+      <c r="AW31" s="43">
         <f>IF(((S31*pax_cap*load_full*ROUND(K31*L31*revleg_full,0))-(((battery/range_nm)*D31*ROUND(K31*L31*revleg_full,0)*VLOOKUP(B31,country_opex,3,FALSE))+V31+W31+X31+Y31+Z31))&lt;=0,"",VLOOKUP(B31,country_opex,7,FALSE)/((S31*pax_cap*load_full*ROUND(K31*L31*revleg_full,0))-(((battery/range_nm)*D31*ROUND(K31*L31*revleg_full,0)*VLOOKUP(B31,country_opex,3,FALSE))+V31+W31+X31+Y31+Z31)))</f>
         <v/>
       </c>
-      <c r="AW31" s="44" t="inlineStr">
+      <c r="AX31" s="44" t="inlineStr">
         <is>
           <t>COMO Hotels official (Tripadvisor FAQ quoting resort): private guest speedboat USD 250++ per person combined return = $125/way. maldivesnomad.com: COMO Cocoa Island $258 RT = $129/way. Private up-to-4-guest charter from ~$900/boat/way (Go Ocean Travel). Premium per-seat $130/way.</t>
         </is>
       </c>
-      <c r="AX31" s="44" t="inlineStr">
+      <c r="AY31" s="44" t="inlineStr">
         <is>
           <t>Modeled from resort key count. COMO Cocoa Island (Makunufushi, South Malé): ~33 villas/keys (published resort/Virtuoso/booking figures). corridor_annual_oneway_pax = keys x 365 x occ(0.75) / avg_stay(7 nights) x guests/key(2) x 2 (arr+dep) ~= keys x 156. 33 keys -&gt; ~5,200 one-way pax/yr. Airport(MLE)&lt;-&gt;this resort is the sole transfer corridor (boat/seaplane only; no road/air alt - R3-EXCEPTION: arrivals = crossing ridership).</t>
         </is>
@@ -7834,7 +7986,7 @@
         <v/>
       </c>
       <c r="AL32" s="34">
-        <f>IF(OR(AG32="",R32=0),"",MIN(IF(AS32="",9.9E+99,AS32),FLOOR(AK32/R32,1)))</f>
+        <f>IF(OR(AG32="",R32=0),"",MIN(IF(AT32="",9.9E+99,AT32),FLOOR(AK32/R32,1)))</f>
         <v/>
       </c>
       <c r="AM32" s="38">
@@ -7842,7 +7994,7 @@
         <v/>
       </c>
       <c r="AN32" s="36">
-        <f>IF(OR(AG32="",R32=0),"",MIN(IF(AS32="",9.9E+99,AS32),AK32/R32))</f>
+        <f>IF(OR(AG32="",R32=0),"",MIN(IF(AT32="",9.9E+99,AT32),AK32/R32))</f>
         <v/>
       </c>
       <c r="AO32" s="38">
@@ -7850,29 +8002,34 @@
         <v/>
       </c>
       <c r="AP32" s="40" t="n"/>
-      <c r="AQ32" s="41" t="n"/>
+      <c r="AQ32" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR32" s="41" t="n"/>
-      <c r="AS32" s="42" t="n">
+      <c r="AS32" s="41" t="n"/>
+      <c r="AT32" s="42" t="n">
         <v>5</v>
       </c>
-      <c r="AT32" s="43">
+      <c r="AU32" s="43">
         <f>IF(((S32*pax_cap*load_thin*ROUND(K32*L32*revleg_thin,0))-(((battery/range_nm)*D32*ROUND(K32*L32*revleg_thin,0)*VLOOKUP(B32,country_opex,3,FALSE))+V32+W32+X32+Y32+Z32))&lt;=0,"",VLOOKUP(B32,country_opex,7,FALSE)/((S32*pax_cap*load_thin*ROUND(K32*L32*revleg_thin,0))-(((battery/range_nm)*D32*ROUND(K32*L32*revleg_thin,0)*VLOOKUP(B32,country_opex,3,FALSE))+V32+W32+X32+Y32+Z32)))</f>
         <v/>
       </c>
-      <c r="AU32" s="43">
+      <c r="AV32" s="43">
         <f>IF(((S32*pax_cap*load_mid*ROUND(K32*L32*revleg_mid,0))-(((battery/range_nm)*D32*ROUND(K32*L32*revleg_mid,0)*VLOOKUP(B32,country_opex,3,FALSE))+V32+W32+X32+Y32+Z32))&lt;=0,"",VLOOKUP(B32,country_opex,7,FALSE)/((S32*pax_cap*load_mid*ROUND(K32*L32*revleg_mid,0))-(((battery/range_nm)*D32*ROUND(K32*L32*revleg_mid,0)*VLOOKUP(B32,country_opex,3,FALSE))+V32+W32+X32+Y32+Z32)))</f>
         <v/>
       </c>
-      <c r="AV32" s="43">
+      <c r="AW32" s="43">
         <f>IF(((S32*pax_cap*load_full*ROUND(K32*L32*revleg_full,0))-(((battery/range_nm)*D32*ROUND(K32*L32*revleg_full,0)*VLOOKUP(B32,country_opex,3,FALSE))+V32+W32+X32+Y32+Z32))&lt;=0,"",VLOOKUP(B32,country_opex,7,FALSE)/((S32*pax_cap*load_full*ROUND(K32*L32*revleg_full,0))-(((battery/range_nm)*D32*ROUND(K32*L32*revleg_full,0)*VLOOKUP(B32,country_opex,3,FALSE))+V32+W32+X32+Y32+Z32)))</f>
         <v/>
       </c>
-      <c r="AW32" s="44" t="inlineStr">
+      <c r="AX32" s="44" t="inlineStr">
         <is>
           <t>immaldives.com Maldives transfer costs (May 2026): shared speedboat $100-490 RT pp (=$50-245 OW); shared seaplane $400-820 RT pp (=$200-410 OW). atolltransfer.com scheduled $30-195 OW. Navier premium per-seat anchored between local premium speedboat and the seaplane the resort otherwise charges (R-MALDIVES-1).</t>
         </is>
       </c>
-      <c r="AX32" s="44" t="inlineStr">
+      <c r="AY32" s="44" t="inlineStr">
         <is>
           <t>Modeled arrivals = published keys x occupancy 0.70 (Maldives Min. of Tourism avg) x (365/6.5 nights avg stay) x 1.9 pax/room. Inbound one-way transfers. T5-modeled/med; keys T1 resort-published. NULL for pure inter-resort excursion legs (R2).</t>
         </is>
@@ -8030,7 +8187,7 @@
         <v/>
       </c>
       <c r="AL33" s="34">
-        <f>IF(OR(AG33="",R33=0),"",MIN(IF(AS33="",9.9E+99,AS33),FLOOR(AK33/R33,1)))</f>
+        <f>IF(OR(AG33="",R33=0),"",MIN(IF(AT33="",9.9E+99,AT33),FLOOR(AK33/R33,1)))</f>
         <v/>
       </c>
       <c r="AM33" s="38">
@@ -8038,7 +8195,7 @@
         <v/>
       </c>
       <c r="AN33" s="36">
-        <f>IF(OR(AG33="",R33=0),"",MIN(IF(AS33="",9.9E+99,AS33),AK33/R33))</f>
+        <f>IF(OR(AG33="",R33=0),"",MIN(IF(AT33="",9.9E+99,AT33),AK33/R33))</f>
         <v/>
       </c>
       <c r="AO33" s="38">
@@ -8046,29 +8203,34 @@
         <v/>
       </c>
       <c r="AP33" s="40" t="n"/>
-      <c r="AQ33" s="41" t="n"/>
+      <c r="AQ33" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR33" s="41" t="n"/>
-      <c r="AS33" s="42" t="n">
+      <c r="AS33" s="41" t="n"/>
+      <c r="AT33" s="42" t="n">
         <v>4</v>
       </c>
-      <c r="AT33" s="43">
+      <c r="AU33" s="43">
         <f>IF(((S33*pax_cap*load_thin*ROUND(K33*L33*revleg_thin,0))-(((battery/range_nm)*D33*ROUND(K33*L33*revleg_thin,0)*VLOOKUP(B33,country_opex,3,FALSE))+V33+W33+X33+Y33+Z33))&lt;=0,"",VLOOKUP(B33,country_opex,7,FALSE)/((S33*pax_cap*load_thin*ROUND(K33*L33*revleg_thin,0))-(((battery/range_nm)*D33*ROUND(K33*L33*revleg_thin,0)*VLOOKUP(B33,country_opex,3,FALSE))+V33+W33+X33+Y33+Z33)))</f>
         <v/>
       </c>
-      <c r="AU33" s="43">
+      <c r="AV33" s="43">
         <f>IF(((S33*pax_cap*load_mid*ROUND(K33*L33*revleg_mid,0))-(((battery/range_nm)*D33*ROUND(K33*L33*revleg_mid,0)*VLOOKUP(B33,country_opex,3,FALSE))+V33+W33+X33+Y33+Z33))&lt;=0,"",VLOOKUP(B33,country_opex,7,FALSE)/((S33*pax_cap*load_mid*ROUND(K33*L33*revleg_mid,0))-(((battery/range_nm)*D33*ROUND(K33*L33*revleg_mid,0)*VLOOKUP(B33,country_opex,3,FALSE))+V33+W33+X33+Y33+Z33)))</f>
         <v/>
       </c>
-      <c r="AV33" s="43">
+      <c r="AW33" s="43">
         <f>IF(((S33*pax_cap*load_full*ROUND(K33*L33*revleg_full,0))-(((battery/range_nm)*D33*ROUND(K33*L33*revleg_full,0)*VLOOKUP(B33,country_opex,3,FALSE))+V33+W33+X33+Y33+Z33))&lt;=0,"",VLOOKUP(B33,country_opex,7,FALSE)/((S33*pax_cap*load_full*ROUND(K33*L33*revleg_full,0))-(((battery/range_nm)*D33*ROUND(K33*L33*revleg_full,0)*VLOOKUP(B33,country_opex,3,FALSE))+V33+W33+X33+Y33+Z33)))</f>
         <v/>
       </c>
-      <c r="AW33" s="44" t="inlineStr">
+      <c r="AX33" s="44" t="inlineStr">
         <is>
           <t>immaldives.com Maldives transfer costs (May 2026): shared speedboat $100-490 RT pp (=$50-245 OW); shared seaplane $400-820 RT pp (=$200-410 OW). atolltransfer.com scheduled $30-195 OW. Navier premium per-seat anchored between local premium speedboat and the seaplane the resort otherwise charges (R-MALDIVES-1).</t>
         </is>
       </c>
-      <c r="AX33" s="44" t="inlineStr">
+      <c r="AY33" s="44" t="inlineStr">
         <is>
           <t>Modeled arrivals = published keys x occupancy 0.70 (Maldives Min. of Tourism avg) x (365/6.5 nights avg stay) x 1.9 pax/room. Inbound one-way transfers. T5-modeled/med; keys T1 resort-published. NULL for pure inter-resort excursion legs (R2).</t>
         </is>
@@ -8226,7 +8388,7 @@
         <v/>
       </c>
       <c r="AL34" s="34">
-        <f>IF(OR(AG34="",R34=0),"",MIN(IF(AS34="",9.9E+99,AS34),FLOOR(AK34/R34,1)))</f>
+        <f>IF(OR(AG34="",R34=0),"",MIN(IF(AT34="",9.9E+99,AT34),FLOOR(AK34/R34,1)))</f>
         <v/>
       </c>
       <c r="AM34" s="38">
@@ -8234,7 +8396,7 @@
         <v/>
       </c>
       <c r="AN34" s="36">
-        <f>IF(OR(AG34="",R34=0),"",MIN(IF(AS34="",9.9E+99,AS34),AK34/R34))</f>
+        <f>IF(OR(AG34="",R34=0),"",MIN(IF(AT34="",9.9E+99,AT34),AK34/R34))</f>
         <v/>
       </c>
       <c r="AO34" s="38">
@@ -8242,29 +8404,34 @@
         <v/>
       </c>
       <c r="AP34" s="40" t="n"/>
-      <c r="AQ34" s="41" t="n"/>
+      <c r="AQ34" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR34" s="41" t="n"/>
-      <c r="AS34" s="42" t="n">
+      <c r="AS34" s="41" t="n"/>
+      <c r="AT34" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="AT34" s="43">
+      <c r="AU34" s="43">
         <f>IF(((S34*pax_cap*load_thin*ROUND(K34*L34*revleg_thin,0))-(((battery/range_nm)*D34*ROUND(K34*L34*revleg_thin,0)*VLOOKUP(B34,country_opex,3,FALSE))+V34+W34+X34+Y34+Z34))&lt;=0,"",VLOOKUP(B34,country_opex,7,FALSE)/((S34*pax_cap*load_thin*ROUND(K34*L34*revleg_thin,0))-(((battery/range_nm)*D34*ROUND(K34*L34*revleg_thin,0)*VLOOKUP(B34,country_opex,3,FALSE))+V34+W34+X34+Y34+Z34)))</f>
         <v/>
       </c>
-      <c r="AU34" s="43">
+      <c r="AV34" s="43">
         <f>IF(((S34*pax_cap*load_mid*ROUND(K34*L34*revleg_mid,0))-(((battery/range_nm)*D34*ROUND(K34*L34*revleg_mid,0)*VLOOKUP(B34,country_opex,3,FALSE))+V34+W34+X34+Y34+Z34))&lt;=0,"",VLOOKUP(B34,country_opex,7,FALSE)/((S34*pax_cap*load_mid*ROUND(K34*L34*revleg_mid,0))-(((battery/range_nm)*D34*ROUND(K34*L34*revleg_mid,0)*VLOOKUP(B34,country_opex,3,FALSE))+V34+W34+X34+Y34+Z34)))</f>
         <v/>
       </c>
-      <c r="AV34" s="43">
+      <c r="AW34" s="43">
         <f>IF(((S34*pax_cap*load_full*ROUND(K34*L34*revleg_full,0))-(((battery/range_nm)*D34*ROUND(K34*L34*revleg_full,0)*VLOOKUP(B34,country_opex,3,FALSE))+V34+W34+X34+Y34+Z34))&lt;=0,"",VLOOKUP(B34,country_opex,7,FALSE)/((S34*pax_cap*load_full*ROUND(K34*L34*revleg_full,0))-(((battery/range_nm)*D34*ROUND(K34*L34*revleg_full,0)*VLOOKUP(B34,country_opex,3,FALSE))+V34+W34+X34+Y34+Z34)))</f>
         <v/>
       </c>
-      <c r="AW34" s="44" t="inlineStr">
+      <c r="AX34" s="44" t="inlineStr">
         <is>
           <t>immaldives.com Maldives transfer costs (May 2026): shared speedboat $100-490 RT pp (=$50-245 OW); shared seaplane $400-820 RT pp (=$200-410 OW). atolltransfer.com scheduled $30-195 OW. Navier premium per-seat anchored between local premium speedboat and the seaplane the resort otherwise charges (R-MALDIVES-1).</t>
         </is>
       </c>
-      <c r="AX34" s="44" t="inlineStr">
+      <c r="AY34" s="44" t="inlineStr">
         <is>
           <t>Modeled arrivals = published keys x occupancy 0.70 (Maldives Min. of Tourism avg) x (365/6.5 nights avg stay) x 1.9 pax/room. Inbound one-way transfers. T5-modeled/med; keys T1 resort-published. NULL for pure inter-resort excursion legs (R2).</t>
         </is>
@@ -8416,7 +8583,7 @@
         <v/>
       </c>
       <c r="AL35" s="34">
-        <f>IF(OR(AG35="",R35=0),"",MIN(IF(AS35="",9.9E+99,AS35),FLOOR(AK35/R35,1)))</f>
+        <f>IF(OR(AG35="",R35=0),"",MIN(IF(AT35="",9.9E+99,AT35),FLOOR(AK35/R35,1)))</f>
         <v/>
       </c>
       <c r="AM35" s="38">
@@ -8424,7 +8591,7 @@
         <v/>
       </c>
       <c r="AN35" s="36">
-        <f>IF(OR(AG35="",R35=0),"",MIN(IF(AS35="",9.9E+99,AS35),AK35/R35))</f>
+        <f>IF(OR(AG35="",R35=0),"",MIN(IF(AT35="",9.9E+99,AT35),AK35/R35))</f>
         <v/>
       </c>
       <c r="AO35" s="38">
@@ -8432,27 +8599,32 @@
         <v/>
       </c>
       <c r="AP35" s="40" t="n"/>
-      <c r="AQ35" s="41" t="n"/>
+      <c r="AQ35" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
       <c r="AR35" s="41" t="n"/>
-      <c r="AS35" s="42" t="n"/>
-      <c r="AT35" s="43">
+      <c r="AS35" s="41" t="n"/>
+      <c r="AT35" s="42" t="n"/>
+      <c r="AU35" s="43">
         <f>IF(((S35*pax_cap*load_thin*ROUND(K35*L35*revleg_thin,0))-(((battery/range_nm)*D35*ROUND(K35*L35*revleg_thin,0)*VLOOKUP(B35,country_opex,3,FALSE))+V35+W35+X35+Y35+Z35))&lt;=0,"",VLOOKUP(B35,country_opex,7,FALSE)/((S35*pax_cap*load_thin*ROUND(K35*L35*revleg_thin,0))-(((battery/range_nm)*D35*ROUND(K35*L35*revleg_thin,0)*VLOOKUP(B35,country_opex,3,FALSE))+V35+W35+X35+Y35+Z35)))</f>
         <v/>
       </c>
-      <c r="AU35" s="43">
+      <c r="AV35" s="43">
         <f>IF(((S35*pax_cap*load_mid*ROUND(K35*L35*revleg_mid,0))-(((battery/range_nm)*D35*ROUND(K35*L35*revleg_mid,0)*VLOOKUP(B35,country_opex,3,FALSE))+V35+W35+X35+Y35+Z35))&lt;=0,"",VLOOKUP(B35,country_opex,7,FALSE)/((S35*pax_cap*load_mid*ROUND(K35*L35*revleg_mid,0))-(((battery/range_nm)*D35*ROUND(K35*L35*revleg_mid,0)*VLOOKUP(B35,country_opex,3,FALSE))+V35+W35+X35+Y35+Z35)))</f>
         <v/>
       </c>
-      <c r="AV35" s="43">
+      <c r="AW35" s="43">
         <f>IF(((S35*pax_cap*load_full*ROUND(K35*L35*revleg_full,0))-(((battery/range_nm)*D35*ROUND(K35*L35*revleg_full,0)*VLOOKUP(B35,country_opex,3,FALSE))+V35+W35+X35+Y35+Z35))&lt;=0,"",VLOOKUP(B35,country_opex,7,FALSE)/((S35*pax_cap*load_full*ROUND(K35*L35*revleg_full,0))-(((battery/range_nm)*D35*ROUND(K35*L35*revleg_full,0)*VLOOKUP(B35,country_opex,3,FALSE))+V35+W35+X35+Y35+Z35)))</f>
         <v/>
       </c>
-      <c r="AW35" s="44" t="inlineStr">
+      <c r="AX35" s="44" t="inlineStr">
         <is>
           <t>immaldives.com Maldives transfer costs (May 2026): shared speedboat $100-490 RT pp (=$50-245 OW); shared seaplane $400-820 RT pp (=$200-410 OW). atolltransfer.com scheduled $30-195 OW. Navier premium per-seat anchored between local premium speedboat and the seaplane the resort otherwise charges (R-MALDIVES-1).</t>
         </is>
       </c>
-      <c r="AX35" s="44" t="inlineStr">
+      <c r="AY35" s="44" t="inlineStr">
         <is>
           <t>NULL — pure inter-resort island-hop; no grounded crossing pool (R2). Geometry only.</t>
         </is>
@@ -8610,7 +8782,7 @@
         <v/>
       </c>
       <c r="AL36" s="34">
-        <f>IF(OR(AG36="",R36=0),"",MIN(IF(AS36="",9.9E+99,AS36),FLOOR(AK36/R36,1)))</f>
+        <f>IF(OR(AG36="",R36=0),"",MIN(IF(AT36="",9.9E+99,AT36),FLOOR(AK36/R36,1)))</f>
         <v/>
       </c>
       <c r="AM36" s="38">
@@ -8618,7 +8790,7 @@
         <v/>
       </c>
       <c r="AN36" s="36">
-        <f>IF(OR(AG36="",R36=0),"",MIN(IF(AS36="",9.9E+99,AS36),AK36/R36))</f>
+        <f>IF(OR(AG36="",R36=0),"",MIN(IF(AT36="",9.9E+99,AT36),AK36/R36))</f>
         <v/>
       </c>
       <c r="AO36" s="38">
@@ -8626,29 +8798,34 @@
         <v/>
       </c>
       <c r="AP36" s="40" t="n"/>
-      <c r="AQ36" s="41" t="n"/>
+      <c r="AQ36" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR36" s="41" t="n"/>
-      <c r="AS36" s="42" t="n">
+      <c r="AS36" s="41" t="n"/>
+      <c r="AT36" s="42" t="n">
         <v>5</v>
       </c>
-      <c r="AT36" s="43">
+      <c r="AU36" s="43">
         <f>IF(((S36*pax_cap*load_thin*ROUND(K36*L36*revleg_thin,0))-(((battery/range_nm)*D36*ROUND(K36*L36*revleg_thin,0)*VLOOKUP(B36,country_opex,3,FALSE))+V36+W36+X36+Y36+Z36))&lt;=0,"",VLOOKUP(B36,country_opex,7,FALSE)/((S36*pax_cap*load_thin*ROUND(K36*L36*revleg_thin,0))-(((battery/range_nm)*D36*ROUND(K36*L36*revleg_thin,0)*VLOOKUP(B36,country_opex,3,FALSE))+V36+W36+X36+Y36+Z36)))</f>
         <v/>
       </c>
-      <c r="AU36" s="43">
+      <c r="AV36" s="43">
         <f>IF(((S36*pax_cap*load_mid*ROUND(K36*L36*revleg_mid,0))-(((battery/range_nm)*D36*ROUND(K36*L36*revleg_mid,0)*VLOOKUP(B36,country_opex,3,FALSE))+V36+W36+X36+Y36+Z36))&lt;=0,"",VLOOKUP(B36,country_opex,7,FALSE)/((S36*pax_cap*load_mid*ROUND(K36*L36*revleg_mid,0))-(((battery/range_nm)*D36*ROUND(K36*L36*revleg_mid,0)*VLOOKUP(B36,country_opex,3,FALSE))+V36+W36+X36+Y36+Z36)))</f>
         <v/>
       </c>
-      <c r="AV36" s="43">
+      <c r="AW36" s="43">
         <f>IF(((S36*pax_cap*load_full*ROUND(K36*L36*revleg_full,0))-(((battery/range_nm)*D36*ROUND(K36*L36*revleg_full,0)*VLOOKUP(B36,country_opex,3,FALSE))+V36+W36+X36+Y36+Z36))&lt;=0,"",VLOOKUP(B36,country_opex,7,FALSE)/((S36*pax_cap*load_full*ROUND(K36*L36*revleg_full,0))-(((battery/range_nm)*D36*ROUND(K36*L36*revleg_full,0)*VLOOKUP(B36,country_opex,3,FALSE))+V36+W36+X36+Y36+Z36)))</f>
         <v/>
       </c>
-      <c r="AW36" s="44" t="inlineStr">
+      <c r="AX36" s="44" t="inlineStr">
         <is>
           <t>One&amp;Only Reethi Rah (oneandonlyresorts.com publishes shared luxury boat transfer at a charge; 45-min). Luxury Escapes listing: airport shuttle USD 1,260/person roundtrip = $630/way (premium scheduled), plus a $325 lower tier. Tripadvisor forum: Reethi Rah transfer quoted $450/person. Premium per-seat ~$500/way.</t>
         </is>
       </c>
-      <c r="AX36" s="44" t="inlineStr">
+      <c r="AY36" s="44" t="inlineStr">
         <is>
           <t>Modeled from resort key count. One&amp;Only Reethi Rah: ~130 villas/keys (published resort/Virtuoso/booking figures). corridor_annual_oneway_pax = keys x 365 x occ(0.75) / avg_stay(7 nights) x guests/key(2) x 2 (arr+dep) ~= keys x 156. 130 keys -&gt; ~20,300 one-way pax/yr. Airport(MLE)&lt;-&gt;this resort is the sole transfer corridor (boat/seaplane only; no road/air alt - R3-EXCEPTION: arrivals = crossing ridership).</t>
         </is>
@@ -8806,7 +8983,7 @@
         <v/>
       </c>
       <c r="AL37" s="34">
-        <f>IF(OR(AG37="",R37=0),"",MIN(IF(AS37="",9.9E+99,AS37),FLOOR(AK37/R37,1)))</f>
+        <f>IF(OR(AG37="",R37=0),"",MIN(IF(AT37="",9.9E+99,AT37),FLOOR(AK37/R37,1)))</f>
         <v/>
       </c>
       <c r="AM37" s="38">
@@ -8814,7 +8991,7 @@
         <v/>
       </c>
       <c r="AN37" s="36">
-        <f>IF(OR(AG37="",R37=0),"",MIN(IF(AS37="",9.9E+99,AS37),AK37/R37))</f>
+        <f>IF(OR(AG37="",R37=0),"",MIN(IF(AT37="",9.9E+99,AT37),AK37/R37))</f>
         <v/>
       </c>
       <c r="AO37" s="38">
@@ -8822,29 +8999,34 @@
         <v/>
       </c>
       <c r="AP37" s="40" t="n"/>
-      <c r="AQ37" s="41" t="n"/>
+      <c r="AQ37" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR37" s="41" t="n"/>
-      <c r="AS37" s="42" t="n">
+      <c r="AS37" s="41" t="n"/>
+      <c r="AT37" s="42" t="n">
         <v>4</v>
       </c>
-      <c r="AT37" s="43">
+      <c r="AU37" s="43">
         <f>IF(((S37*pax_cap*load_thin*ROUND(K37*L37*revleg_thin,0))-(((battery/range_nm)*D37*ROUND(K37*L37*revleg_thin,0)*VLOOKUP(B37,country_opex,3,FALSE))+V37+W37+X37+Y37+Z37))&lt;=0,"",VLOOKUP(B37,country_opex,7,FALSE)/((S37*pax_cap*load_thin*ROUND(K37*L37*revleg_thin,0))-(((battery/range_nm)*D37*ROUND(K37*L37*revleg_thin,0)*VLOOKUP(B37,country_opex,3,FALSE))+V37+W37+X37+Y37+Z37)))</f>
         <v/>
       </c>
-      <c r="AU37" s="43">
+      <c r="AV37" s="43">
         <f>IF(((S37*pax_cap*load_mid*ROUND(K37*L37*revleg_mid,0))-(((battery/range_nm)*D37*ROUND(K37*L37*revleg_mid,0)*VLOOKUP(B37,country_opex,3,FALSE))+V37+W37+X37+Y37+Z37))&lt;=0,"",VLOOKUP(B37,country_opex,7,FALSE)/((S37*pax_cap*load_mid*ROUND(K37*L37*revleg_mid,0))-(((battery/range_nm)*D37*ROUND(K37*L37*revleg_mid,0)*VLOOKUP(B37,country_opex,3,FALSE))+V37+W37+X37+Y37+Z37)))</f>
         <v/>
       </c>
-      <c r="AV37" s="43">
+      <c r="AW37" s="43">
         <f>IF(((S37*pax_cap*load_full*ROUND(K37*L37*revleg_full,0))-(((battery/range_nm)*D37*ROUND(K37*L37*revleg_full,0)*VLOOKUP(B37,country_opex,3,FALSE))+V37+W37+X37+Y37+Z37))&lt;=0,"",VLOOKUP(B37,country_opex,7,FALSE)/((S37*pax_cap*load_full*ROUND(K37*L37*revleg_full,0))-(((battery/range_nm)*D37*ROUND(K37*L37*revleg_full,0)*VLOOKUP(B37,country_opex,3,FALSE))+V37+W37+X37+Y37+Z37)))</f>
         <v/>
       </c>
-      <c r="AW37" s="44" t="inlineStr">
+      <c r="AX37" s="44" t="inlineStr">
         <is>
           <t>immaldives.com Maldives transfer costs (May 2026): shared speedboat $100-490 RT pp (=$50-245 OW); shared seaplane $400-820 RT pp (=$200-410 OW). atolltransfer.com scheduled $30-195 OW. Navier premium per-seat anchored between local premium speedboat and the seaplane the resort otherwise charges (R-MALDIVES-1).</t>
         </is>
       </c>
-      <c r="AX37" s="44" t="inlineStr">
+      <c r="AY37" s="44" t="inlineStr">
         <is>
           <t>Modeled arrivals = published keys x occupancy 0.70 (Maldives Min. of Tourism avg) x (365/6.5 nights avg stay) x 1.9 pax/room. Inbound one-way transfers. T5-modeled/med; keys T1 resort-published. NULL for pure inter-resort excursion legs (R2).</t>
         </is>
@@ -9002,7 +9184,7 @@
         <v/>
       </c>
       <c r="AL38" s="34">
-        <f>IF(OR(AG38="",R38=0),"",MIN(IF(AS38="",9.9E+99,AS38),FLOOR(AK38/R38,1)))</f>
+        <f>IF(OR(AG38="",R38=0),"",MIN(IF(AT38="",9.9E+99,AT38),FLOOR(AK38/R38,1)))</f>
         <v/>
       </c>
       <c r="AM38" s="38">
@@ -9010,7 +9192,7 @@
         <v/>
       </c>
       <c r="AN38" s="36">
-        <f>IF(OR(AG38="",R38=0),"",MIN(IF(AS38="",9.9E+99,AS38),AK38/R38))</f>
+        <f>IF(OR(AG38="",R38=0),"",MIN(IF(AT38="",9.9E+99,AT38),AK38/R38))</f>
         <v/>
       </c>
       <c r="AO38" s="38">
@@ -9018,29 +9200,34 @@
         <v/>
       </c>
       <c r="AP38" s="40" t="n"/>
-      <c r="AQ38" s="41" t="n"/>
+      <c r="AQ38" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR38" s="41" t="n"/>
-      <c r="AS38" s="42" t="n">
+      <c r="AS38" s="41" t="n"/>
+      <c r="AT38" s="42" t="n">
         <v>4</v>
       </c>
-      <c r="AT38" s="43">
+      <c r="AU38" s="43">
         <f>IF(((S38*pax_cap*load_thin*ROUND(K38*L38*revleg_thin,0))-(((battery/range_nm)*D38*ROUND(K38*L38*revleg_thin,0)*VLOOKUP(B38,country_opex,3,FALSE))+V38+W38+X38+Y38+Z38))&lt;=0,"",VLOOKUP(B38,country_opex,7,FALSE)/((S38*pax_cap*load_thin*ROUND(K38*L38*revleg_thin,0))-(((battery/range_nm)*D38*ROUND(K38*L38*revleg_thin,0)*VLOOKUP(B38,country_opex,3,FALSE))+V38+W38+X38+Y38+Z38)))</f>
         <v/>
       </c>
-      <c r="AU38" s="43">
+      <c r="AV38" s="43">
         <f>IF(((S38*pax_cap*load_mid*ROUND(K38*L38*revleg_mid,0))-(((battery/range_nm)*D38*ROUND(K38*L38*revleg_mid,0)*VLOOKUP(B38,country_opex,3,FALSE))+V38+W38+X38+Y38+Z38))&lt;=0,"",VLOOKUP(B38,country_opex,7,FALSE)/((S38*pax_cap*load_mid*ROUND(K38*L38*revleg_mid,0))-(((battery/range_nm)*D38*ROUND(K38*L38*revleg_mid,0)*VLOOKUP(B38,country_opex,3,FALSE))+V38+W38+X38+Y38+Z38)))</f>
         <v/>
       </c>
-      <c r="AV38" s="43">
+      <c r="AW38" s="43">
         <f>IF(((S38*pax_cap*load_full*ROUND(K38*L38*revleg_full,0))-(((battery/range_nm)*D38*ROUND(K38*L38*revleg_full,0)*VLOOKUP(B38,country_opex,3,FALSE))+V38+W38+X38+Y38+Z38))&lt;=0,"",VLOOKUP(B38,country_opex,7,FALSE)/((S38*pax_cap*load_full*ROUND(K38*L38*revleg_full,0))-(((battery/range_nm)*D38*ROUND(K38*L38*revleg_full,0)*VLOOKUP(B38,country_opex,3,FALSE))+V38+W38+X38+Y38+Z38)))</f>
         <v/>
       </c>
-      <c r="AW38" s="44" t="inlineStr">
+      <c r="AX38" s="44" t="inlineStr">
         <is>
           <t>Ritz-Carlton Maldives Fari Islands OFFICIAL (ritzcarlton.com): on-demand roundtrip speedboat USD 1,027 net/adult (incl 10% service) = $513/way. johnnyafrica review: $1,024/person 2025. FlyerTalk master thread: shared speedboat $901/adult RT; private 48' speedboat $2,800/person (charter). Premium per-seat $510/way.</t>
         </is>
       </c>
-      <c r="AX38" s="44" t="inlineStr">
+      <c r="AY38" s="44" t="inlineStr">
         <is>
           <t>Modeled from resort key count. The Ritz-Carlton Maldives, Fari Islands: ~100 villas/keys (published resort/Virtuoso/booking figures). corridor_annual_oneway_pax = keys x 365 x occ(0.75) / avg_stay(7 nights) x guests/key(2) x 2 (arr+dep) ~= keys x 156. 100 keys -&gt; ~15,600 one-way pax/yr. Airport(MLE)&lt;-&gt;this resort is the sole transfer corridor (boat/seaplane only; no road/air alt - R3-EXCEPTION: arrivals = crossing ridership).</t>
         </is>
@@ -9198,7 +9385,7 @@
         <v/>
       </c>
       <c r="AL39" s="34">
-        <f>IF(OR(AG39="",R39=0),"",MIN(IF(AS39="",9.9E+99,AS39),FLOOR(AK39/R39,1)))</f>
+        <f>IF(OR(AG39="",R39=0),"",MIN(IF(AT39="",9.9E+99,AT39),FLOOR(AK39/R39,1)))</f>
         <v/>
       </c>
       <c r="AM39" s="38">
@@ -9206,7 +9393,7 @@
         <v/>
       </c>
       <c r="AN39" s="36">
-        <f>IF(OR(AG39="",R39=0),"",MIN(IF(AS39="",9.9E+99,AS39),AK39/R39))</f>
+        <f>IF(OR(AG39="",R39=0),"",MIN(IF(AT39="",9.9E+99,AT39),AK39/R39))</f>
         <v/>
       </c>
       <c r="AO39" s="38">
@@ -9214,29 +9401,34 @@
         <v/>
       </c>
       <c r="AP39" s="40" t="n"/>
-      <c r="AQ39" s="41" t="n"/>
+      <c r="AQ39" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR39" s="41" t="n"/>
-      <c r="AS39" s="42" t="n">
+      <c r="AS39" s="41" t="n"/>
+      <c r="AT39" s="42" t="n">
         <v>4</v>
       </c>
-      <c r="AT39" s="43">
+      <c r="AU39" s="43">
         <f>IF(((S39*pax_cap*load_thin*ROUND(K39*L39*revleg_thin,0))-(((battery/range_nm)*D39*ROUND(K39*L39*revleg_thin,0)*VLOOKUP(B39,country_opex,3,FALSE))+V39+W39+X39+Y39+Z39))&lt;=0,"",VLOOKUP(B39,country_opex,7,FALSE)/((S39*pax_cap*load_thin*ROUND(K39*L39*revleg_thin,0))-(((battery/range_nm)*D39*ROUND(K39*L39*revleg_thin,0)*VLOOKUP(B39,country_opex,3,FALSE))+V39+W39+X39+Y39+Z39)))</f>
         <v/>
       </c>
-      <c r="AU39" s="43">
+      <c r="AV39" s="43">
         <f>IF(((S39*pax_cap*load_mid*ROUND(K39*L39*revleg_mid,0))-(((battery/range_nm)*D39*ROUND(K39*L39*revleg_mid,0)*VLOOKUP(B39,country_opex,3,FALSE))+V39+W39+X39+Y39+Z39))&lt;=0,"",VLOOKUP(B39,country_opex,7,FALSE)/((S39*pax_cap*load_mid*ROUND(K39*L39*revleg_mid,0))-(((battery/range_nm)*D39*ROUND(K39*L39*revleg_mid,0)*VLOOKUP(B39,country_opex,3,FALSE))+V39+W39+X39+Y39+Z39)))</f>
         <v/>
       </c>
-      <c r="AV39" s="43">
+      <c r="AW39" s="43">
         <f>IF(((S39*pax_cap*load_full*ROUND(K39*L39*revleg_full,0))-(((battery/range_nm)*D39*ROUND(K39*L39*revleg_full,0)*VLOOKUP(B39,country_opex,3,FALSE))+V39+W39+X39+Y39+Z39))&lt;=0,"",VLOOKUP(B39,country_opex,7,FALSE)/((S39*pax_cap*load_full*ROUND(K39*L39*revleg_full,0))-(((battery/range_nm)*D39*ROUND(K39*L39*revleg_full,0)*VLOOKUP(B39,country_opex,3,FALSE))+V39+W39+X39+Y39+Z39)))</f>
         <v/>
       </c>
-      <c r="AW39" s="44" t="inlineStr">
+      <c r="AX39" s="44" t="inlineStr">
         <is>
           <t>Patina Maldives Fari Islands. Luxury Escapes listing: shared roundtrip speedboat US$950/adult +28.7% tax = ~$610/way all-in. The Luxury Traveller review: $730/adult RT = $365/way. Same Fari Islands lagoon as Ritz (~50-min speedboat). Premium per-seat ~$450/way (mid of $365-475 base band).</t>
         </is>
       </c>
-      <c r="AX39" s="44" t="inlineStr">
+      <c r="AY39" s="44" t="inlineStr">
         <is>
           <t>Modeled from resort key count. Patina Maldives, Fari Islands: ~90 villas/keys (published resort/Virtuoso/booking figures). corridor_annual_oneway_pax = keys x 365 x occ(0.75) / avg_stay(7 nights) x guests/key(2) x 2 (arr+dep) ~= keys x 156. 90 keys -&gt; ~14,100 one-way pax/yr. Airport(MLE)&lt;-&gt;this resort is the sole transfer corridor (boat/seaplane only; no road/air alt - R3-EXCEPTION: arrivals = crossing ridership).</t>
         </is>
@@ -9394,7 +9586,7 @@
         <v/>
       </c>
       <c r="AL40" s="34">
-        <f>IF(OR(AG40="",R40=0),"",MIN(IF(AS40="",9.9E+99,AS40),FLOOR(AK40/R40,1)))</f>
+        <f>IF(OR(AG40="",R40=0),"",MIN(IF(AT40="",9.9E+99,AT40),FLOOR(AK40/R40,1)))</f>
         <v/>
       </c>
       <c r="AM40" s="38">
@@ -9402,7 +9594,7 @@
         <v/>
       </c>
       <c r="AN40" s="36">
-        <f>IF(OR(AG40="",R40=0),"",MIN(IF(AS40="",9.9E+99,AS40),AK40/R40))</f>
+        <f>IF(OR(AG40="",R40=0),"",MIN(IF(AT40="",9.9E+99,AT40),AK40/R40))</f>
         <v/>
       </c>
       <c r="AO40" s="38">
@@ -9410,29 +9602,34 @@
         <v/>
       </c>
       <c r="AP40" s="40" t="n"/>
-      <c r="AQ40" s="41" t="n"/>
+      <c r="AQ40" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR40" s="41" t="n"/>
-      <c r="AS40" s="42" t="n">
+      <c r="AS40" s="41" t="n"/>
+      <c r="AT40" s="42" t="n">
         <v>5</v>
       </c>
-      <c r="AT40" s="43">
+      <c r="AU40" s="43">
         <f>IF(((S40*pax_cap*load_thin*ROUND(K40*L40*revleg_thin,0))-(((battery/range_nm)*D40*ROUND(K40*L40*revleg_thin,0)*VLOOKUP(B40,country_opex,3,FALSE))+V40+W40+X40+Y40+Z40))&lt;=0,"",VLOOKUP(B40,country_opex,7,FALSE)/((S40*pax_cap*load_thin*ROUND(K40*L40*revleg_thin,0))-(((battery/range_nm)*D40*ROUND(K40*L40*revleg_thin,0)*VLOOKUP(B40,country_opex,3,FALSE))+V40+W40+X40+Y40+Z40)))</f>
         <v/>
       </c>
-      <c r="AU40" s="43">
+      <c r="AV40" s="43">
         <f>IF(((S40*pax_cap*load_mid*ROUND(K40*L40*revleg_mid,0))-(((battery/range_nm)*D40*ROUND(K40*L40*revleg_mid,0)*VLOOKUP(B40,country_opex,3,FALSE))+V40+W40+X40+Y40+Z40))&lt;=0,"",VLOOKUP(B40,country_opex,7,FALSE)/((S40*pax_cap*load_mid*ROUND(K40*L40*revleg_mid,0))-(((battery/range_nm)*D40*ROUND(K40*L40*revleg_mid,0)*VLOOKUP(B40,country_opex,3,FALSE))+V40+W40+X40+Y40+Z40)))</f>
         <v/>
       </c>
-      <c r="AV40" s="43">
+      <c r="AW40" s="43">
         <f>IF(((S40*pax_cap*load_full*ROUND(K40*L40*revleg_full,0))-(((battery/range_nm)*D40*ROUND(K40*L40*revleg_full,0)*VLOOKUP(B40,country_opex,3,FALSE))+V40+W40+X40+Y40+Z40))&lt;=0,"",VLOOKUP(B40,country_opex,7,FALSE)/((S40*pax_cap*load_full*ROUND(K40*L40*revleg_full,0))-(((battery/range_nm)*D40*ROUND(K40*L40*revleg_full,0)*VLOOKUP(B40,country_opex,3,FALSE))+V40+W40+X40+Y40+Z40)))</f>
         <v/>
       </c>
-      <c r="AW40" s="44" t="inlineStr">
+      <c r="AX40" s="44" t="inlineStr">
         <is>
           <t>immaldives.com Maldives transfer costs (May 2026): shared speedboat $100-490 RT pp (=$50-245 OW); shared seaplane $400-820 RT pp (=$200-410 OW). atolltransfer.com scheduled $30-195 OW. Navier premium per-seat anchored between local premium speedboat and the seaplane the resort otherwise charges (R-MALDIVES-1).</t>
         </is>
       </c>
-      <c r="AX40" s="44" t="inlineStr">
+      <c r="AY40" s="44" t="inlineStr">
         <is>
           <t>Modeled arrivals = published keys x occupancy 0.70 (Maldives Min. of Tourism avg) x (365/6.5 nights avg stay) x 1.9 pax/room. Inbound one-way transfers. T5-modeled/med; keys T1 resort-published. NULL for pure inter-resort excursion legs (R2).</t>
         </is>
@@ -9590,7 +9787,7 @@
         <v/>
       </c>
       <c r="AL41" s="34">
-        <f>IF(OR(AG41="",R41=0),"",MIN(IF(AS41="",9.9E+99,AS41),FLOOR(AK41/R41,1)))</f>
+        <f>IF(OR(AG41="",R41=0),"",MIN(IF(AT41="",9.9E+99,AT41),FLOOR(AK41/R41,1)))</f>
         <v/>
       </c>
       <c r="AM41" s="38">
@@ -9598,7 +9795,7 @@
         <v/>
       </c>
       <c r="AN41" s="36">
-        <f>IF(OR(AG41="",R41=0),"",MIN(IF(AS41="",9.9E+99,AS41),AK41/R41))</f>
+        <f>IF(OR(AG41="",R41=0),"",MIN(IF(AT41="",9.9E+99,AT41),AK41/R41))</f>
         <v/>
       </c>
       <c r="AO41" s="38">
@@ -9606,29 +9803,34 @@
         <v/>
       </c>
       <c r="AP41" s="40" t="n"/>
-      <c r="AQ41" s="41" t="n"/>
+      <c r="AQ41" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR41" s="41" t="n"/>
-      <c r="AS41" s="42" t="n">
+      <c r="AS41" s="41" t="n"/>
+      <c r="AT41" s="42" t="n">
         <v>5</v>
       </c>
-      <c r="AT41" s="43">
+      <c r="AU41" s="43">
         <f>IF(((S41*pax_cap*load_thin*ROUND(K41*L41*revleg_thin,0))-(((battery/range_nm)*D41*ROUND(K41*L41*revleg_thin,0)*VLOOKUP(B41,country_opex,3,FALSE))+V41+W41+X41+Y41+Z41))&lt;=0,"",VLOOKUP(B41,country_opex,7,FALSE)/((S41*pax_cap*load_thin*ROUND(K41*L41*revleg_thin,0))-(((battery/range_nm)*D41*ROUND(K41*L41*revleg_thin,0)*VLOOKUP(B41,country_opex,3,FALSE))+V41+W41+X41+Y41+Z41)))</f>
         <v/>
       </c>
-      <c r="AU41" s="43">
+      <c r="AV41" s="43">
         <f>IF(((S41*pax_cap*load_mid*ROUND(K41*L41*revleg_mid,0))-(((battery/range_nm)*D41*ROUND(K41*L41*revleg_mid,0)*VLOOKUP(B41,country_opex,3,FALSE))+V41+W41+X41+Y41+Z41))&lt;=0,"",VLOOKUP(B41,country_opex,7,FALSE)/((S41*pax_cap*load_mid*ROUND(K41*L41*revleg_mid,0))-(((battery/range_nm)*D41*ROUND(K41*L41*revleg_mid,0)*VLOOKUP(B41,country_opex,3,FALSE))+V41+W41+X41+Y41+Z41)))</f>
         <v/>
       </c>
-      <c r="AV41" s="43">
+      <c r="AW41" s="43">
         <f>IF(((S41*pax_cap*load_full*ROUND(K41*L41*revleg_full,0))-(((battery/range_nm)*D41*ROUND(K41*L41*revleg_full,0)*VLOOKUP(B41,country_opex,3,FALSE))+V41+W41+X41+Y41+Z41))&lt;=0,"",VLOOKUP(B41,country_opex,7,FALSE)/((S41*pax_cap*load_full*ROUND(K41*L41*revleg_full,0))-(((battery/range_nm)*D41*ROUND(K41*L41*revleg_full,0)*VLOOKUP(B41,country_opex,3,FALSE))+V41+W41+X41+Y41+Z41)))</f>
         <v/>
       </c>
-      <c r="AW41" s="44" t="inlineStr">
+      <c r="AX41" s="44" t="inlineStr">
         <is>
           <t>immaldives.com Maldives transfer costs (May 2026): shared speedboat $100-490 RT pp (=$50-245 OW); shared seaplane $400-820 RT pp (=$200-410 OW). atolltransfer.com scheduled $30-195 OW. Navier premium per-seat anchored between local premium speedboat and the seaplane the resort otherwise charges (R-MALDIVES-1).</t>
         </is>
       </c>
-      <c r="AX41" s="44" t="inlineStr">
+      <c r="AY41" s="44" t="inlineStr">
         <is>
           <t>Modeled arrivals = published keys x occupancy 0.70 (Maldives Min. of Tourism avg) x (365/6.5 nights avg stay) x 1.9 pax/room. Inbound one-way transfers. T5-modeled/med; keys T1 resort-published. NULL for pure inter-resort excursion legs (R2).</t>
         </is>
@@ -9786,7 +9988,7 @@
         <v/>
       </c>
       <c r="AL42" s="34">
-        <f>IF(OR(AG42="",R42=0),"",MIN(IF(AS42="",9.9E+99,AS42),FLOOR(AK42/R42,1)))</f>
+        <f>IF(OR(AG42="",R42=0),"",MIN(IF(AT42="",9.9E+99,AT42),FLOOR(AK42/R42,1)))</f>
         <v/>
       </c>
       <c r="AM42" s="38">
@@ -9794,7 +9996,7 @@
         <v/>
       </c>
       <c r="AN42" s="36">
-        <f>IF(OR(AG42="",R42=0),"",MIN(IF(AS42="",9.9E+99,AS42),AK42/R42))</f>
+        <f>IF(OR(AG42="",R42=0),"",MIN(IF(AT42="",9.9E+99,AT42),AK42/R42))</f>
         <v/>
       </c>
       <c r="AO42" s="38">
@@ -9802,29 +10004,34 @@
         <v/>
       </c>
       <c r="AP42" s="40" t="n"/>
-      <c r="AQ42" s="41" t="n"/>
+      <c r="AQ42" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR42" s="41" t="n"/>
-      <c r="AS42" s="42" t="n">
+      <c r="AS42" s="41" t="n"/>
+      <c r="AT42" s="42" t="n">
         <v>4</v>
       </c>
-      <c r="AT42" s="43">
+      <c r="AU42" s="43">
         <f>IF(((S42*pax_cap*load_thin*ROUND(K42*L42*revleg_thin,0))-(((battery/range_nm)*D42*ROUND(K42*L42*revleg_thin,0)*VLOOKUP(B42,country_opex,3,FALSE))+V42+W42+X42+Y42+Z42))&lt;=0,"",VLOOKUP(B42,country_opex,7,FALSE)/((S42*pax_cap*load_thin*ROUND(K42*L42*revleg_thin,0))-(((battery/range_nm)*D42*ROUND(K42*L42*revleg_thin,0)*VLOOKUP(B42,country_opex,3,FALSE))+V42+W42+X42+Y42+Z42)))</f>
         <v/>
       </c>
-      <c r="AU42" s="43">
+      <c r="AV42" s="43">
         <f>IF(((S42*pax_cap*load_mid*ROUND(K42*L42*revleg_mid,0))-(((battery/range_nm)*D42*ROUND(K42*L42*revleg_mid,0)*VLOOKUP(B42,country_opex,3,FALSE))+V42+W42+X42+Y42+Z42))&lt;=0,"",VLOOKUP(B42,country_opex,7,FALSE)/((S42*pax_cap*load_mid*ROUND(K42*L42*revleg_mid,0))-(((battery/range_nm)*D42*ROUND(K42*L42*revleg_mid,0)*VLOOKUP(B42,country_opex,3,FALSE))+V42+W42+X42+Y42+Z42)))</f>
         <v/>
       </c>
-      <c r="AV42" s="43">
+      <c r="AW42" s="43">
         <f>IF(((S42*pax_cap*load_full*ROUND(K42*L42*revleg_full,0))-(((battery/range_nm)*D42*ROUND(K42*L42*revleg_full,0)*VLOOKUP(B42,country_opex,3,FALSE))+V42+W42+X42+Y42+Z42))&lt;=0,"",VLOOKUP(B42,country_opex,7,FALSE)/((S42*pax_cap*load_full*ROUND(K42*L42*revleg_full,0))-(((battery/range_nm)*D42*ROUND(K42*L42*revleg_full,0)*VLOOKUP(B42,country_opex,3,FALSE))+V42+W42+X42+Y42+Z42)))</f>
         <v/>
       </c>
-      <c r="AW42" s="44" t="inlineStr">
+      <c r="AX42" s="44" t="inlineStr">
         <is>
           <t>Constance Halaveli, North Ari, 25-min seaplane. Tripadvisor FAQ (resort-quoted): seaplane USD 530/adult RT = $265/way. Booking.com 2026: seaplane both-ways service fee USD 650/adult = $325/way. 90-min speedboat alternative also offered (Angelfish Travel). Private seaplane ~$1,500/way (charter). Premium per-seat seaplane $300/way. NOTE: &gt;40nm leg - Navier (Pioneer II &lt;=70nm) substitutes the SEAPLANE here, big value capture.</t>
         </is>
       </c>
-      <c r="AX42" s="44" t="inlineStr">
+      <c r="AY42" s="44" t="inlineStr">
         <is>
           <t>Modeled from resort key count. Constance Halaveli (North Ari): ~86 villas/keys (published resort/Virtuoso/booking figures). corridor_annual_oneway_pax = keys x 365 x occ(0.75) / avg_stay(7 nights) x guests/key(2) x 2 (arr+dep) ~= keys x 156. 86 keys -&gt; ~13,400 one-way pax/yr. Airport(MLE)&lt;-&gt;this resort is the sole transfer corridor (boat/seaplane only; no road/air alt - R3-EXCEPTION: arrivals = crossing ridership).</t>
         </is>
@@ -9982,7 +10189,7 @@
         <v/>
       </c>
       <c r="AL43" s="34">
-        <f>IF(OR(AG43="",R43=0),"",MIN(IF(AS43="",9.9E+99,AS43),FLOOR(AK43/R43,1)))</f>
+        <f>IF(OR(AG43="",R43=0),"",MIN(IF(AT43="",9.9E+99,AT43),FLOOR(AK43/R43,1)))</f>
         <v/>
       </c>
       <c r="AM43" s="38">
@@ -9990,7 +10197,7 @@
         <v/>
       </c>
       <c r="AN43" s="36">
-        <f>IF(OR(AG43="",R43=0),"",MIN(IF(AS43="",9.9E+99,AS43),AK43/R43))</f>
+        <f>IF(OR(AG43="",R43=0),"",MIN(IF(AT43="",9.9E+99,AT43),AK43/R43))</f>
         <v/>
       </c>
       <c r="AO43" s="38">
@@ -9998,29 +10205,34 @@
         <v/>
       </c>
       <c r="AP43" s="40" t="n"/>
-      <c r="AQ43" s="41" t="n"/>
+      <c r="AQ43" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR43" s="41" t="n"/>
-      <c r="AS43" s="42" t="n">
+      <c r="AS43" s="41" t="n"/>
+      <c r="AT43" s="42" t="n">
         <v>5</v>
       </c>
-      <c r="AT43" s="43">
+      <c r="AU43" s="43">
         <f>IF(((S43*pax_cap*load_thin*ROUND(K43*L43*revleg_thin,0))-(((battery/range_nm)*D43*ROUND(K43*L43*revleg_thin,0)*VLOOKUP(B43,country_opex,3,FALSE))+V43+W43+X43+Y43+Z43))&lt;=0,"",VLOOKUP(B43,country_opex,7,FALSE)/((S43*pax_cap*load_thin*ROUND(K43*L43*revleg_thin,0))-(((battery/range_nm)*D43*ROUND(K43*L43*revleg_thin,0)*VLOOKUP(B43,country_opex,3,FALSE))+V43+W43+X43+Y43+Z43)))</f>
         <v/>
       </c>
-      <c r="AU43" s="43">
+      <c r="AV43" s="43">
         <f>IF(((S43*pax_cap*load_mid*ROUND(K43*L43*revleg_mid,0))-(((battery/range_nm)*D43*ROUND(K43*L43*revleg_mid,0)*VLOOKUP(B43,country_opex,3,FALSE))+V43+W43+X43+Y43+Z43))&lt;=0,"",VLOOKUP(B43,country_opex,7,FALSE)/((S43*pax_cap*load_mid*ROUND(K43*L43*revleg_mid,0))-(((battery/range_nm)*D43*ROUND(K43*L43*revleg_mid,0)*VLOOKUP(B43,country_opex,3,FALSE))+V43+W43+X43+Y43+Z43)))</f>
         <v/>
       </c>
-      <c r="AV43" s="43">
+      <c r="AW43" s="43">
         <f>IF(((S43*pax_cap*load_full*ROUND(K43*L43*revleg_full,0))-(((battery/range_nm)*D43*ROUND(K43*L43*revleg_full,0)*VLOOKUP(B43,country_opex,3,FALSE))+V43+W43+X43+Y43+Z43))&lt;=0,"",VLOOKUP(B43,country_opex,7,FALSE)/((S43*pax_cap*load_full*ROUND(K43*L43*revleg_full,0))-(((battery/range_nm)*D43*ROUND(K43*L43*revleg_full,0)*VLOOKUP(B43,country_opex,3,FALSE))+V43+W43+X43+Y43+Z43)))</f>
         <v/>
       </c>
-      <c r="AW43" s="44" t="inlineStr">
+      <c r="AX43" s="44" t="inlineStr">
         <is>
           <t>immaldives.com Maldives transfer costs (May 2026): shared speedboat $100-490 RT pp (=$50-245 OW); shared seaplane $400-820 RT pp (=$200-410 OW). atolltransfer.com scheduled $30-195 OW. Navier premium per-seat anchored between local premium speedboat and the seaplane the resort otherwise charges (R-MALDIVES-1).</t>
         </is>
       </c>
-      <c r="AX43" s="44" t="inlineStr">
+      <c r="AY43" s="44" t="inlineStr">
         <is>
           <t>Modeled arrivals = published keys x occupancy 0.70 (Maldives Min. of Tourism avg) x (365/6.5 nights avg stay) x 1.9 pax/room. Inbound one-way transfers. T5-modeled/med; keys T1 resort-published. NULL for pure inter-resort excursion legs (R2).</t>
         </is>
@@ -10178,7 +10390,7 @@
         <v/>
       </c>
       <c r="AL44" s="34">
-        <f>IF(OR(AG44="",R44=0),"",MIN(IF(AS44="",9.9E+99,AS44),FLOOR(AK44/R44,1)))</f>
+        <f>IF(OR(AG44="",R44=0),"",MIN(IF(AT44="",9.9E+99,AT44),FLOOR(AK44/R44,1)))</f>
         <v/>
       </c>
       <c r="AM44" s="38">
@@ -10186,7 +10398,7 @@
         <v/>
       </c>
       <c r="AN44" s="36">
-        <f>IF(OR(AG44="",R44=0),"",MIN(IF(AS44="",9.9E+99,AS44),AK44/R44))</f>
+        <f>IF(OR(AG44="",R44=0),"",MIN(IF(AT44="",9.9E+99,AT44),AK44/R44))</f>
         <v/>
       </c>
       <c r="AO44" s="38">
@@ -10194,29 +10406,34 @@
         <v/>
       </c>
       <c r="AP44" s="40" t="n"/>
-      <c r="AQ44" s="41" t="n"/>
+      <c r="AQ44" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR44" s="41" t="n"/>
-      <c r="AS44" s="42" t="n">
+      <c r="AS44" s="41" t="n"/>
+      <c r="AT44" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="AT44" s="43">
+      <c r="AU44" s="43">
         <f>IF(((S44*pax_cap*load_thin*ROUND(K44*L44*revleg_thin,0))-(((battery/range_nm)*D44*ROUND(K44*L44*revleg_thin,0)*VLOOKUP(B44,country_opex,3,FALSE))+V44+W44+X44+Y44+Z44))&lt;=0,"",VLOOKUP(B44,country_opex,7,FALSE)/((S44*pax_cap*load_thin*ROUND(K44*L44*revleg_thin,0))-(((battery/range_nm)*D44*ROUND(K44*L44*revleg_thin,0)*VLOOKUP(B44,country_opex,3,FALSE))+V44+W44+X44+Y44+Z44)))</f>
         <v/>
       </c>
-      <c r="AU44" s="43">
+      <c r="AV44" s="43">
         <f>IF(((S44*pax_cap*load_mid*ROUND(K44*L44*revleg_mid,0))-(((battery/range_nm)*D44*ROUND(K44*L44*revleg_mid,0)*VLOOKUP(B44,country_opex,3,FALSE))+V44+W44+X44+Y44+Z44))&lt;=0,"",VLOOKUP(B44,country_opex,7,FALSE)/((S44*pax_cap*load_mid*ROUND(K44*L44*revleg_mid,0))-(((battery/range_nm)*D44*ROUND(K44*L44*revleg_mid,0)*VLOOKUP(B44,country_opex,3,FALSE))+V44+W44+X44+Y44+Z44)))</f>
         <v/>
       </c>
-      <c r="AV44" s="43">
+      <c r="AW44" s="43">
         <f>IF(((S44*pax_cap*load_full*ROUND(K44*L44*revleg_full,0))-(((battery/range_nm)*D44*ROUND(K44*L44*revleg_full,0)*VLOOKUP(B44,country_opex,3,FALSE))+V44+W44+X44+Y44+Z44))&lt;=0,"",VLOOKUP(B44,country_opex,7,FALSE)/((S44*pax_cap*load_full*ROUND(K44*L44*revleg_full,0))-(((battery/range_nm)*D44*ROUND(K44*L44*revleg_full,0)*VLOOKUP(B44,country_opex,3,FALSE))+V44+W44+X44+Y44+Z44)))</f>
         <v/>
       </c>
-      <c r="AW44" s="44" t="inlineStr">
+      <c r="AX44" s="44" t="inlineStr">
         <is>
           <t>Conrad Maldives Rangali Island OFFICIAL (conradmaldives.com): seaplane return transfer USD 700 net/adult = $350/way. Frequent Miler: seaplane for two = $1,350 = $337/way. getexperience blog: $600-750 RT typical. Premium per-seat seaplane $350/way. &gt;40nm - Navier substitutes the SEAPLANE (Pioneer II reaches 57.6nm &lt;=70nm); large value capture vs $700 RT seaplane.</t>
         </is>
       </c>
-      <c r="AX44" s="44" t="inlineStr">
+      <c r="AY44" s="44" t="inlineStr">
         <is>
           <t>Modeled from resort key count. Conrad Maldives Rangali Island (South Ari): ~150 villas/keys (published resort/Virtuoso/booking figures). corridor_annual_oneway_pax = keys x 365 x occ(0.75) / avg_stay(7 nights) x guests/key(2) x 2 (arr+dep) ~= keys x 156. 150 keys -&gt; ~23,500 one-way pax/yr. Airport(MLE)&lt;-&gt;this resort is the sole transfer corridor (boat/seaplane only; no road/air alt - R3-EXCEPTION: arrivals = crossing ridership).</t>
         </is>
@@ -10374,7 +10591,7 @@
         <v/>
       </c>
       <c r="AL45" s="34">
-        <f>IF(OR(AG45="",R45=0),"",MIN(IF(AS45="",9.9E+99,AS45),FLOOR(AK45/R45,1)))</f>
+        <f>IF(OR(AG45="",R45=0),"",MIN(IF(AT45="",9.9E+99,AT45),FLOOR(AK45/R45,1)))</f>
         <v/>
       </c>
       <c r="AM45" s="38">
@@ -10382,7 +10599,7 @@
         <v/>
       </c>
       <c r="AN45" s="36">
-        <f>IF(OR(AG45="",R45=0),"",MIN(IF(AS45="",9.9E+99,AS45),AK45/R45))</f>
+        <f>IF(OR(AG45="",R45=0),"",MIN(IF(AT45="",9.9E+99,AT45),AK45/R45))</f>
         <v/>
       </c>
       <c r="AO45" s="38">
@@ -10390,29 +10607,34 @@
         <v/>
       </c>
       <c r="AP45" s="40" t="n"/>
-      <c r="AQ45" s="41" t="n"/>
+      <c r="AQ45" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR45" s="41" t="n"/>
-      <c r="AS45" s="42" t="n">
+      <c r="AS45" s="41" t="n"/>
+      <c r="AT45" s="42" t="n">
         <v>4</v>
       </c>
-      <c r="AT45" s="43">
+      <c r="AU45" s="43">
         <f>IF(((S45*pax_cap*load_thin*ROUND(K45*L45*revleg_thin,0))-(((battery/range_nm)*D45*ROUND(K45*L45*revleg_thin,0)*VLOOKUP(B45,country_opex,3,FALSE))+V45+W45+X45+Y45+Z45))&lt;=0,"",VLOOKUP(B45,country_opex,7,FALSE)/((S45*pax_cap*load_thin*ROUND(K45*L45*revleg_thin,0))-(((battery/range_nm)*D45*ROUND(K45*L45*revleg_thin,0)*VLOOKUP(B45,country_opex,3,FALSE))+V45+W45+X45+Y45+Z45)))</f>
         <v/>
       </c>
-      <c r="AU45" s="43">
+      <c r="AV45" s="43">
         <f>IF(((S45*pax_cap*load_mid*ROUND(K45*L45*revleg_mid,0))-(((battery/range_nm)*D45*ROUND(K45*L45*revleg_mid,0)*VLOOKUP(B45,country_opex,3,FALSE))+V45+W45+X45+Y45+Z45))&lt;=0,"",VLOOKUP(B45,country_opex,7,FALSE)/((S45*pax_cap*load_mid*ROUND(K45*L45*revleg_mid,0))-(((battery/range_nm)*D45*ROUND(K45*L45*revleg_mid,0)*VLOOKUP(B45,country_opex,3,FALSE))+V45+W45+X45+Y45+Z45)))</f>
         <v/>
       </c>
-      <c r="AV45" s="43">
+      <c r="AW45" s="43">
         <f>IF(((S45*pax_cap*load_full*ROUND(K45*L45*revleg_full,0))-(((battery/range_nm)*D45*ROUND(K45*L45*revleg_full,0)*VLOOKUP(B45,country_opex,3,FALSE))+V45+W45+X45+Y45+Z45))&lt;=0,"",VLOOKUP(B45,country_opex,7,FALSE)/((S45*pax_cap*load_full*ROUND(K45*L45*revleg_full,0))-(((battery/range_nm)*D45*ROUND(K45*L45*revleg_full,0)*VLOOKUP(B45,country_opex,3,FALSE))+V45+W45+X45+Y45+Z45)))</f>
         <v/>
       </c>
-      <c r="AW45" s="44" t="inlineStr">
+      <c r="AX45" s="44" t="inlineStr">
         <is>
           <t>The Westin Maldives Miriandhoo OFFICIAL (marriott.com): return seaplane USD 620/adult RT = $310/way (domestic flight+speedboat alt USD 495 RT). The Points Guy: $475 RT; hyderseatravels: $500 RT; traveltomtom: $375 RT (incl taxes). Premium per-seat seaplane $310/way. &gt;40nm - Navier substitutes SEAPLANE (60.6nm &lt;=70nm).</t>
         </is>
       </c>
-      <c r="AX45" s="44" t="inlineStr">
+      <c r="AY45" s="44" t="inlineStr">
         <is>
           <t>Modeled from resort key count. The Westin Maldives Miriandhoo (Baa): ~70 villas/keys (published resort/Virtuoso/booking figures). corridor_annual_oneway_pax = keys x 365 x occ(0.75) / avg_stay(7 nights) x guests/key(2) x 2 (arr+dep) ~= keys x 156. 70 keys -&gt; ~10,900 one-way pax/yr. Airport(MLE)&lt;-&gt;this resort is the sole transfer corridor (boat/seaplane only; no road/air alt - R3-EXCEPTION: arrivals = crossing ridership).</t>
         </is>
@@ -10570,7 +10792,7 @@
         <v/>
       </c>
       <c r="AL46" s="34">
-        <f>IF(OR(AG46="",R46=0),"",MIN(IF(AS46="",9.9E+99,AS46),FLOOR(AK46/R46,1)))</f>
+        <f>IF(OR(AG46="",R46=0),"",MIN(IF(AT46="",9.9E+99,AT46),FLOOR(AK46/R46,1)))</f>
         <v/>
       </c>
       <c r="AM46" s="38">
@@ -10578,7 +10800,7 @@
         <v/>
       </c>
       <c r="AN46" s="36">
-        <f>IF(OR(AG46="",R46=0),"",MIN(IF(AS46="",9.9E+99,AS46),AK46/R46))</f>
+        <f>IF(OR(AG46="",R46=0),"",MIN(IF(AT46="",9.9E+99,AT46),AK46/R46))</f>
         <v/>
       </c>
       <c r="AO46" s="38">
@@ -10586,29 +10808,34 @@
         <v/>
       </c>
       <c r="AP46" s="40" t="n"/>
-      <c r="AQ46" s="41" t="n"/>
+      <c r="AQ46" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR46" s="41" t="n"/>
-      <c r="AS46" s="42" t="n">
+      <c r="AS46" s="41" t="n"/>
+      <c r="AT46" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="AT46" s="43">
+      <c r="AU46" s="43">
         <f>IF(((S46*pax_cap*load_thin*ROUND(K46*L46*revleg_thin,0))-(((battery/range_nm)*D46*ROUND(K46*L46*revleg_thin,0)*VLOOKUP(B46,country_opex,3,FALSE))+V46+W46+X46+Y46+Z46))&lt;=0,"",VLOOKUP(B46,country_opex,7,FALSE)/((S46*pax_cap*load_thin*ROUND(K46*L46*revleg_thin,0))-(((battery/range_nm)*D46*ROUND(K46*L46*revleg_thin,0)*VLOOKUP(B46,country_opex,3,FALSE))+V46+W46+X46+Y46+Z46)))</f>
         <v/>
       </c>
-      <c r="AU46" s="43">
+      <c r="AV46" s="43">
         <f>IF(((S46*pax_cap*load_mid*ROUND(K46*L46*revleg_mid,0))-(((battery/range_nm)*D46*ROUND(K46*L46*revleg_mid,0)*VLOOKUP(B46,country_opex,3,FALSE))+V46+W46+X46+Y46+Z46))&lt;=0,"",VLOOKUP(B46,country_opex,7,FALSE)/((S46*pax_cap*load_mid*ROUND(K46*L46*revleg_mid,0))-(((battery/range_nm)*D46*ROUND(K46*L46*revleg_mid,0)*VLOOKUP(B46,country_opex,3,FALSE))+V46+W46+X46+Y46+Z46)))</f>
         <v/>
       </c>
-      <c r="AV46" s="43">
+      <c r="AW46" s="43">
         <f>IF(((S46*pax_cap*load_full*ROUND(K46*L46*revleg_full,0))-(((battery/range_nm)*D46*ROUND(K46*L46*revleg_full,0)*VLOOKUP(B46,country_opex,3,FALSE))+V46+W46+X46+Y46+Z46))&lt;=0,"",VLOOKUP(B46,country_opex,7,FALSE)/((S46*pax_cap*load_full*ROUND(K46*L46*revleg_full,0))-(((battery/range_nm)*D46*ROUND(K46*L46*revleg_full,0)*VLOOKUP(B46,country_opex,3,FALSE))+V46+W46+X46+Y46+Z46)))</f>
         <v/>
       </c>
-      <c r="AW46" s="44" t="inlineStr">
+      <c r="AX46" s="44" t="inlineStr">
         <is>
           <t>Soneva Fushi, Baa, OFFICIAL (soneva.com 'Your Journey'): round-trip SHARED Soneva private seaplane USD 1,300/adult = $650/way; luxurytravelexpert confirms $1,300 RT. immaldives 2026 shared-TMA band $550-720 RT (=~$635/way mid) for the generic operator. Soneva runs its own premium seaplane (the premium tier) - anchor $650/way. &gt;40nm - Navier substitutes SEAPLANE (61.8nm &lt;=70nm).</t>
         </is>
       </c>
-      <c r="AX46" s="44" t="inlineStr">
+      <c r="AY46" s="44" t="inlineStr">
         <is>
           <t>Modeled from resort key count. Soneva Fushi (Kunfunadhoo, Baa): ~71 villas/keys (published resort/Virtuoso/booking figures). corridor_annual_oneway_pax = keys x 365 x occ(0.75) / avg_stay(7 nights) x guests/key(2) x 2 (arr+dep) ~= keys x 156. 71 keys -&gt; ~11,100 one-way pax/yr. Airport(MLE)&lt;-&gt;this resort is the sole transfer corridor (boat/seaplane only; no road/air alt - R3-EXCEPTION: arrivals = crossing ridership).</t>
         </is>
@@ -10687,7 +10914,7 @@
         </is>
       </c>
       <c r="C51" s="23">
-        <f>SUMIFS(AN4:AN46,A4:A46,"Maldives (JIH)",AP4:AP46,"=",AQ4:AQ46,"=",AR4:AR46,"=")</f>
+        <f>SUMIFS(AN4:AN46,A4:A46,"Maldives (JIH)",AP4:AP46,"=",AQ4:AQ46,"Grounded")</f>
         <v/>
       </c>
       <c r="D51" s="49">
@@ -10695,7 +10922,7 @@
         <v/>
       </c>
       <c r="E51" s="50">
-        <f>SUMIFS(AO4:AO46,A4:A46,"Maldives (JIH)",AP4:AP46,"=",AQ4:AQ46,"=",AR4:AR46,"=")</f>
+        <f>SUMIFS(AO4:AO46,A4:A46,"Maldives (JIH)",AP4:AP46,"=",AQ4:AQ46,"Grounded")</f>
         <v/>
       </c>
     </row>
@@ -10711,6 +10938,21 @@
       </c>
       <c r="E52" s="46">
         <f>SUM(E51:E51)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="20" t="inlineStr">
+        <is>
+          <t>ESTIMATED DEMAND (country-median cascade; held OUT of grounded floor)</t>
+        </is>
+      </c>
+      <c r="D53" s="51">
+        <f>SUMIF(AQ4:AQ46,"Estimated",AL4:AL46)</f>
+        <v/>
+      </c>
+      <c r="E53" s="52">
+        <f>SUMIF(AQ4:AQ46,"Estimated",AM4:AM46)</f>
         <v/>
       </c>
     </row>
@@ -10940,7 +11182,7 @@
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Live sum of grounded corridor market-rev (10% capture, today's demand, sourced corridors).</t>
+          <t>Live sum of grounded-floor corridor market-rev only (Floor bucket = Grounded; cascade-estimated rows held out). Matches growth.py _headline_anchor and deck TAM.</t>
         </is>
       </c>
     </row>
@@ -11129,12 +11371,12 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="51" t="inlineStr">
+      <c r="A26" s="53" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="B26" s="52" t="inlineStr">
+      <c r="B26" s="54" t="inlineStr">
         <is>
           <t>All rungs are one multiplication chain off M_today, which is live off the corridor floor. Change any input (a fare, a multiplier, the scenario) and the whole ladder moves. Bands (low/MID/high) are never single points; greenfield census is per-partner.</t>
         </is>
